--- a/src/global/utils/file-utils/locators(2).xlsx
+++ b/src/global/utils/file-utils/locators(2).xlsx
@@ -2721,8 +2721,8 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -13640,7 +13640,7 @@
       <c r="E2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="31"/>
+      <c r="F2" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
@@ -13658,7 +13658,7 @@
       <c r="E3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="31"/>
+      <c r="F3" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
@@ -13676,7 +13676,7 @@
       <c r="E4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="31"/>
+      <c r="F4" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
@@ -13694,7 +13694,7 @@
       <c r="E5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="31"/>
+      <c r="F5" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
@@ -13712,7 +13712,7 @@
       <c r="E6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="31"/>
+      <c r="F6" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
@@ -13730,7 +13730,7 @@
       <c r="E7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="31"/>
+      <c r="F7" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
@@ -13748,7 +13748,7 @@
       <c r="E8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13768,7 +13768,7 @@
       <c r="E9" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13788,7 +13788,7 @@
       <c r="E10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="31"/>
+      <c r="F10" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
@@ -13806,7 +13806,7 @@
       <c r="E11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13826,7 +13826,7 @@
       <c r="E12" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       <c r="E13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="31"/>
+      <c r="F13" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6" t="s">
@@ -13864,7 +13864,7 @@
       <c r="E14" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13884,7 +13884,7 @@
       <c r="E15" s="6" t="s">
         <v>604</v>
       </c>
-      <c r="F15" s="32">
+      <c r="F15" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13904,7 +13904,7 @@
       <c r="E16" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="F16" s="31"/>
+      <c r="F16" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6" t="s">
@@ -13922,7 +13922,7 @@
       <c r="E17" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="F17" s="31"/>
+      <c r="F17" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6" t="s">
@@ -13940,7 +13940,7 @@
       <c r="E18" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="F18" s="31"/>
+      <c r="F18" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6" t="s">
@@ -13958,7 +13958,7 @@
       <c r="E19" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="31"/>
+      <c r="F19" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6" t="s">
@@ -13976,7 +13976,7 @@
       <c r="E20" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="F20" s="31"/>
+      <c r="F20" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="6" t="s">
@@ -13994,7 +13994,7 @@
       <c r="E21" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="8">
         <v>0</v>
       </c>
     </row>
@@ -14014,7 +14014,7 @@
       <c r="E22" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="8">
         <v>0</v>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       <c r="E23" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="8">
         <v>0</v>
       </c>
     </row>
@@ -14054,7 +14054,7 @@
       <c r="E24" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="8">
         <v>0</v>
       </c>
     </row>
@@ -14074,7 +14074,7 @@
       <c r="E25" s="6" t="s">
         <v>614</v>
       </c>
-      <c r="F25" s="31"/>
+      <c r="F25" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="6" t="s">
@@ -14092,7 +14092,7 @@
       <c r="E26" s="6" t="s">
         <v>617</v>
       </c>
-      <c r="F26" s="32">
+      <c r="F26" s="8">
         <v>1</v>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       <c r="E27" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="31"/>
+      <c r="F27" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/global/utils/file-utils/locators(2).xlsx
+++ b/src/global/utils/file-utils/locators(2).xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="18"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="HomePage"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2812" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2817" uniqueCount="809">
   <si>
     <t>page</t>
   </si>
@@ -2456,6 +2456,9 @@
   </si>
   <si>
     <t>a[href="https://x.com/betway"]</t>
+  </si>
+  <si>
+    <t>howtobet2</t>
   </si>
 </sst>
 </file>
@@ -2463,7 +2466,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2548,12 +2551,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2629,7 +2626,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="43">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2721,40 +2718,31 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="15" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="15" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="15" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="15" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
@@ -2763,7 +2751,7 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="18" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3095,7 +3083,7 @@
       <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="40" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3417,7 +3405,7 @@
       <c r="C19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="45" t="s">
+      <c r="D19" s="42" t="s">
         <v>807</v>
       </c>
       <c r="E19" s="29" t="s">
@@ -3426,11 +3414,21 @@
       <c r="F19" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="29"/>
+      <c r="A20" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>774</v>
+      </c>
       <c r="F20" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
@@ -9929,7 +9927,7 @@
     <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9949,7 +9947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -9969,7 +9967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -9989,7 +9987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -10009,7 +10007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -10029,7 +10027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -10049,7 +10047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -10069,7 +10067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -10087,7 +10085,7 @@
       </c>
       <c r="F8" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -10105,7 +10103,7 @@
       </c>
       <c r="F9" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -10125,7 +10123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -10143,7 +10141,7 @@
       </c>
       <c r="F11" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -10161,7 +10159,7 @@
       </c>
       <c r="F12" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -10181,7 +10179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
@@ -10201,7 +10199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
@@ -10221,7 +10219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -10239,7 +10237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="1" t="s">
         <v>6</v>
       </c>
@@ -10257,7 +10255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
@@ -10275,7 +10273,7 @@
       </c>
       <c r="F18" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
@@ -10293,7 +10291,7 @@
       </c>
       <c r="F19" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="1" t="s">
         <v>6</v>
       </c>
@@ -10313,7 +10311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="1" t="s">
         <v>6</v>
       </c>
@@ -10333,7 +10331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="1" t="s">
         <v>6</v>
       </c>
@@ -10351,7 +10349,7 @@
       </c>
       <c r="F22" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
@@ -10371,7 +10369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="1" t="s">
         <v>6</v>
       </c>
@@ -10389,7 +10387,7 @@
       </c>
       <c r="F24" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="1" t="s">
         <v>6</v>
       </c>
@@ -10407,7 +10405,7 @@
       </c>
       <c r="F25" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="1" t="s">
         <v>6</v>
       </c>
@@ -10427,7 +10425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="1" t="s">
         <v>6</v>
       </c>
@@ -10445,7 +10443,7 @@
       </c>
       <c r="F27" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
@@ -10465,7 +10463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="1" t="s">
         <v>6</v>
       </c>
@@ -10483,7 +10481,7 @@
       </c>
       <c r="F29" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="1" t="s">
         <v>6</v>
       </c>
@@ -10503,7 +10501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="1" t="s">
         <v>6</v>
       </c>
@@ -10614,7 +10612,7 @@
       <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="40" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11357,7 +11355,7 @@
       <c r="B9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="41" t="s">
         <v>755</v>
       </c>
       <c r="D9" s="14" t="s">
@@ -11428,7 +11426,7 @@
       <c r="D1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="40" t="s">
         <v>5</v>
       </c>
     </row>
@@ -12111,274 +12109,274 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="36" t="s">
+      <c r="A1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="34" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="35" t="s">
         <v>716</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="36" t="s">
         <v>717</v>
       </c>
-      <c r="C2" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="39" t="s">
+      <c r="C2" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="36" t="s">
         <v>718</v>
       </c>
-      <c r="F2" s="40">
+      <c r="F2" s="37">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="35" t="s">
         <v>716</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="36" t="s">
         <v>719</v>
       </c>
-      <c r="C3" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="39" t="s">
+      <c r="C3" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="36" t="s">
         <v>720</v>
       </c>
-      <c r="F3" s="40">
+      <c r="F3" s="37">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="35" t="s">
         <v>716</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="36" t="s">
         <v>721</v>
       </c>
-      <c r="C4" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="39" t="s">
+      <c r="C4" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="36" t="s">
         <v>722</v>
       </c>
-      <c r="E4" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="41"/>
+      <c r="E4" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="35" t="s">
         <v>716</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="36" t="s">
         <v>723</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="36" t="s">
         <v>724</v>
       </c>
-      <c r="E5" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="40">
+      <c r="E5" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="37">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="35" t="s">
         <v>716</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="36" t="s">
         <v>725</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="36" t="s">
         <v>726</v>
       </c>
-      <c r="E6" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="40">
+      <c r="E6" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="37">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="35" t="s">
         <v>716</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="36" t="s">
         <v>727</v>
       </c>
-      <c r="C7" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="39" t="s">
+      <c r="C7" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="36" t="s">
         <v>728</v>
       </c>
-      <c r="E7" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="41"/>
+      <c r="E7" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="35" t="s">
         <v>716</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="36" t="s">
         <v>729</v>
       </c>
-      <c r="C8" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="39" t="s">
+      <c r="C8" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="36" t="s">
         <v>730</v>
       </c>
-      <c r="E8" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="41"/>
+      <c r="E8" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="35" t="s">
         <v>716</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="36" t="s">
         <v>731</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="36" t="s">
         <v>732</v>
       </c>
-      <c r="E9" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="40">
+      <c r="E9" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="37">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="35" t="s">
         <v>716</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="36" t="s">
         <v>733</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="36" t="s">
         <v>734</v>
       </c>
-      <c r="E10" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="40">
+      <c r="E10" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="37">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="35" t="s">
         <v>716</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="36" t="s">
         <v>470</v>
       </c>
-      <c r="C11" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="39" t="s">
+      <c r="C11" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="36" t="s">
         <v>735</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="36" t="s">
         <v>471</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="37">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="35" t="s">
         <v>716</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="36" t="s">
         <v>472</v>
       </c>
-      <c r="C12" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="39" t="s">
+      <c r="C12" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="36" t="s">
         <v>735</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="36" t="s">
         <v>473</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="37">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="35" t="s">
         <v>716</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="36" t="s">
         <v>736</v>
       </c>
-      <c r="C13" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="39" t="s">
+      <c r="C13" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="36" t="s">
         <v>737</v>
       </c>
-      <c r="E13" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="41"/>
+      <c r="E13" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="35" t="s">
         <v>716</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="35" t="s">
         <v>738</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="E14" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="42">
+      <c r="E14" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="39">
         <v>0</v>
       </c>
     </row>
@@ -12433,7 +12431,7 @@
       <c r="C2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="31" t="s">
         <v>30</v>
       </c>
       <c r="E2" s="17" t="s">
@@ -12453,7 +12451,7 @@
       <c r="C3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="31" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="17" t="s">
@@ -12471,7 +12469,7 @@
       <c r="C4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="31" t="s">
         <v>271</v>
       </c>
       <c r="E4" s="17" t="s">
@@ -12489,7 +12487,7 @@
       <c r="C5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="31" t="s">
         <v>76</v>
       </c>
       <c r="E5" s="17" t="s">
@@ -12509,7 +12507,7 @@
       <c r="C6" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="31" t="s">
         <v>105</v>
       </c>
       <c r="E6" s="17" t="s">
@@ -12527,7 +12525,7 @@
       <c r="C7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="31" t="s">
         <v>168</v>
       </c>
       <c r="E7" s="17" t="s">
@@ -12545,7 +12543,7 @@
       <c r="C8" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="31" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="17" t="s">
@@ -12565,7 +12563,7 @@
       <c r="C9" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="31" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="17" t="s">
@@ -12585,7 +12583,7 @@
       <c r="C10" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="D10" s="31" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="17" t="s">
@@ -12603,7 +12601,7 @@
       <c r="C11" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="31" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="17" t="s">
@@ -12623,7 +12621,7 @@
       <c r="C12" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="31" t="s">
         <v>625</v>
       </c>
       <c r="E12" s="17" t="s">
@@ -12641,7 +12639,7 @@
       <c r="C13" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="31" t="s">
         <v>627</v>
       </c>
       <c r="E13" s="17" t="s">
@@ -12659,7 +12657,7 @@
       <c r="C14" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="31" t="s">
         <v>629</v>
       </c>
       <c r="E14" s="17" t="s">
@@ -12679,7 +12677,7 @@
       <c r="C15" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="31" t="s">
         <v>631</v>
       </c>
       <c r="E15" s="17" t="s">
@@ -12697,7 +12695,7 @@
       <c r="C16" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="34" t="s">
+      <c r="D16" s="31" t="s">
         <v>631</v>
       </c>
       <c r="E16" s="17" t="s">
@@ -12715,7 +12713,7 @@
       <c r="C17" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="34" t="s">
+      <c r="D17" s="31" t="s">
         <v>634</v>
       </c>
       <c r="E17" s="17" t="s">
@@ -12733,7 +12731,7 @@
       <c r="C18" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="34" t="s">
+      <c r="D18" s="31" t="s">
         <v>636</v>
       </c>
       <c r="E18" s="17" t="s">
@@ -12753,7 +12751,7 @@
       <c r="C19" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="D19" s="31" t="s">
         <v>638</v>
       </c>
       <c r="E19" s="17" t="s">
@@ -12791,7 +12789,7 @@
       <c r="C21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="31" t="s">
         <v>380</v>
       </c>
       <c r="E21" s="17" t="s">
@@ -12809,7 +12807,7 @@
       <c r="C22" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="34" t="s">
+      <c r="D22" s="31" t="s">
         <v>381</v>
       </c>
       <c r="E22" s="17" t="s">
@@ -12827,7 +12825,7 @@
       <c r="C23" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="34" t="s">
+      <c r="D23" s="31" t="s">
         <v>642</v>
       </c>
       <c r="E23" s="17" t="s">
@@ -12845,7 +12843,7 @@
       <c r="C24" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="34" t="s">
+      <c r="D24" s="31" t="s">
         <v>644</v>
       </c>
       <c r="E24" s="17" t="s">
@@ -12863,7 +12861,7 @@
       <c r="C25" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D25" s="34" t="s">
+      <c r="D25" s="31" t="s">
         <v>384</v>
       </c>
       <c r="E25" s="17" t="s">
@@ -12881,7 +12879,7 @@
       <c r="C26" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="34" t="s">
+      <c r="D26" s="31" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="17" t="s">
@@ -12899,7 +12897,7 @@
       <c r="C27" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="34" t="s">
+      <c r="D27" s="31" t="s">
         <v>647</v>
       </c>
       <c r="E27" s="17" t="s">
@@ -12917,7 +12915,7 @@
       <c r="C28" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="34" t="s">
+      <c r="D28" s="31" t="s">
         <v>649</v>
       </c>
       <c r="E28" s="17" t="s">
@@ -12935,7 +12933,7 @@
       <c r="C29" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="34" t="s">
+      <c r="D29" s="31" t="s">
         <v>76</v>
       </c>
       <c r="E29" s="17" t="s">
@@ -12955,7 +12953,7 @@
       <c r="C30" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="34" t="s">
+      <c r="D30" s="31" t="s">
         <v>652</v>
       </c>
       <c r="E30" s="17" t="s">
@@ -12973,7 +12971,7 @@
       <c r="C31" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="34" t="s">
+      <c r="D31" s="31" t="s">
         <v>654</v>
       </c>
       <c r="E31" s="17" t="s">
@@ -12991,7 +12989,7 @@
       <c r="C32" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="34" t="s">
+      <c r="D32" s="31" t="s">
         <v>656</v>
       </c>
       <c r="E32" s="17" t="s">
@@ -13009,7 +13007,7 @@
       <c r="C33" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D33" s="34" t="s">
+      <c r="D33" s="31" t="s">
         <v>658</v>
       </c>
       <c r="E33" s="17" t="s">
@@ -13027,7 +13025,7 @@
       <c r="C34" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D34" s="34" t="s">
+      <c r="D34" s="31" t="s">
         <v>660</v>
       </c>
       <c r="E34" s="17" t="s">
@@ -13045,7 +13043,7 @@
       <c r="C35" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D35" s="34" t="s">
+      <c r="D35" s="31" t="s">
         <v>184</v>
       </c>
       <c r="E35" s="17" t="s">
@@ -13063,7 +13061,7 @@
       <c r="C36" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D36" s="34" t="s">
+      <c r="D36" s="31" t="s">
         <v>662</v>
       </c>
       <c r="E36" s="17" t="s">
@@ -13081,7 +13079,7 @@
       <c r="C37" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D37" s="34" t="s">
+      <c r="D37" s="31" t="s">
         <v>664</v>
       </c>
       <c r="E37" s="17" t="s">
@@ -13099,7 +13097,7 @@
       <c r="C38" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D38" s="34" t="s">
+      <c r="D38" s="31" t="s">
         <v>666</v>
       </c>
       <c r="E38" s="17" t="s">
@@ -13117,7 +13115,7 @@
       <c r="C39" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="34" t="s">
+      <c r="D39" s="31" t="s">
         <v>668</v>
       </c>
       <c r="E39" s="17" t="s">
@@ -13135,7 +13133,7 @@
       <c r="C40" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="34" t="s">
+      <c r="D40" s="31" t="s">
         <v>670</v>
       </c>
       <c r="E40" s="17" t="s">
@@ -13153,7 +13151,7 @@
       <c r="C41" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D41" s="34" t="s">
+      <c r="D41" s="31" t="s">
         <v>672</v>
       </c>
       <c r="E41" s="17" t="s">
@@ -13171,7 +13169,7 @@
       <c r="C42" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="34" t="s">
+      <c r="D42" s="31" t="s">
         <v>674</v>
       </c>
       <c r="E42" s="17" t="s">
@@ -13189,7 +13187,7 @@
       <c r="C43" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D43" s="34" t="s">
+      <c r="D43" s="31" t="s">
         <v>676</v>
       </c>
       <c r="E43" s="17" t="s">
@@ -13207,7 +13205,7 @@
       <c r="C44" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D44" s="34" t="s">
+      <c r="D44" s="31" t="s">
         <v>76</v>
       </c>
       <c r="E44" s="17" t="s">
@@ -13227,7 +13225,7 @@
       <c r="C45" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="34" t="s">
+      <c r="D45" s="31" t="s">
         <v>679</v>
       </c>
       <c r="E45" s="17" t="s">
@@ -13245,7 +13243,7 @@
       <c r="C46" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="34" t="s">
+      <c r="D46" s="31" t="s">
         <v>681</v>
       </c>
       <c r="E46" s="17" t="s">
@@ -13265,7 +13263,7 @@
       <c r="C47" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D47" s="34" t="s">
+      <c r="D47" s="31" t="s">
         <v>683</v>
       </c>
       <c r="E47" s="17" t="s">
@@ -13283,7 +13281,7 @@
       <c r="C48" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="34" t="s">
+      <c r="D48" s="31" t="s">
         <v>685</v>
       </c>
       <c r="E48" s="17" t="s">
@@ -13301,7 +13299,7 @@
       <c r="C49" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D49" s="34" t="s">
+      <c r="D49" s="31" t="s">
         <v>687</v>
       </c>
       <c r="E49" s="17" t="s">
@@ -13319,7 +13317,7 @@
       <c r="C50" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D50" s="34" t="s">
+      <c r="D50" s="31" t="s">
         <v>689</v>
       </c>
       <c r="E50" s="17" t="s">
@@ -13337,7 +13335,7 @@
       <c r="C51" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D51" s="34" t="s">
+      <c r="D51" s="31" t="s">
         <v>691</v>
       </c>
       <c r="E51" s="17" t="s">
@@ -13355,7 +13353,7 @@
       <c r="C52" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D52" s="34" t="s">
+      <c r="D52" s="31" t="s">
         <v>689</v>
       </c>
       <c r="E52" s="17" t="s">
@@ -13373,7 +13371,7 @@
       <c r="C53" s="17" t="s">
         <v>694</v>
       </c>
-      <c r="D53" s="34" t="s">
+      <c r="D53" s="31" t="s">
         <v>695</v>
       </c>
       <c r="E53" s="17" t="s">
@@ -13391,7 +13389,7 @@
       <c r="C54" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D54" s="34" t="s">
+      <c r="D54" s="31" t="s">
         <v>697</v>
       </c>
       <c r="E54" s="17" t="s">
@@ -13409,7 +13407,7 @@
       <c r="C55" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D55" s="34" t="s">
+      <c r="D55" s="31" t="s">
         <v>697</v>
       </c>
       <c r="E55" s="17" t="s">
@@ -13429,7 +13427,7 @@
       <c r="C56" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D56" s="34" t="s">
+      <c r="D56" s="31" t="s">
         <v>689</v>
       </c>
       <c r="E56" s="17" t="s">
@@ -13447,7 +13445,7 @@
       <c r="C57" s="17" t="s">
         <v>694</v>
       </c>
-      <c r="D57" s="34" t="s">
+      <c r="D57" s="31" t="s">
         <v>701</v>
       </c>
       <c r="E57" s="17" t="s">
@@ -13465,7 +13463,7 @@
       <c r="C58" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D58" s="34" t="s">
+      <c r="D58" s="31" t="s">
         <v>14</v>
       </c>
       <c r="E58" s="17" t="s">
@@ -13485,7 +13483,7 @@
       <c r="C59" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D59" s="34" t="s">
+      <c r="D59" s="31" t="s">
         <v>705</v>
       </c>
       <c r="E59" s="17" t="s">
@@ -13503,7 +13501,7 @@
       <c r="C60" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D60" s="34" t="s">
+      <c r="D60" s="31" t="s">
         <v>707</v>
       </c>
       <c r="E60" s="17" t="s">
@@ -13575,7 +13573,7 @@
       <c r="C64" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D64" s="34" t="s">
+      <c r="D64" s="31" t="s">
         <v>715</v>
       </c>
       <c r="E64" s="17" t="s">
@@ -13601,7 +13599,7 @@
     <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="9" width="27.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="33" width="23.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="23.433571428571426" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -13620,7 +13618,7 @@
       <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
     </row>
@@ -13640,7 +13638,7 @@
       <c r="E2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="32"/>
+      <c r="F2" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
@@ -13658,7 +13656,7 @@
       <c r="E3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="32"/>
+      <c r="F3" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
@@ -13676,7 +13674,7 @@
       <c r="E4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="32"/>
+      <c r="F4" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
@@ -13694,7 +13692,7 @@
       <c r="E5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="32"/>
+      <c r="F5" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
@@ -13712,7 +13710,7 @@
       <c r="E6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="32"/>
+      <c r="F6" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
@@ -13730,7 +13728,7 @@
       <c r="E7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="32"/>
+      <c r="F7" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
@@ -13788,7 +13786,7 @@
       <c r="E10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="32"/>
+      <c r="F10" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
@@ -13846,7 +13844,7 @@
       <c r="E13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="32"/>
+      <c r="F13" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6" t="s">
@@ -13904,7 +13902,7 @@
       <c r="E16" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="F16" s="32"/>
+      <c r="F16" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6" t="s">
@@ -13922,7 +13920,7 @@
       <c r="E17" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="F17" s="32"/>
+      <c r="F17" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6" t="s">
@@ -13940,7 +13938,7 @@
       <c r="E18" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="F18" s="32"/>
+      <c r="F18" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6" t="s">
@@ -13958,7 +13956,7 @@
       <c r="E19" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="32"/>
+      <c r="F19" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6" t="s">
@@ -13976,7 +13974,7 @@
       <c r="E20" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="F20" s="32"/>
+      <c r="F20" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="6" t="s">
@@ -14074,7 +14072,7 @@
       <c r="E25" s="6" t="s">
         <v>614</v>
       </c>
-      <c r="F25" s="32"/>
+      <c r="F25" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="6" t="s">
@@ -14112,7 +14110,7 @@
       <c r="E27" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="32"/>
+      <c r="F27" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/global/utils/file-utils/locators(2).xlsx
+++ b/src/global/utils/file-utils/locators(2).xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="HomePage"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2868" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2873" uniqueCount="828">
   <si>
     <t>page</t>
   </si>
@@ -1342,9 +1342,6 @@
     <t>winBoostToolTipZM</t>
   </si>
   <si>
-    <t>Win Boost 2%. 1 more for 3% (Min odds 1.2)</t>
-  </si>
-  <si>
     <t>winBoostToolTip</t>
   </si>
   <si>
@@ -1378,7 +1375,7 @@
     <t>winBoostValueZM</t>
   </si>
   <si>
-    <t>Win Boost (2%): K</t>
+    <t>Win Boost (3%): K</t>
   </si>
   <si>
     <t>winBoostValue</t>
@@ -1979,6 +1976,9 @@
   </si>
   <si>
     <t>bettingRules</t>
+  </si>
+  <si>
+    <t>bettingRulesZM</t>
   </si>
   <si>
     <t>bettingRulesMZ</t>
@@ -4298,7 +4298,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B2" s="31" t="s">
         <v>164</v>
@@ -4310,7 +4310,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F2" s="33">
         <v>0</v>
@@ -4318,7 +4318,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>165</v>
@@ -4338,10 +4338,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C4" s="31" t="s">
         <v>8</v>
@@ -4350,7 +4350,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F4" s="33">
         <v>0</v>
@@ -4358,10 +4358,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C5" s="31" t="s">
         <v>8</v>
@@ -4370,7 +4370,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F5" s="33">
         <v>0</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C6" s="31" t="s">
         <v>8</v>
@@ -4390,7 +4390,7 @@
         <v>9</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F6" s="7">
         <v>0</v>
@@ -4398,7 +4398,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>13</v>
@@ -4418,7 +4418,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>172</v>
@@ -4438,10 +4438,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>8</v>
@@ -4450,7 +4450,7 @@
         <v>14</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F9" s="33">
         <v>0</v>
@@ -4458,10 +4458,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C10" s="31" t="s">
         <v>8</v>
@@ -4470,7 +4470,7 @@
         <v>14</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F10" s="33">
         <v>0</v>
@@ -4478,10 +4478,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C11" s="31" t="s">
         <v>8</v>
@@ -4490,7 +4490,7 @@
         <v>14</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F11" s="33">
         <v>0</v>
@@ -4498,7 +4498,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>105</v>
@@ -4518,10 +4518,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>8</v>
@@ -4538,10 +4538,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C14" s="31" t="s">
         <v>8</v>
@@ -4550,7 +4550,7 @@
         <v>355</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F14" s="33">
         <v>0</v>
@@ -4558,19 +4558,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B15" s="31" t="s">
+        <v>492</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="32" t="s">
         <v>493</v>
       </c>
-      <c r="C15" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>494</v>
-      </c>
       <c r="E15" s="31" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F15" s="33">
         <v>0</v>
@@ -4578,16 +4578,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C16" s="31" t="s">
         <v>68</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E16" s="31" t="s">
         <v>23</v>
@@ -4598,10 +4598,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>8</v>
@@ -4610,7 +4610,7 @@
         <v>9</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F17" s="35">
         <v>0</v>
@@ -4618,10 +4618,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>8</v>
@@ -4630,7 +4630,7 @@
         <v>9</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F18" s="33">
         <v>0</v>
@@ -4638,10 +4638,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C19" s="31" t="s">
         <v>8</v>
@@ -4650,7 +4650,7 @@
         <v>355</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F19" s="33">
         <v>0</v>
@@ -4658,16 +4658,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C20" s="31" t="s">
         <v>68</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E20" s="31" t="s">
         <v>23</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C21" s="31" t="s">
         <v>8</v>
@@ -4690,7 +4690,7 @@
         <v>9</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F21" s="33">
         <v>0</v>
@@ -4698,10 +4698,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C22" s="31" t="s">
         <v>8</v>
@@ -4710,7 +4710,7 @@
         <v>9</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F22" s="33">
         <v>0</v>
@@ -4718,19 +4718,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C23" s="31" t="s">
         <v>144</v>
       </c>
       <c r="D23" s="32" t="s">
+        <v>508</v>
+      </c>
+      <c r="E23" s="31" t="s">
         <v>509</v>
-      </c>
-      <c r="E23" s="31" t="s">
-        <v>510</v>
       </c>
       <c r="F23" s="33">
         <v>0</v>
@@ -4738,10 +4738,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C24" s="31" t="s">
         <v>68</v>
@@ -4758,16 +4758,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B25" s="31" t="s">
+        <v>511</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>512</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>513</v>
       </c>
       <c r="E25" s="31" t="s">
         <v>23</v>
@@ -4778,10 +4778,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C26" s="31" t="s">
         <v>8</v>
@@ -4790,7 +4790,7 @@
         <v>9</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F26" s="33">
         <v>0</v>
@@ -4798,10 +4798,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C27" s="31" t="s">
         <v>8</v>
@@ -4810,7 +4810,7 @@
         <v>9</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F27" s="33">
         <v>0</v>
@@ -4947,13 +4947,13 @@
         <v>379</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C35" s="31" t="s">
         <v>68</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E35" s="31" t="s">
         <v>23</v>
@@ -4965,13 +4965,13 @@
         <v>379</v>
       </c>
       <c r="B36" s="31" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C36" s="31" t="s">
         <v>68</v>
       </c>
       <c r="D36" s="32" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E36" s="31" t="s">
         <v>23</v>
@@ -4983,16 +4983,16 @@
         <v>379</v>
       </c>
       <c r="B37" s="31" t="s">
+        <v>519</v>
+      </c>
+      <c r="C37" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="32" t="s">
         <v>520</v>
       </c>
-      <c r="C37" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" s="32" t="s">
+      <c r="E37" s="31" t="s">
         <v>521</v>
-      </c>
-      <c r="E37" s="31" t="s">
-        <v>522</v>
       </c>
       <c r="F37" s="35">
         <v>1</v>
@@ -5003,7 +5003,7 @@
         <v>379</v>
       </c>
       <c r="B38" s="31" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C38" s="31" t="s">
         <v>68</v>
@@ -5021,13 +5021,13 @@
         <v>379</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C39" s="31" t="s">
         <v>68</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E39" s="31" t="s">
         <v>23</v>
@@ -5041,13 +5041,13 @@
         <v>379</v>
       </c>
       <c r="B40" s="31" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C40" s="31" t="s">
         <v>68</v>
       </c>
       <c r="D40" s="32" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E40" s="31" t="s">
         <v>23</v>
@@ -5061,13 +5061,13 @@
         <v>379</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C41" s="31" t="s">
         <v>68</v>
       </c>
       <c r="D41" s="32" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E41" s="31" t="s">
         <v>23</v>
@@ -5079,13 +5079,13 @@
         <v>379</v>
       </c>
       <c r="B42" s="31" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C42" s="31" t="s">
         <v>68</v>
       </c>
       <c r="D42" s="32" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E42" s="31" t="s">
         <v>23</v>
@@ -5808,7 +5808,7 @@
         <v>68</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>23</v>
@@ -5820,13 +5820,13 @@
         <v>379</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C40" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E40" s="17" t="s">
         <v>23</v>
@@ -5838,13 +5838,13 @@
         <v>379</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>23</v>
@@ -5856,13 +5856,13 @@
         <v>379</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>23</v>
@@ -5874,13 +5874,13 @@
         <v>379</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>23</v>
@@ -5892,13 +5892,13 @@
         <v>379</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>23</v>
@@ -5910,13 +5910,13 @@
         <v>379</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>23</v>
@@ -5928,13 +5928,13 @@
         <v>379</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>23</v>
@@ -5946,7 +5946,7 @@
         <v>379</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>68</v>
@@ -5964,13 +5964,13 @@
         <v>379</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>23</v>
@@ -5984,13 +5984,13 @@
         <v>379</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>23</v>
@@ -6004,13 +6004,13 @@
         <v>379</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C50" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>23</v>
@@ -6022,13 +6022,13 @@
         <v>379</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>23</v>
@@ -6040,13 +6040,13 @@
         <v>379</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>23</v>
@@ -6058,13 +6058,13 @@
         <v>379</v>
       </c>
       <c r="B53" s="17" t="s">
+        <v>460</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="17" t="s">
         <v>461</v>
-      </c>
-      <c r="C53" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D53" s="17" t="s">
-        <v>462</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>23</v>
@@ -6078,13 +6078,13 @@
         <v>379</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E54" s="17" t="s">
         <v>23</v>
@@ -6098,13 +6098,13 @@
         <v>379</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>23</v>
@@ -6118,7 +6118,7 @@
         <v>379</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C56" s="17" t="s">
         <v>21</v>
@@ -6136,13 +6136,13 @@
         <v>379</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C57" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>23</v>
@@ -6154,13 +6154,13 @@
         <v>379</v>
       </c>
       <c r="B58" s="27" t="s">
+        <v>467</v>
+      </c>
+      <c r="C58" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="27" t="s">
         <v>468</v>
-      </c>
-      <c r="C58" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D58" s="27" t="s">
-        <v>469</v>
       </c>
       <c r="E58" s="27" t="s">
         <v>23</v>
@@ -6172,13 +6172,13 @@
         <v>379</v>
       </c>
       <c r="B59" s="27" t="s">
+        <v>469</v>
+      </c>
+      <c r="C59" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" s="27" t="s">
         <v>470</v>
-      </c>
-      <c r="C59" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D59" s="27" t="s">
-        <v>471</v>
       </c>
       <c r="E59" s="27" t="s">
         <v>23</v>
@@ -6190,13 +6190,13 @@
         <v>379</v>
       </c>
       <c r="B60" s="27" t="s">
+        <v>471</v>
+      </c>
+      <c r="C60" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" s="27" t="s">
         <v>472</v>
-      </c>
-      <c r="C60" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D60" s="27" t="s">
-        <v>473</v>
       </c>
       <c r="E60" s="27" t="s">
         <v>23</v>
@@ -6208,13 +6208,13 @@
         <v>379</v>
       </c>
       <c r="B61" s="27" t="s">
+        <v>473</v>
+      </c>
+      <c r="C61" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" s="27" t="s">
         <v>474</v>
-      </c>
-      <c r="C61" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D61" s="27" t="s">
-        <v>475</v>
       </c>
       <c r="E61" s="27" t="s">
         <v>23</v>
@@ -12539,7 +12539,7 @@
         <v>735</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C11" s="42" t="s">
         <v>21</v>
@@ -12548,7 +12548,7 @@
         <v>754</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F11" s="43">
         <v>0</v>
@@ -12559,7 +12559,7 @@
         <v>735</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C12" s="42" t="s">
         <v>21</v>
@@ -12568,7 +12568,7 @@
         <v>754</v>
       </c>
       <c r="E12" s="42" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F12" s="43">
         <v>0</v>
@@ -12622,7 +12622,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="4" width="12.290714285714287" customWidth="1" bestFit="1"/>
@@ -12655,10 +12655,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="17" t="s">
+        <v>635</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>636</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>637</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>30</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F2" s="18">
         <v>0</v>
@@ -12675,7 +12675,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>7</v>
@@ -12693,7 +12693,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>271</v>
@@ -12711,7 +12711,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>273</v>
@@ -12731,7 +12731,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>105</v>
@@ -12749,7 +12749,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>13</v>
@@ -12767,7 +12767,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>170</v>
@@ -12787,10 +12787,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>8</v>
@@ -12807,7 +12807,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>172</v>
@@ -12825,7 +12825,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>174</v>
@@ -12845,16 +12845,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>25</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>23</v>
@@ -12863,16 +12863,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>23</v>
@@ -12881,16 +12881,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>23</v>
@@ -12901,16 +12901,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>23</v>
@@ -12919,16 +12919,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>23</v>
@@ -12937,16 +12937,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>23</v>
@@ -12955,16 +12955,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>23</v>
@@ -12973,92 +12973,92 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="18">
-        <v>0</v>
-      </c>
+      <c r="F19" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="16"/>
+      <c r="F20" s="18">
+        <v>0</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="18">
-        <v>27</v>
+      <c r="D21" s="37" t="s">
+        <v>655</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="16">
-        <v>0</v>
-      </c>
+      <c r="F21" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>381</v>
+        <v>68</v>
+      </c>
+      <c r="D22" s="18">
+        <v>27</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="16"/>
+      <c r="F22" s="16">
+        <v>0</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>165</v>
+        <v>657</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>23</v>
@@ -13067,16 +13067,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>658</v>
+        <v>165</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>659</v>
+        <v>382</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>23</v>
@@ -13085,16 +13085,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D25" s="37" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>23</v>
@@ -13103,16 +13103,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>384</v>
+        <v>660</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>385</v>
+        <v>661</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>23</v>
@@ -13121,52 +13121,52 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>662</v>
+        <v>384</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>14</v>
+        <v>385</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F27" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>664</v>
+        <v>14</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="F28" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D29" s="37" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>23</v>
@@ -13175,54 +13175,54 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>77</v>
+        <v>666</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F30" s="18">
-        <v>1</v>
-      </c>
+      <c r="F30" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>669</v>
+        <v>77</v>
       </c>
       <c r="E31" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F31" s="16"/>
+      <c r="F31" s="18">
+        <v>1</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>23</v>
@@ -13231,16 +13231,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E33" s="17" t="s">
         <v>23</v>
@@ -13249,16 +13249,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>23</v>
@@ -13267,16 +13267,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D35" s="37" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>23</v>
@@ -13285,16 +13285,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>184</v>
+        <v>676</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D36" s="37" t="s">
-        <v>185</v>
+        <v>677</v>
       </c>
       <c r="E36" s="17" t="s">
         <v>23</v>
@@ -13303,16 +13303,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>678</v>
+        <v>184</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D37" s="37" t="s">
-        <v>679</v>
+        <v>185</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>23</v>
@@ -13321,16 +13321,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>23</v>
@@ -13339,16 +13339,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>23</v>
@@ -13357,16 +13357,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E40" s="17" t="s">
         <v>23</v>
@@ -13375,16 +13375,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D41" s="37" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>23</v>
@@ -13393,16 +13393,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>23</v>
@@ -13411,16 +13411,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>23</v>
@@ -13429,16 +13429,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D44" s="37" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>23</v>
@@ -13447,74 +13447,72 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D45" s="37" t="s">
-        <v>77</v>
+        <v>693</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F45" s="18">
-        <v>1</v>
-      </c>
+      <c r="F45" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>696</v>
+        <v>77</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F46" s="16"/>
+      <c r="F46" s="18">
+        <v>1</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D47" s="37" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F47" s="18">
-        <v>0</v>
-      </c>
+      <c r="F47" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D48" s="37" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>23</v>
@@ -13525,70 +13523,72 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B49" s="17" t="s">
+        <v>699</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" s="37" t="s">
+        <v>700</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F49" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+      <c r="A50" s="17" t="s">
+        <v>635</v>
+      </c>
+      <c r="B50" s="17" t="s">
         <v>701</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C50" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D49" s="37" t="s">
+      <c r="D50" s="37" t="s">
         <v>702</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E50" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="F49" s="16"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
-      <c r="A50" s="17" t="s">
-        <v>636</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>703</v>
-      </c>
-      <c r="C50" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D50" s="37" t="s">
-        <v>704</v>
-      </c>
-      <c r="E50" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F50" s="37"/>
+      <c r="F50" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
       <c r="A51" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D51" s="37" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F51" s="16"/>
+      <c r="F51" s="37"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
       <c r="A52" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D52" s="37" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>23</v>
@@ -13597,16 +13597,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
       <c r="A53" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D53" s="37" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>23</v>
@@ -13615,16 +13615,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5">
       <c r="A54" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D54" s="37" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E54" s="17" t="s">
         <v>23</v>
@@ -13633,16 +13633,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="19.5">
       <c r="A55" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>713</v>
+        <v>68</v>
       </c>
       <c r="D55" s="37" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>23</v>
@@ -13651,16 +13651,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="19.5">
       <c r="A56" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>68</v>
+        <v>713</v>
       </c>
       <c r="D56" s="37" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="E56" s="17" t="s">
         <v>23</v>
@@ -13669,10 +13669,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
       <c r="A57" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C57" s="17" t="s">
         <v>68</v>
@@ -13683,40 +13683,40 @@
       <c r="E57" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F57" s="18">
-        <v>1</v>
-      </c>
+      <c r="F57" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="19.5">
       <c r="A58" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D58" s="37" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="E58" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F58" s="16"/>
+      <c r="F58" s="18">
+        <v>1</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
       <c r="A59" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>713</v>
+        <v>68</v>
       </c>
       <c r="D59" s="37" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>23</v>
@@ -13725,90 +13725,90 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
       <c r="A60" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>8</v>
+        <v>713</v>
       </c>
       <c r="D60" s="37" t="s">
-        <v>14</v>
+        <v>720</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>722</v>
-      </c>
-      <c r="F60" s="18">
-        <v>1</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F60" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
       <c r="A61" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B61" s="17" t="s">
+        <v>721</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="17" t="s">
+        <v>722</v>
+      </c>
+      <c r="F61" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="19.5">
+      <c r="A62" s="17" t="s">
+        <v>635</v>
+      </c>
+      <c r="B62" s="17" t="s">
         <v>723</v>
       </c>
-      <c r="C61" s="17" t="s">
+      <c r="C62" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D61" s="37" t="s">
+      <c r="D62" s="37" t="s">
         <v>724</v>
       </c>
-      <c r="E61" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F61" s="16"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
-      <c r="A62" s="17" t="s">
-        <v>636</v>
-      </c>
-      <c r="B62" s="17" t="s">
+      <c r="E62" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F62" s="16"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
+      <c r="A63" s="17" t="s">
+        <v>635</v>
+      </c>
+      <c r="B63" s="17" t="s">
         <v>725</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C63" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D62" s="37" t="s">
+      <c r="D63" s="37" t="s">
         <v>726</v>
       </c>
-      <c r="E62" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F62" s="16"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
-      <c r="A63" s="34" t="s">
-        <v>636</v>
-      </c>
-      <c r="B63" s="34" t="s">
-        <v>727</v>
-      </c>
-      <c r="C63" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>728</v>
-      </c>
-      <c r="E63" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="F63" s="7"/>
+      <c r="E63" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="34" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B64" s="34" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C64" s="34" t="s">
         <v>25</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E64" s="34" t="s">
         <v>23</v>
@@ -13817,39 +13817,57 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="34" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B65" s="34" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C65" s="34" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="E65" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F65" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+      <c r="A66" s="34" t="s">
+        <v>635</v>
+      </c>
+      <c r="B66" s="34" t="s">
+        <v>731</v>
+      </c>
+      <c r="C66" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="D66" s="7" t="s">
         <v>732</v>
       </c>
-      <c r="E65" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="F65" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
-      <c r="A66" s="17" t="s">
-        <v>636</v>
-      </c>
-      <c r="B66" s="17" t="s">
+      <c r="E66" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5">
+      <c r="A67" s="17" t="s">
+        <v>635</v>
+      </c>
+      <c r="B67" s="17" t="s">
         <v>733</v>
       </c>
-      <c r="C66" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D66" s="37" t="s">
+      <c r="C67" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" s="37" t="s">
         <v>734</v>
       </c>
-      <c r="E66" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F66" s="16"/>
+      <c r="E67" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F67" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13894,16 +13912,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>592</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>593</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>594</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>23</v>
@@ -13912,16 +13930,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>595</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>596</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>23</v>
@@ -13930,16 +13948,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>597</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>598</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>23</v>
@@ -13948,16 +13966,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>599</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>600</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>23</v>
@@ -13966,16 +13984,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>601</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>602</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>23</v>
@@ -13984,16 +14002,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>23</v>
@@ -14002,16 +14020,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>23</v>
@@ -14022,19 +14040,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D9" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>608</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>609</v>
       </c>
       <c r="F9" s="8">
         <v>0</v>
@@ -14042,16 +14060,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>23</v>
@@ -14060,16 +14078,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>612</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>613</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>23</v>
@@ -14080,19 +14098,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F12" s="8">
         <v>0</v>
@@ -14100,16 +14118,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>23</v>
@@ -14118,7 +14136,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>320</v>
@@ -14127,10 +14145,10 @@
         <v>68</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F14" s="8">
         <v>0</v>
@@ -14138,10 +14156,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>8</v>
@@ -14150,7 +14168,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
@@ -14158,10 +14176,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>68</v>
@@ -14170,34 +14188,34 @@
         <v>197</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F16" s="26"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>622</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="6" t="s">
+      <c r="E17" s="6" t="s">
         <v>623</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>624</v>
       </c>
       <c r="F17" s="26"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>68</v>
@@ -14206,22 +14224,22 @@
         <v>282</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F18" s="26"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>23</v>
@@ -14230,10 +14248,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>68</v>
@@ -14242,13 +14260,13 @@
         <v>213</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F20" s="26"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>7</v>
@@ -14268,7 +14286,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>11</v>
@@ -14288,7 +14306,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>13</v>
@@ -14308,7 +14326,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>76</v>
@@ -14328,37 +14346,37 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>629</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>623</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>630</v>
       </c>
       <c r="F25" s="26"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D26" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>632</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>633</v>
       </c>
       <c r="F26" s="8">
         <v>1</v>
@@ -14366,16 +14384,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>23</v>
@@ -14425,16 +14443,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>524</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>525</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>23</v>
@@ -14445,16 +14463,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>144</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>23</v>
@@ -14463,16 +14481,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>528</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>529</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>23</v>
@@ -14483,19 +14501,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>531</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>532</v>
       </c>
       <c r="F5" s="8">
         <v>1</v>
@@ -14503,19 +14521,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>144</v>
       </c>
       <c r="D6" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>534</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>535</v>
       </c>
       <c r="F6" s="8">
         <v>1</v>
@@ -14523,10 +14541,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>8</v>
@@ -14535,7 +14553,7 @@
         <v>14</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F7" s="8">
         <v>0</v>
@@ -14543,16 +14561,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>538</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>539</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>23</v>
@@ -14561,10 +14579,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>8</v>
@@ -14573,7 +14591,7 @@
         <v>9</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F9" s="8">
         <v>0</v>
@@ -14581,10 +14599,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>8</v>
@@ -14593,7 +14611,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F10" s="8">
         <v>0</v>
@@ -14601,10 +14619,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>8</v>
@@ -14613,7 +14631,7 @@
         <v>14</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
@@ -14621,16 +14639,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>546</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>547</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>23</v>
@@ -14641,16 +14659,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>548</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>549</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>23</v>
@@ -14661,10 +14679,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>8</v>
@@ -14673,7 +14691,7 @@
         <v>14</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F14" s="8">
         <v>10</v>
@@ -14681,10 +14699,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>8</v>
@@ -14693,7 +14711,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
@@ -14701,16 +14719,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>23</v>
@@ -14721,10 +14739,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>8</v>
@@ -14733,7 +14751,7 @@
         <v>9</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F17" s="8">
         <v>0</v>
@@ -14741,16 +14759,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>144</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>23</v>
@@ -14761,10 +14779,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>8</v>
@@ -14773,7 +14791,7 @@
         <v>14</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F19" s="8">
         <v>0</v>
@@ -14781,19 +14799,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F20" s="8">
         <v>0</v>
@@ -14801,16 +14819,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>563</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>564</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>23</v>
@@ -14821,10 +14839,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>8</v>
@@ -14833,7 +14851,7 @@
         <v>14</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F22" s="8">
         <v>0</v>
@@ -14841,19 +14859,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F23" s="8">
         <v>0</v>
@@ -14861,10 +14879,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>8</v>
@@ -14873,7 +14891,7 @@
         <v>14</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F24" s="8">
         <v>10</v>
@@ -14881,7 +14899,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>32</v>
@@ -14893,7 +14911,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F25" s="8">
         <v>0</v>
@@ -14901,19 +14919,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F26" s="8">
         <v>0</v>
@@ -14921,7 +14939,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>61</v>
@@ -14930,7 +14948,7 @@
         <v>21</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>23</v>
@@ -14941,10 +14959,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>21</v>
@@ -14961,7 +14979,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>76</v>
@@ -14981,16 +14999,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B30" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>575</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>576</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>23</v>
@@ -15001,10 +15019,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>8</v>
@@ -15013,7 +15031,7 @@
         <v>14</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="F31" s="8">
         <v>0</v>
@@ -15021,16 +15039,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B32" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>579</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>580</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>23</v>
@@ -15041,10 +15059,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>8</v>
@@ -15053,7 +15071,7 @@
         <v>9</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F33" s="8">
         <v>0</v>
@@ -15061,19 +15079,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>144</v>
       </c>
       <c r="D34" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>534</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>535</v>
       </c>
       <c r="F34" s="8">
         <v>0</v>
@@ -15081,10 +15099,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>8</v>
@@ -15093,7 +15111,7 @@
         <v>14</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F35" s="8">
         <v>0</v>
@@ -15101,10 +15119,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>8</v>
@@ -15113,7 +15131,7 @@
         <v>9</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="F36" s="8">
         <v>0</v>
@@ -15121,16 +15139,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B37" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>588</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>589</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>23</v>
@@ -15141,16 +15159,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B38" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="6" t="s">
         <v>590</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>591</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>23</v>
@@ -15161,7 +15179,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>7</v>
@@ -15181,7 +15199,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>11</v>
@@ -15201,7 +15219,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>13</v>

--- a/src/global/utils/file-utils/locators(2).xlsx
+++ b/src/global/utils/file-utils/locators(2).xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="HomePage"/>
@@ -2696,7 +2696,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="47">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2770,13 +2770,13 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -2797,14 +2797,8 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3171,7 +3165,7 @@
       <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="46" t="s">
+      <c r="F1" s="44" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3188,7 +3182,7 @@
       <c r="D2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="27" t="s">
         <v>793</v>
       </c>
       <c r="F2" s="8">
@@ -3208,7 +3202,7 @@
       <c r="D3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="27" t="s">
         <v>795</v>
       </c>
       <c r="F3" s="8"/>
@@ -3226,7 +3220,7 @@
       <c r="D4" s="6" t="s">
         <v>797</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F4" s="8"/>
@@ -3244,7 +3238,7 @@
       <c r="D5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="27" t="s">
         <v>799</v>
       </c>
       <c r="F5" s="8"/>
@@ -3262,7 +3256,7 @@
       <c r="D6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="27" t="s">
         <v>801</v>
       </c>
       <c r="F6" s="8"/>
@@ -3280,7 +3274,7 @@
       <c r="D7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="27" t="s">
         <v>803</v>
       </c>
       <c r="F7" s="8"/>
@@ -3298,7 +3292,7 @@
       <c r="D8" s="6" t="s">
         <v>805</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="8"/>
@@ -3316,7 +3310,7 @@
       <c r="D9" s="6" t="s">
         <v>807</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F9" s="8"/>
@@ -3334,7 +3328,7 @@
       <c r="D10" s="6" t="s">
         <v>809</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="E10" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F10" s="8"/>
@@ -3352,7 +3346,7 @@
       <c r="D11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="34" t="s">
+      <c r="E11" s="27" t="s">
         <v>811</v>
       </c>
       <c r="F11" s="8"/>
@@ -3370,7 +3364,7 @@
       <c r="D12" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F12" s="8"/>
@@ -3388,7 +3382,7 @@
       <c r="D13" s="6" t="s">
         <v>814</v>
       </c>
-      <c r="E13" s="34" t="s">
+      <c r="E13" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F13" s="8"/>
@@ -3406,7 +3400,7 @@
       <c r="D14" s="6" t="s">
         <v>816</v>
       </c>
-      <c r="E14" s="34" t="s">
+      <c r="E14" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F14" s="8"/>
@@ -3424,7 +3418,7 @@
       <c r="D15" s="6" t="s">
         <v>818</v>
       </c>
-      <c r="E15" s="34" t="s">
+      <c r="E15" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="8"/>
@@ -3442,7 +3436,7 @@
       <c r="D16" s="6" t="s">
         <v>820</v>
       </c>
-      <c r="E16" s="34" t="s">
+      <c r="E16" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F16" s="8"/>
@@ -3460,7 +3454,7 @@
       <c r="D17" s="6" t="s">
         <v>822</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F17" s="8"/>
@@ -3478,7 +3472,7 @@
       <c r="D18" s="6" t="s">
         <v>824</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="8"/>
@@ -3493,10 +3487,10 @@
       <c r="C19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="48" t="s">
+      <c r="D19" s="46" t="s">
         <v>826</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F19" s="8"/>
@@ -3514,7 +3508,7 @@
       <c r="D20" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="34" t="s">
+      <c r="E20" s="27" t="s">
         <v>793</v>
       </c>
       <c r="F20" s="8"/>
@@ -3524,7 +3518,7 @@
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
-      <c r="E21" s="34"/>
+      <c r="E21" s="27"/>
       <c r="F21" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
@@ -3532,7 +3526,7 @@
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
-      <c r="E22" s="34"/>
+      <c r="E22" s="27"/>
       <c r="F22" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
@@ -3540,7 +3534,7 @@
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
-      <c r="E23" s="34"/>
+      <c r="E23" s="27"/>
       <c r="F23" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
@@ -3548,7 +3542,7 @@
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="34"/>
+      <c r="E24" s="27"/>
       <c r="F24" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
@@ -3556,7 +3550,7 @@
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
-      <c r="E25" s="34"/>
+      <c r="E25" s="27"/>
       <c r="F25" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
@@ -3564,7 +3558,7 @@
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
-      <c r="E26" s="34"/>
+      <c r="E26" s="27"/>
       <c r="F26" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
@@ -3572,7 +3566,7 @@
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
-      <c r="E27" s="34"/>
+      <c r="E27" s="27"/>
       <c r="F27" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
@@ -3580,7 +3574,7 @@
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
-      <c r="E28" s="34"/>
+      <c r="E28" s="27"/>
       <c r="F28" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
@@ -3588,7 +3582,7 @@
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
-      <c r="E29" s="34"/>
+      <c r="E29" s="27"/>
       <c r="F29" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
@@ -3596,7 +3590,7 @@
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
-      <c r="E30" s="34"/>
+      <c r="E30" s="27"/>
       <c r="F30" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
@@ -3604,7 +3598,7 @@
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
-      <c r="E31" s="34"/>
+      <c r="E31" s="27"/>
       <c r="F31" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
@@ -3612,7 +3606,7 @@
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
-      <c r="E32" s="34"/>
+      <c r="E32" s="27"/>
       <c r="F32" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
@@ -3620,7 +3614,7 @@
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
-      <c r="E33" s="34"/>
+      <c r="E33" s="27"/>
       <c r="F33" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
@@ -3628,7 +3622,7 @@
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
-      <c r="E34" s="34"/>
+      <c r="E34" s="27"/>
       <c r="F34" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
@@ -3636,7 +3630,7 @@
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
-      <c r="E35" s="34"/>
+      <c r="E35" s="27"/>
       <c r="F35" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
@@ -3644,7 +3638,7 @@
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
-      <c r="E36" s="34"/>
+      <c r="E36" s="27"/>
       <c r="F36" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
@@ -3652,7 +3646,7 @@
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
-      <c r="E37" s="34"/>
+      <c r="E37" s="27"/>
       <c r="F37" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
@@ -3660,7 +3654,7 @@
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
-      <c r="E38" s="34"/>
+      <c r="E38" s="27"/>
       <c r="F38" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
@@ -3668,7 +3662,7 @@
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
-      <c r="E39" s="34"/>
+      <c r="E39" s="27"/>
       <c r="F39" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
@@ -3676,7 +3670,7 @@
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
-      <c r="E40" s="34"/>
+      <c r="E40" s="27"/>
       <c r="F40" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
@@ -3684,7 +3678,7 @@
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
-      <c r="E41" s="34"/>
+      <c r="E41" s="27"/>
       <c r="F41" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
@@ -3692,7 +3686,7 @@
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
-      <c r="E42" s="34"/>
+      <c r="E42" s="27"/>
       <c r="F42" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
@@ -3700,7 +3694,7 @@
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
-      <c r="E43" s="34"/>
+      <c r="E43" s="27"/>
       <c r="F43" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
@@ -3708,7 +3702,7 @@
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
-      <c r="E44" s="34"/>
+      <c r="E44" s="27"/>
       <c r="F44" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
@@ -3716,7 +3710,7 @@
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
-      <c r="E45" s="34"/>
+      <c r="E45" s="27"/>
       <c r="F45" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
@@ -3724,7 +3718,7 @@
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
-      <c r="E46" s="34"/>
+      <c r="E46" s="27"/>
       <c r="F46" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
@@ -3732,7 +3726,7 @@
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
-      <c r="E47" s="34"/>
+      <c r="E47" s="27"/>
       <c r="F47" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
@@ -3740,7 +3734,7 @@
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
-      <c r="E48" s="34"/>
+      <c r="E48" s="27"/>
       <c r="F48" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
@@ -3748,7 +3742,7 @@
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
-      <c r="E49" s="34"/>
+      <c r="E49" s="27"/>
       <c r="F49" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
@@ -3876,7 +3870,7 @@
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
-      <c r="E65" s="34"/>
+      <c r="E65" s="27"/>
       <c r="F65" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
@@ -4036,7 +4030,7 @@
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
       <c r="D85" s="6"/>
-      <c r="E85" s="34"/>
+      <c r="E85" s="27"/>
       <c r="F85" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
@@ -4044,7 +4038,7 @@
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
       <c r="D86" s="6"/>
-      <c r="E86" s="34"/>
+      <c r="E86" s="27"/>
       <c r="F86" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
@@ -4052,7 +4046,7 @@
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
       <c r="D87" s="6"/>
-      <c r="E87" s="34"/>
+      <c r="E87" s="27"/>
       <c r="F87" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
@@ -4060,7 +4054,7 @@
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
       <c r="D88" s="6"/>
-      <c r="E88" s="34"/>
+      <c r="E88" s="27"/>
       <c r="F88" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
@@ -4068,7 +4062,7 @@
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
       <c r="D89" s="6"/>
-      <c r="E89" s="34"/>
+      <c r="E89" s="27"/>
       <c r="F89" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
@@ -4076,7 +4070,7 @@
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
       <c r="D90" s="6"/>
-      <c r="E90" s="34"/>
+      <c r="E90" s="27"/>
       <c r="F90" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
@@ -4084,7 +4078,7 @@
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
       <c r="D91" s="6"/>
-      <c r="E91" s="34"/>
+      <c r="E91" s="27"/>
       <c r="F91" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
@@ -4092,7 +4086,7 @@
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
       <c r="D92" s="6"/>
-      <c r="E92" s="34"/>
+      <c r="E92" s="27"/>
       <c r="F92" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
@@ -4100,7 +4094,7 @@
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
       <c r="D93" s="6"/>
-      <c r="E93" s="34"/>
+      <c r="E93" s="27"/>
       <c r="F93" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
@@ -4108,7 +4102,7 @@
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
-      <c r="E94" s="34"/>
+      <c r="E94" s="27"/>
       <c r="F94" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
@@ -4116,7 +4110,7 @@
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
       <c r="D95" s="6"/>
-      <c r="E95" s="34"/>
+      <c r="E95" s="27"/>
       <c r="F95" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
@@ -4124,7 +4118,7 @@
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
       <c r="D96" s="6"/>
-      <c r="E96" s="34"/>
+      <c r="E96" s="27"/>
       <c r="F96" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
@@ -4132,7 +4126,7 @@
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
       <c r="D97" s="6"/>
-      <c r="E97" s="34"/>
+      <c r="E97" s="27"/>
       <c r="F97" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
@@ -4140,7 +4134,7 @@
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
       <c r="D98" s="6"/>
-      <c r="E98" s="34"/>
+      <c r="E98" s="27"/>
       <c r="F98" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
@@ -4148,7 +4142,7 @@
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
-      <c r="E99" s="34"/>
+      <c r="E99" s="27"/>
       <c r="F99" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
@@ -4156,7 +4150,7 @@
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
       <c r="D100" s="6"/>
-      <c r="E100" s="34"/>
+      <c r="E100" s="27"/>
       <c r="F100" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
@@ -4164,7 +4158,7 @@
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
       <c r="D101" s="6"/>
-      <c r="E101" s="34"/>
+      <c r="E101" s="27"/>
       <c r="F101" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
@@ -4172,7 +4166,7 @@
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
-      <c r="E102" s="34"/>
+      <c r="E102" s="27"/>
       <c r="F102" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
@@ -4180,7 +4174,7 @@
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
       <c r="D103" s="6"/>
-      <c r="E103" s="34"/>
+      <c r="E103" s="27"/>
       <c r="F103" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
@@ -4188,7 +4182,7 @@
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
       <c r="D104" s="6"/>
-      <c r="E104" s="34"/>
+      <c r="E104" s="27"/>
       <c r="F104" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
@@ -4196,7 +4190,7 @@
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
       <c r="D105" s="6"/>
-      <c r="E105" s="34"/>
+      <c r="E105" s="27"/>
       <c r="F105" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
@@ -4204,7 +4198,7 @@
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
       <c r="D106" s="6"/>
-      <c r="E106" s="34"/>
+      <c r="E106" s="27"/>
       <c r="F106" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
@@ -4212,7 +4206,7 @@
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
       <c r="D107" s="6"/>
-      <c r="E107" s="34"/>
+      <c r="E107" s="27"/>
       <c r="F107" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
@@ -4220,7 +4214,7 @@
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
       <c r="D108" s="6"/>
-      <c r="E108" s="34"/>
+      <c r="E108" s="27"/>
       <c r="F108" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
@@ -4380,7 +4374,7 @@
       <c r="A6" s="29" t="s">
         <v>475</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="27" t="s">
         <v>481</v>
       </c>
       <c r="C6" s="31" t="s">
@@ -4612,7 +4606,7 @@
       <c r="E17" s="31" t="s">
         <v>491</v>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="34">
         <v>0</v>
       </c>
     </row>
@@ -4994,7 +4988,7 @@
       <c r="E37" s="31" t="s">
         <v>521</v>
       </c>
-      <c r="F37" s="35">
+      <c r="F37" s="34">
         <v>1</v>
       </c>
     </row>
@@ -5032,7 +5026,7 @@
       <c r="E39" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="F39" s="35">
+      <c r="F39" s="34">
         <v>0</v>
       </c>
     </row>
@@ -5052,7 +5046,7 @@
       <c r="E40" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="F40" s="35">
+      <c r="F40" s="34">
         <v>0</v>
       </c>
     </row>
@@ -10844,7 +10838,7 @@
       <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="46" t="s">
+      <c r="F1" s="44" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11587,7 +11581,7 @@
       <c r="B9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="45" t="s">
         <v>774</v>
       </c>
       <c r="D9" s="14" t="s">
@@ -11658,7 +11652,7 @@
       <c r="D1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="E1" s="44" t="s">
         <v>5</v>
       </c>
     </row>
@@ -12341,274 +12335,274 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="39" t="s">
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="F1" s="38" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="39" t="s">
         <v>735</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="40" t="s">
         <v>736</v>
       </c>
-      <c r="C2" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="42" t="s">
+      <c r="C2" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="40" t="s">
         <v>737</v>
       </c>
-      <c r="F2" s="43">
+      <c r="F2" s="41">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="39" t="s">
         <v>735</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="40" t="s">
         <v>738</v>
       </c>
-      <c r="C3" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="42" t="s">
+      <c r="C3" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="42" t="s">
+      <c r="E3" s="40" t="s">
         <v>739</v>
       </c>
-      <c r="F3" s="43">
+      <c r="F3" s="41">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="39" t="s">
         <v>735</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="40" t="s">
         <v>740</v>
       </c>
-      <c r="C4" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="42" t="s">
+      <c r="C4" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="40" t="s">
         <v>741</v>
       </c>
-      <c r="E4" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="44"/>
+      <c r="E4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="39" t="s">
         <v>735</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="40" t="s">
         <v>742</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="40" t="s">
         <v>743</v>
       </c>
-      <c r="E5" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="43">
+      <c r="E5" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="41">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="39" t="s">
         <v>735</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="40" t="s">
         <v>744</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="40" t="s">
         <v>745</v>
       </c>
-      <c r="E6" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="43">
+      <c r="E6" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="41">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="39" t="s">
         <v>735</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="40" t="s">
         <v>746</v>
       </c>
-      <c r="C7" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="42" t="s">
+      <c r="C7" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="40" t="s">
         <v>747</v>
       </c>
-      <c r="E7" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="44"/>
+      <c r="E7" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="39" t="s">
         <v>735</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="40" t="s">
         <v>748</v>
       </c>
-      <c r="C8" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="42" t="s">
+      <c r="C8" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="40" t="s">
         <v>749</v>
       </c>
-      <c r="E8" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="44"/>
+      <c r="E8" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="39" t="s">
         <v>735</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="40" t="s">
         <v>750</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="40" t="s">
         <v>751</v>
       </c>
-      <c r="E9" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="43">
+      <c r="E9" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="41">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="39" t="s">
         <v>735</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="40" t="s">
         <v>752</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="D10" s="40" t="s">
         <v>753</v>
       </c>
-      <c r="E10" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="43">
+      <c r="E10" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="41">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="39" t="s">
         <v>735</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="40" t="s">
         <v>483</v>
       </c>
-      <c r="C11" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="42" t="s">
+      <c r="C11" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="40" t="s">
         <v>754</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="40" t="s">
         <v>484</v>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="41">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="39" t="s">
         <v>735</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="40" t="s">
         <v>485</v>
       </c>
-      <c r="C12" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="42" t="s">
+      <c r="C12" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="40" t="s">
         <v>754</v>
       </c>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="40" t="s">
         <v>486</v>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="41">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="39" t="s">
         <v>735</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="40" t="s">
         <v>755</v>
       </c>
-      <c r="C13" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="42" t="s">
+      <c r="C13" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="40" t="s">
         <v>756</v>
       </c>
-      <c r="E13" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="44"/>
+      <c r="E13" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="39" t="s">
         <v>735</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="39" t="s">
         <v>757</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="39" t="s">
         <v>758</v>
       </c>
-      <c r="E14" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="45">
+      <c r="E14" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="43">
         <v>0</v>
       </c>
     </row>
@@ -12663,7 +12657,7 @@
       <c r="C2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="35" t="s">
         <v>30</v>
       </c>
       <c r="E2" s="17" t="s">
@@ -12683,7 +12677,7 @@
       <c r="C3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="35" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="17" t="s">
@@ -12701,7 +12695,7 @@
       <c r="C4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="35" t="s">
         <v>272</v>
       </c>
       <c r="E4" s="17" t="s">
@@ -12719,7 +12713,7 @@
       <c r="C5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E5" s="17" t="s">
@@ -12739,7 +12733,7 @@
       <c r="C6" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="35" t="s">
         <v>106</v>
       </c>
       <c r="E6" s="17" t="s">
@@ -12757,7 +12751,7 @@
       <c r="C7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="35" t="s">
         <v>169</v>
       </c>
       <c r="E7" s="17" t="s">
@@ -12775,7 +12769,7 @@
       <c r="C8" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="35" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="17" t="s">
@@ -12795,7 +12789,7 @@
       <c r="C9" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="35" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="17" t="s">
@@ -12815,7 +12809,7 @@
       <c r="C10" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="35" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="17" t="s">
@@ -12833,7 +12827,7 @@
       <c r="C11" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="35" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="17" t="s">
@@ -12853,7 +12847,7 @@
       <c r="C12" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="37" t="s">
+      <c r="D12" s="35" t="s">
         <v>640</v>
       </c>
       <c r="E12" s="17" t="s">
@@ -12871,7 +12865,7 @@
       <c r="C13" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="35" t="s">
         <v>642</v>
       </c>
       <c r="E13" s="17" t="s">
@@ -12889,7 +12883,7 @@
       <c r="C14" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="35" t="s">
         <v>644</v>
       </c>
       <c r="E14" s="17" t="s">
@@ -12909,7 +12903,7 @@
       <c r="C15" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="35" t="s">
         <v>646</v>
       </c>
       <c r="E15" s="17" t="s">
@@ -12927,7 +12921,7 @@
       <c r="C16" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D16" s="35" t="s">
         <v>646</v>
       </c>
       <c r="E16" s="17" t="s">
@@ -12945,7 +12939,7 @@
       <c r="C17" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="35" t="s">
         <v>646</v>
       </c>
       <c r="E17" s="17" t="s">
@@ -12963,7 +12957,7 @@
       <c r="C18" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="D18" s="35" t="s">
         <v>646</v>
       </c>
       <c r="E18" s="17" t="s">
@@ -12981,7 +12975,7 @@
       <c r="C19" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="35" t="s">
         <v>651</v>
       </c>
       <c r="E19" s="17" t="s">
@@ -12999,7 +12993,7 @@
       <c r="C20" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D20" s="35" t="s">
         <v>653</v>
       </c>
       <c r="E20" s="17" t="s">
@@ -13019,7 +13013,7 @@
       <c r="C21" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="D21" s="35" t="s">
         <v>655</v>
       </c>
       <c r="E21" s="17" t="s">
@@ -13057,7 +13051,7 @@
       <c r="C23" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="37" t="s">
+      <c r="D23" s="35" t="s">
         <v>381</v>
       </c>
       <c r="E23" s="17" t="s">
@@ -13075,7 +13069,7 @@
       <c r="C24" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="37" t="s">
+      <c r="D24" s="35" t="s">
         <v>382</v>
       </c>
       <c r="E24" s="17" t="s">
@@ -13093,7 +13087,7 @@
       <c r="C25" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="D25" s="35" t="s">
         <v>659</v>
       </c>
       <c r="E25" s="17" t="s">
@@ -13111,7 +13105,7 @@
       <c r="C26" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="37" t="s">
+      <c r="D26" s="35" t="s">
         <v>661</v>
       </c>
       <c r="E26" s="17" t="s">
@@ -13129,7 +13123,7 @@
       <c r="C27" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="D27" s="35" t="s">
         <v>385</v>
       </c>
       <c r="E27" s="17" t="s">
@@ -13147,7 +13141,7 @@
       <c r="C28" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="37" t="s">
+      <c r="D28" s="35" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="17" t="s">
@@ -13165,7 +13159,7 @@
       <c r="C29" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="37" t="s">
+      <c r="D29" s="35" t="s">
         <v>664</v>
       </c>
       <c r="E29" s="17" t="s">
@@ -13183,7 +13177,7 @@
       <c r="C30" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="37" t="s">
+      <c r="D30" s="35" t="s">
         <v>666</v>
       </c>
       <c r="E30" s="17" t="s">
@@ -13201,7 +13195,7 @@
       <c r="C31" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="37" t="s">
+      <c r="D31" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E31" s="17" t="s">
@@ -13221,7 +13215,7 @@
       <c r="C32" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="37" t="s">
+      <c r="D32" s="35" t="s">
         <v>669</v>
       </c>
       <c r="E32" s="17" t="s">
@@ -13239,7 +13233,7 @@
       <c r="C33" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D33" s="37" t="s">
+      <c r="D33" s="35" t="s">
         <v>671</v>
       </c>
       <c r="E33" s="17" t="s">
@@ -13257,7 +13251,7 @@
       <c r="C34" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="37" t="s">
+      <c r="D34" s="35" t="s">
         <v>673</v>
       </c>
       <c r="E34" s="17" t="s">
@@ -13275,7 +13269,7 @@
       <c r="C35" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="37" t="s">
+      <c r="D35" s="35" t="s">
         <v>675</v>
       </c>
       <c r="E35" s="17" t="s">
@@ -13293,7 +13287,7 @@
       <c r="C36" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D36" s="37" t="s">
+      <c r="D36" s="35" t="s">
         <v>677</v>
       </c>
       <c r="E36" s="17" t="s">
@@ -13311,7 +13305,7 @@
       <c r="C37" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D37" s="37" t="s">
+      <c r="D37" s="35" t="s">
         <v>185</v>
       </c>
       <c r="E37" s="17" t="s">
@@ -13329,7 +13323,7 @@
       <c r="C38" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="37" t="s">
+      <c r="D38" s="35" t="s">
         <v>679</v>
       </c>
       <c r="E38" s="17" t="s">
@@ -13347,7 +13341,7 @@
       <c r="C39" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="37" t="s">
+      <c r="D39" s="35" t="s">
         <v>681</v>
       </c>
       <c r="E39" s="17" t="s">
@@ -13365,7 +13359,7 @@
       <c r="C40" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="37" t="s">
+      <c r="D40" s="35" t="s">
         <v>683</v>
       </c>
       <c r="E40" s="17" t="s">
@@ -13383,7 +13377,7 @@
       <c r="C41" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="37" t="s">
+      <c r="D41" s="35" t="s">
         <v>685</v>
       </c>
       <c r="E41" s="17" t="s">
@@ -13401,7 +13395,7 @@
       <c r="C42" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="37" t="s">
+      <c r="D42" s="35" t="s">
         <v>687</v>
       </c>
       <c r="E42" s="17" t="s">
@@ -13419,7 +13413,7 @@
       <c r="C43" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D43" s="37" t="s">
+      <c r="D43" s="35" t="s">
         <v>689</v>
       </c>
       <c r="E43" s="17" t="s">
@@ -13437,7 +13431,7 @@
       <c r="C44" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D44" s="37" t="s">
+      <c r="D44" s="35" t="s">
         <v>691</v>
       </c>
       <c r="E44" s="17" t="s">
@@ -13455,7 +13449,7 @@
       <c r="C45" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="37" t="s">
+      <c r="D45" s="35" t="s">
         <v>693</v>
       </c>
       <c r="E45" s="17" t="s">
@@ -13473,7 +13467,7 @@
       <c r="C46" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="37" t="s">
+      <c r="D46" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E46" s="17" t="s">
@@ -13493,7 +13487,7 @@
       <c r="C47" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D47" s="37" t="s">
+      <c r="D47" s="35" t="s">
         <v>696</v>
       </c>
       <c r="E47" s="17" t="s">
@@ -13511,7 +13505,7 @@
       <c r="C48" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="37" t="s">
+      <c r="D48" s="35" t="s">
         <v>698</v>
       </c>
       <c r="E48" s="17" t="s">
@@ -13531,7 +13525,7 @@
       <c r="C49" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="37" t="s">
+      <c r="D49" s="35" t="s">
         <v>700</v>
       </c>
       <c r="E49" s="17" t="s">
@@ -13551,7 +13545,7 @@
       <c r="C50" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D50" s="37" t="s">
+      <c r="D50" s="35" t="s">
         <v>702</v>
       </c>
       <c r="E50" s="17" t="s">
@@ -13569,13 +13563,13 @@
       <c r="C51" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D51" s="37" t="s">
+      <c r="D51" s="35" t="s">
         <v>704</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F51" s="37"/>
+      <c r="F51" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
       <c r="A52" s="17" t="s">
@@ -13587,7 +13581,7 @@
       <c r="C52" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D52" s="37" t="s">
+      <c r="D52" s="35" t="s">
         <v>706</v>
       </c>
       <c r="E52" s="17" t="s">
@@ -13605,7 +13599,7 @@
       <c r="C53" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="37" t="s">
+      <c r="D53" s="35" t="s">
         <v>708</v>
       </c>
       <c r="E53" s="17" t="s">
@@ -13623,7 +13617,7 @@
       <c r="C54" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D54" s="37" t="s">
+      <c r="D54" s="35" t="s">
         <v>710</v>
       </c>
       <c r="E54" s="17" t="s">
@@ -13641,7 +13635,7 @@
       <c r="C55" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D55" s="37" t="s">
+      <c r="D55" s="35" t="s">
         <v>708</v>
       </c>
       <c r="E55" s="17" t="s">
@@ -13659,7 +13653,7 @@
       <c r="C56" s="17" t="s">
         <v>713</v>
       </c>
-      <c r="D56" s="37" t="s">
+      <c r="D56" s="35" t="s">
         <v>714</v>
       </c>
       <c r="E56" s="17" t="s">
@@ -13677,7 +13671,7 @@
       <c r="C57" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="37" t="s">
+      <c r="D57" s="35" t="s">
         <v>716</v>
       </c>
       <c r="E57" s="17" t="s">
@@ -13695,7 +13689,7 @@
       <c r="C58" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="37" t="s">
+      <c r="D58" s="35" t="s">
         <v>716</v>
       </c>
       <c r="E58" s="17" t="s">
@@ -13715,7 +13709,7 @@
       <c r="C59" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D59" s="37" t="s">
+      <c r="D59" s="35" t="s">
         <v>708</v>
       </c>
       <c r="E59" s="17" t="s">
@@ -13733,7 +13727,7 @@
       <c r="C60" s="17" t="s">
         <v>713</v>
       </c>
-      <c r="D60" s="37" t="s">
+      <c r="D60" s="35" t="s">
         <v>720</v>
       </c>
       <c r="E60" s="17" t="s">
@@ -13751,7 +13745,7 @@
       <c r="C61" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D61" s="37" t="s">
+      <c r="D61" s="35" t="s">
         <v>14</v>
       </c>
       <c r="E61" s="17" t="s">
@@ -13771,7 +13765,7 @@
       <c r="C62" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D62" s="37" t="s">
+      <c r="D62" s="35" t="s">
         <v>724</v>
       </c>
       <c r="E62" s="17" t="s">
@@ -13789,7 +13783,7 @@
       <c r="C63" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D63" s="37" t="s">
+      <c r="D63" s="35" t="s">
         <v>726</v>
       </c>
       <c r="E63" s="17" t="s">
@@ -13798,55 +13792,55 @@
       <c r="F63" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
-      <c r="A64" s="34" t="s">
+      <c r="A64" s="27" t="s">
         <v>635</v>
       </c>
-      <c r="B64" s="34" t="s">
+      <c r="B64" s="27" t="s">
         <v>727</v>
       </c>
-      <c r="C64" s="34" t="s">
+      <c r="C64" s="27" t="s">
         <v>25</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>728</v>
       </c>
-      <c r="E64" s="34" t="s">
+      <c r="E64" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F64" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
-      <c r="A65" s="34" t="s">
+      <c r="A65" s="27" t="s">
         <v>635</v>
       </c>
-      <c r="B65" s="34" t="s">
+      <c r="B65" s="27" t="s">
         <v>729</v>
       </c>
-      <c r="C65" s="34" t="s">
+      <c r="C65" s="27" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="7" t="s">
         <v>730</v>
       </c>
-      <c r="E65" s="34" t="s">
+      <c r="E65" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F65" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
-      <c r="A66" s="34" t="s">
+      <c r="A66" s="27" t="s">
         <v>635</v>
       </c>
-      <c r="B66" s="34" t="s">
+      <c r="B66" s="27" t="s">
         <v>731</v>
       </c>
-      <c r="C66" s="34" t="s">
+      <c r="C66" s="27" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>732</v>
       </c>
-      <c r="E66" s="34" t="s">
+      <c r="E66" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F66" s="7"/>
@@ -13861,7 +13855,7 @@
       <c r="C67" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D67" s="37" t="s">
+      <c r="D67" s="35" t="s">
         <v>734</v>
       </c>
       <c r="E67" s="17" t="s">
@@ -13883,7 +13877,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="9" width="31.005" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="9" width="27.14785714285714" customWidth="1" bestFit="1"/>
@@ -13906,7 +13900,7 @@
       <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
     </row>

--- a/src/global/utils/file-utils/locators(2).xlsx
+++ b/src/global/utils/file-utils/locators(2).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2898" uniqueCount="834">
   <si>
     <t>page</t>
   </si>
@@ -1336,18 +1336,21 @@
     <t>winBoostToolTipMZ</t>
   </si>
   <si>
+    <t>Win Boost 2%. 1 more for 3% (Min odds 1.2)</t>
+  </si>
+  <si>
     <t>winBoostToolTipGHS</t>
   </si>
   <si>
     <t>winBoostToolTipZM</t>
   </si>
   <si>
+    <t>winBoostToolTipMW</t>
+  </si>
+  <si>
     <t>winBoostToolTipBW</t>
   </si>
   <si>
-    <t>Win Boost 2%. 1 more for 3% (Min odds 1.2)</t>
-  </si>
-  <si>
     <t>winBoostToolTip</t>
   </si>
   <si>
@@ -1372,7 +1375,7 @@
     <t>winBoostValueMZ</t>
   </si>
   <si>
-    <t>Win Boost (3%): MT</t>
+    <t>Win Boost (2%): MT</t>
   </si>
   <si>
     <t>winBoostValueZM</t>
@@ -1381,6 +1384,12 @@
     <t>Win Boost (3%): K</t>
   </si>
   <si>
+    <t>winBoostValueMW</t>
+  </si>
+  <si>
+    <t>Win Boost (2%): MK</t>
+  </si>
+  <si>
     <t>winBoostValueBW</t>
   </si>
   <si>
@@ -1714,7 +1723,7 @@
     <t>helpInComments</t>
   </si>
   <si>
-    <t>Header Actions</t>
+    <t>feeds-comments-author ui-button:has(img[alt="dots-icon"])</t>
   </si>
   <si>
     <t>submitincomments</t>
@@ -1891,7 +1900,7 @@
     <t>gameDiv</t>
   </si>
   <si>
-    <t>//*[@id="tab"]/div/div[2]/div/div[2]/div/div/div[1]/div[1]</t>
+    <t>//*[@id="tab"]/div/div[1]/div/div[2]/div/div/div/div[1]/div[1]</t>
   </si>
   <si>
     <t>Play</t>
@@ -1942,6 +1951,12 @@
     <t>{ "exact": true }</t>
   </si>
   <si>
+    <t>logOut</t>
+  </si>
+  <si>
+    <t>#Log\ Out-hamburger-menu-btn</t>
+  </si>
+  <si>
     <t>gameDivVirtuals</t>
   </si>
   <si>
@@ -2117,12 +2132,6 @@
   </si>
   <si>
     <t>#Change\ password-hamburger-menu-btn</t>
-  </si>
-  <si>
-    <t>logOut</t>
-  </si>
-  <si>
-    <t>#Log\ out-hamburger-menu-btn</t>
   </si>
   <si>
     <t>closeMyAccountOptions</t>
@@ -2699,7 +2708,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2775,6 +2784,12 @@
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3159,16 +3174,16 @@
       <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="43" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>8</v>
@@ -3177,7 +3192,7 @@
         <v>30</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="F2" s="8">
         <v>1</v>
@@ -3185,10 +3200,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>8</v>
@@ -3197,22 +3212,22 @@
         <v>30</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="F3" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>23</v>
@@ -3221,10 +3236,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>8</v>
@@ -3233,16 +3248,16 @@
         <v>30</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="F5" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>8</v>
@@ -3251,16 +3266,16 @@
         <v>30</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="F6" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>8</v>
@@ -3269,22 +3284,22 @@
         <v>30</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="F7" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>23</v>
@@ -3293,16 +3308,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>23</v>
@@ -3311,16 +3326,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>23</v>
@@ -3329,10 +3344,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>8</v>
@@ -3341,22 +3356,22 @@
         <v>30</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="F11" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>23</v>
@@ -3365,16 +3380,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>23</v>
@@ -3383,16 +3398,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>23</v>
@@ -3401,16 +3416,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>23</v>
@@ -3419,16 +3434,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>23</v>
@@ -3437,16 +3452,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>23</v>
@@ -3455,16 +3470,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>23</v>
@@ -3473,16 +3488,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="43" t="s">
-        <v>829</v>
+      <c r="D19" s="45" t="s">
+        <v>832</v>
       </c>
       <c r="E19" s="25" t="s">
         <v>23</v>
@@ -3491,10 +3506,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>8</v>
@@ -3503,7 +3518,7 @@
         <v>30</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="F20" s="8"/>
     </row>
@@ -4265,820 +4280,820 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="26" t="s">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="29" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B2" s="28" t="s">
+      <c r="A2" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B2" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="29" t="s">
+      <c r="C2" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="28" t="s">
-        <v>479</v>
-      </c>
-      <c r="F2" s="30">
+      <c r="E2" s="30" t="s">
+        <v>482</v>
+      </c>
+      <c r="F2" s="32">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B3" s="28" t="s">
+      <c r="A3" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B3" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="C3" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="29" t="s">
+      <c r="C3" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="F3" s="30">
+      <c r="F3" s="32">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>480</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="29" t="s">
+      <c r="A4" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>483</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="30" t="s">
+        <v>484</v>
+      </c>
+      <c r="F4" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="28" t="s">
         <v>481</v>
       </c>
-      <c r="F4" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>482</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="29" t="s">
+      <c r="B5" s="30" t="s">
+        <v>485</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="28" t="s">
-        <v>483</v>
-      </c>
-      <c r="F5" s="30">
+      <c r="E5" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="F5" s="32">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="26" t="s">
-        <v>478</v>
+      <c r="A6" s="28" t="s">
+        <v>481</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>484</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="28" t="s">
-        <v>485</v>
+      <c r="E6" s="30" t="s">
+        <v>488</v>
       </c>
       <c r="F6" s="7">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B7" s="28" t="s">
+      <c r="A7" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B7" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="29" t="s">
+      <c r="C7" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="32">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B8" s="28" t="s">
+      <c r="A8" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B8" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="C8" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="29" t="s">
+      <c r="C8" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="32">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>486</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="29" t="s">
+      <c r="A9" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>489</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="28" t="s">
-        <v>487</v>
-      </c>
-      <c r="F9" s="30">
+      <c r="E9" s="30" t="s">
+        <v>490</v>
+      </c>
+      <c r="F9" s="32">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>488</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="29" t="s">
+      <c r="A10" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>491</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="28" t="s">
-        <v>489</v>
-      </c>
-      <c r="F10" s="30">
+      <c r="E10" s="30" t="s">
+        <v>492</v>
+      </c>
+      <c r="F10" s="32">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>490</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="29" t="s">
+      <c r="A11" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>493</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="28" t="s">
-        <v>491</v>
-      </c>
-      <c r="F11" s="30">
+      <c r="E11" s="30" t="s">
+        <v>494</v>
+      </c>
+      <c r="F11" s="32">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B12" s="28" t="s">
+      <c r="A12" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B12" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="29" t="s">
+      <c r="C12" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="30">
+      <c r="E12" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="32">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>492</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="29" t="s">
+      <c r="A13" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>495</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="32">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>493</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="29" t="s">
+      <c r="A14" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>496</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="31" t="s">
         <v>355</v>
       </c>
-      <c r="E14" s="28" t="s">
-        <v>494</v>
-      </c>
-      <c r="F14" s="30">
+      <c r="E14" s="30" t="s">
+        <v>497</v>
+      </c>
+      <c r="F14" s="32">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>495</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>496</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>494</v>
-      </c>
-      <c r="F15" s="30">
+      <c r="A15" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>498</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>499</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>497</v>
+      </c>
+      <c r="F15" s="32">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B16" s="28" t="s">
+      <c r="A16" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>500</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>501</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>502</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="30" t="s">
         <v>497</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="F17" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>503</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>504</v>
+      </c>
+      <c r="F18" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>505</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="31" t="s">
+        <v>355</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>506</v>
+      </c>
+      <c r="F19" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>507</v>
+      </c>
+      <c r="C20" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="29" t="s">
-        <v>498</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>499</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="29" t="s">
+      <c r="D20" s="31" t="s">
+        <v>508</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>509</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="28" t="s">
-        <v>494</v>
-      </c>
-      <c r="F17" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>500</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="29" t="s">
+      <c r="E21" s="30" t="s">
+        <v>510</v>
+      </c>
+      <c r="F21" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>511</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="28" t="s">
-        <v>501</v>
-      </c>
-      <c r="F18" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>502</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="29" t="s">
-        <v>355</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>503</v>
-      </c>
-      <c r="F19" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>504</v>
-      </c>
-      <c r="C20" s="28" t="s">
+      <c r="E22" s="30" t="s">
+        <v>512</v>
+      </c>
+      <c r="F22" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>513</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" s="31" t="s">
+        <v>514</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>515</v>
+      </c>
+      <c r="F23" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>516</v>
+      </c>
+      <c r="C24" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="29" t="s">
-        <v>505</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B21" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="C21" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="29" t="s">
+      <c r="D24" s="31">
+        <v>27</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>517</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="31" t="s">
+        <v>518</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>519</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="F21" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B22" s="28" t="s">
-        <v>508</v>
-      </c>
-      <c r="C22" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="29" t="s">
+      <c r="E26" s="30" t="s">
+        <v>520</v>
+      </c>
+      <c r="F26" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>521</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="28" t="s">
-        <v>509</v>
-      </c>
-      <c r="F22" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B23" s="28" t="s">
-        <v>510</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="D23" s="29" t="s">
-        <v>511</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>512</v>
-      </c>
-      <c r="F23" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>513</v>
-      </c>
-      <c r="C24" s="28" t="s">
+      <c r="E27" s="30" t="s">
+        <v>522</v>
+      </c>
+      <c r="F27" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>418</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="32"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>419</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" s="32"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>420</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="31" t="s">
+        <v>421</v>
+      </c>
+      <c r="E30" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" s="32"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>422</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" s="32"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>424</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="31" t="s">
+        <v>425</v>
+      </c>
+      <c r="E32" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" s="32"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>426</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="31" t="s">
+        <v>427</v>
+      </c>
+      <c r="E33" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="32"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+      <c r="A34" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="B34" s="30" t="s">
+        <v>428</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="31" t="s">
+        <v>429</v>
+      </c>
+      <c r="E34" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" s="32"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+      <c r="A35" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="B35" s="30" t="s">
+        <v>439</v>
+      </c>
+      <c r="C35" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="29">
-        <v>27</v>
-      </c>
-      <c r="E24" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24" s="30">
+      <c r="D35" s="31" t="s">
+        <v>523</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" s="32"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+      <c r="A36" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="B36" s="30" t="s">
+        <v>454</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="31" t="s">
+        <v>524</v>
+      </c>
+      <c r="E36" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" s="32"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+      <c r="A37" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="B37" s="30" t="s">
+        <v>525</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="31" t="s">
+        <v>526</v>
+      </c>
+      <c r="E37" s="30" t="s">
+        <v>527</v>
+      </c>
+      <c r="F37" s="33">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B25" s="28" t="s">
-        <v>514</v>
-      </c>
-      <c r="C25" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="29" t="s">
-        <v>515</v>
-      </c>
-      <c r="E25" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B26" s="28" t="s">
-        <v>516</v>
-      </c>
-      <c r="C26" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="28" t="s">
-        <v>517</v>
-      </c>
-      <c r="F26" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B27" s="28" t="s">
-        <v>518</v>
-      </c>
-      <c r="C27" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="28" t="s">
-        <v>519</v>
-      </c>
-      <c r="F27" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="26" t="s">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+      <c r="A38" s="28" t="s">
         <v>379</v>
       </c>
-      <c r="B28" s="28" t="s">
-        <v>418</v>
-      </c>
-      <c r="C28" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" s="30"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="26" t="s">
+      <c r="B38" s="30" t="s">
+        <v>456</v>
+      </c>
+      <c r="C38" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38" s="32"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+      <c r="A39" s="28" t="s">
         <v>379</v>
       </c>
-      <c r="B29" s="28" t="s">
-        <v>419</v>
-      </c>
-      <c r="C29" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D29" s="29" t="s">
-        <v>222</v>
-      </c>
-      <c r="E29" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F29" s="30"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="26" t="s">
+      <c r="B39" s="30" t="s">
+        <v>457</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="31" t="s">
+        <v>458</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+      <c r="A40" s="28" t="s">
         <v>379</v>
       </c>
-      <c r="B30" s="28" t="s">
-        <v>420</v>
-      </c>
-      <c r="C30" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" s="29" t="s">
-        <v>421</v>
-      </c>
-      <c r="E30" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30" s="30"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="26" t="s">
+      <c r="B40" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="C40" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" s="31" t="s">
+        <v>460</v>
+      </c>
+      <c r="E40" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+      <c r="A41" s="28" t="s">
         <v>379</v>
       </c>
-      <c r="B31" s="28" t="s">
-        <v>422</v>
-      </c>
-      <c r="C31" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="29" t="s">
-        <v>423</v>
-      </c>
-      <c r="E31" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" s="30"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="26" t="s">
+      <c r="B41" s="30" t="s">
+        <v>461</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="31" t="s">
+        <v>462</v>
+      </c>
+      <c r="E41" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41" s="32"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+      <c r="A42" s="28" t="s">
         <v>379</v>
       </c>
-      <c r="B32" s="28" t="s">
-        <v>424</v>
-      </c>
-      <c r="C32" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="29" t="s">
-        <v>425</v>
-      </c>
-      <c r="E32" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F32" s="30"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="B33" s="28" t="s">
-        <v>426</v>
-      </c>
-      <c r="C33" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="29" t="s">
-        <v>427</v>
-      </c>
-      <c r="E33" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33" s="30"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="B34" s="28" t="s">
-        <v>428</v>
-      </c>
-      <c r="C34" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="29" t="s">
-        <v>429</v>
-      </c>
-      <c r="E34" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34" s="30"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="B35" s="28" t="s">
-        <v>438</v>
-      </c>
-      <c r="C35" s="28" t="s">
+      <c r="B42" s="30" t="s">
+        <v>463</v>
+      </c>
+      <c r="C42" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="29" t="s">
-        <v>520</v>
-      </c>
-      <c r="E35" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F35" s="30"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="B36" s="28" t="s">
-        <v>451</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="D36" s="29" t="s">
-        <v>521</v>
-      </c>
-      <c r="E36" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F36" s="30"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="B37" s="28" t="s">
-        <v>522</v>
-      </c>
-      <c r="C37" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" s="29" t="s">
-        <v>523</v>
-      </c>
-      <c r="E37" s="28" t="s">
-        <v>524</v>
-      </c>
-      <c r="F37" s="31">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>453</v>
-      </c>
-      <c r="C38" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="E38" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F38" s="30"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="B39" s="28" t="s">
-        <v>454</v>
-      </c>
-      <c r="C39" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="D39" s="29" t="s">
-        <v>455</v>
-      </c>
-      <c r="E39" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F39" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="B40" s="28" t="s">
-        <v>456</v>
-      </c>
-      <c r="C40" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" s="29" t="s">
-        <v>457</v>
-      </c>
-      <c r="E40" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F40" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="B41" s="28" t="s">
-        <v>458</v>
-      </c>
-      <c r="C41" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="D41" s="29" t="s">
-        <v>459</v>
-      </c>
-      <c r="E41" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F41" s="30"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="B42" s="28" t="s">
-        <v>460</v>
-      </c>
-      <c r="C42" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="D42" s="29" t="s">
-        <v>459</v>
-      </c>
-      <c r="E42" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F42" s="30"/>
+      <c r="D42" s="31" t="s">
+        <v>462</v>
+      </c>
+      <c r="E42" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5090,7 +5105,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="4" width="16.576428571428572" customWidth="1" bestFit="1"/>
@@ -5760,7 +5775,7 @@
         <v>68</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>23</v>
@@ -5772,7 +5787,7 @@
         <v>379</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>68</v>
@@ -5790,7 +5805,7 @@
         <v>379</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>68</v>
@@ -5804,22 +5819,22 @@
       <c r="F39" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="26" t="s">
         <v>379</v>
       </c>
-      <c r="B40" s="17" t="s">
-        <v>436</v>
-      </c>
-      <c r="C40" s="17" t="s">
+      <c r="B40" s="26" t="s">
+        <v>437</v>
+      </c>
+      <c r="C40" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F40" s="16"/>
+      <c r="D40" s="26" t="s">
+        <v>434</v>
+      </c>
+      <c r="E40" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="17" t="s">
@@ -5832,7 +5847,7 @@
         <v>68</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>23</v>
@@ -5850,7 +5865,7 @@
         <v>68</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>23</v>
@@ -5862,13 +5877,13 @@
         <v>379</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>23</v>
@@ -5880,13 +5895,13 @@
         <v>379</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>23</v>
@@ -5898,31 +5913,31 @@
         <v>379</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F45" s="18"/>
+      <c r="F45" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="17" t="s">
         <v>379</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>23</v>
@@ -5934,31 +5949,31 @@
         <v>379</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F47" s="16"/>
+      <c r="F47" s="18"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="17" t="s">
         <v>379</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>23</v>
@@ -5970,13 +5985,13 @@
         <v>379</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>95</v>
+        <v>453</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>23</v>
@@ -5999,9 +6014,7 @@
       <c r="E50" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F50" s="16">
-        <v>0</v>
-      </c>
+      <c r="F50" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="17" t="s">
@@ -6014,50 +6027,52 @@
         <v>68</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>457</v>
+        <v>95</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F51" s="18">
-        <v>0</v>
-      </c>
+      <c r="F51" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="17" t="s">
         <v>379</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F52" s="18"/>
+      <c r="F52" s="16">
+        <v>0</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="17" t="s">
         <v>379</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F53" s="18"/>
+      <c r="F53" s="18">
+        <v>0</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="17" t="s">
@@ -6075,7 +6090,7 @@
       <c r="E54" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F54" s="16"/>
+      <c r="F54" s="18"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="17" t="s">
@@ -6085,37 +6100,33 @@
         <v>463</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F55" s="16">
-        <v>0</v>
-      </c>
+      <c r="F55" s="18"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="17" t="s">
         <v>379</v>
       </c>
       <c r="B56" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" s="17" t="s">
         <v>465</v>
       </c>
-      <c r="C56" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D56" s="17" t="s">
-        <v>464</v>
-      </c>
       <c r="E56" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F56" s="16">
-        <v>1</v>
-      </c>
+      <c r="F56" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="17" t="s">
@@ -6128,13 +6139,13 @@
         <v>21</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>23</v>
       </c>
       <c r="F57" s="16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
@@ -6142,85 +6153,89 @@
         <v>379</v>
       </c>
       <c r="B58" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="C58" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="C58" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D58" s="17" t="s">
-        <v>218</v>
-      </c>
       <c r="E58" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F58" s="16"/>
+      <c r="F58" s="16">
+        <v>1</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="17" t="s">
         <v>379</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C59" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F59" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+      <c r="A60" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="B60" s="17" t="s">
+        <v>470</v>
+      </c>
+      <c r="C60" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="E60" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F60" s="16"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+      <c r="A61" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>471</v>
+      </c>
+      <c r="C61" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D59" s="17" t="s">
-        <v>469</v>
-      </c>
-      <c r="E59" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F59" s="16"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
-      <c r="A60" s="25" t="s">
-        <v>379</v>
-      </c>
-      <c r="B60" s="25" t="s">
-        <v>470</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D60" s="25" t="s">
-        <v>471</v>
-      </c>
-      <c r="E60" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F60" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
-      <c r="A61" s="25" t="s">
-        <v>379</v>
-      </c>
-      <c r="B61" s="25" t="s">
+      <c r="D61" s="17" t="s">
         <v>472</v>
       </c>
-      <c r="C61" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D61" s="25" t="s">
-        <v>473</v>
-      </c>
-      <c r="E61" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F61" s="8"/>
+      <c r="E61" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F61" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="25" t="s">
         <v>379</v>
       </c>
       <c r="B62" s="25" t="s">
+        <v>473</v>
+      </c>
+      <c r="C62" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="25" t="s">
         <v>474</v>
-      </c>
-      <c r="C62" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>475</v>
       </c>
       <c r="E62" s="25" t="s">
         <v>23</v>
@@ -6232,18 +6247,54 @@
         <v>379</v>
       </c>
       <c r="B63" s="25" t="s">
+        <v>475</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="25" t="s">
         <v>476</v>
       </c>
-      <c r="C63" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D63" s="25" t="s">
+      <c r="E63" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+      <c r="A64" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="B64" s="25" t="s">
         <v>477</v>
       </c>
-      <c r="E63" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F63" s="8"/>
+      <c r="C64" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" s="25" t="s">
+        <v>478</v>
+      </c>
+      <c r="E64" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F64" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+      <c r="A65" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="B65" s="25" t="s">
+        <v>479</v>
+      </c>
+      <c r="C65" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D65" s="25" t="s">
+        <v>480</v>
+      </c>
+      <c r="E65" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F65" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10868,13 +10919,13 @@
       <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="43" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>176</v>
@@ -10894,7 +10945,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>187</v>
@@ -10906,7 +10957,7 @@
         <v>30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="F3" s="8">
         <v>0</v>
@@ -10914,7 +10965,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>189</v>
@@ -10934,7 +10985,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>191</v>
@@ -10954,7 +11005,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>193</v>
@@ -10974,7 +11025,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>195</v>
@@ -10994,7 +11045,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>197</v>
@@ -11006,7 +11057,7 @@
         <v>30</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="F8" s="8">
         <v>0</v>
@@ -11014,7 +11065,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>199</v>
@@ -11026,7 +11077,7 @@
         <v>30</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="F9" s="8">
         <v>0</v>
@@ -11034,7 +11085,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>201</v>
@@ -11046,7 +11097,7 @@
         <v>30</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="F10" s="8">
         <v>0</v>
@@ -11054,7 +11105,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>203</v>
@@ -11066,7 +11117,7 @@
         <v>30</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
@@ -11074,7 +11125,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>205</v>
@@ -11086,7 +11137,7 @@
         <v>30</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="F12" s="8">
         <v>0</v>
@@ -11094,7 +11145,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>207</v>
@@ -11106,7 +11157,7 @@
         <v>30</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="F13" s="8">
         <v>0</v>
@@ -11114,7 +11165,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>209</v>
@@ -11134,7 +11185,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>211</v>
@@ -11146,7 +11197,7 @@
         <v>30</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
@@ -11154,7 +11205,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>213</v>
@@ -11166,7 +11217,7 @@
         <v>30</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="F16" s="8">
         <v>0</v>
@@ -11174,7 +11225,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>215</v>
@@ -11186,7 +11237,7 @@
         <v>30</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="F17" s="8">
         <v>0</v>
@@ -11194,7 +11245,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>217</v>
@@ -11214,7 +11265,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>384</v>
@@ -11234,7 +11285,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>220</v>
@@ -11254,7 +11305,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>221</v>
@@ -11274,7 +11325,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>32</v>
@@ -11294,7 +11345,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>223</v>
@@ -11314,7 +11365,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>225</v>
@@ -11334,7 +11385,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>227</v>
@@ -11354,7 +11405,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="6" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>229</v>
@@ -11451,7 +11502,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>23</v>
@@ -11499,13 +11550,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="14" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>23</v>
@@ -11516,13 +11567,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="14" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>23</v>
@@ -11531,13 +11582,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="14" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>23</v>
@@ -11546,13 +11597,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="14" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>23</v>
@@ -11561,13 +11612,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="14" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>23</v>
@@ -11582,7 +11633,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>23</v>
@@ -11591,13 +11642,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>23</v>
@@ -11606,13 +11657,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="42" t="s">
-        <v>777</v>
+      <c r="C9" s="44" t="s">
+        <v>780</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>23</v>
@@ -11621,13 +11672,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>23</v>
@@ -11636,7 +11687,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>8</v>
@@ -11645,7 +11696,7 @@
         <v>14</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="E11" s="8"/>
     </row>
@@ -11682,7 +11733,7 @@
       <c r="D1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="E1" s="43" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11714,7 +11765,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="E3" s="15">
         <v>0</v>
@@ -12365,274 +12416,274 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="34" t="s">
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="37" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="36" t="s">
-        <v>738</v>
-      </c>
-      <c r="B2" s="37" t="s">
-        <v>739</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="37" t="s">
+      <c r="A2" s="38" t="s">
+        <v>741</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>742</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="37" t="s">
-        <v>740</v>
-      </c>
-      <c r="F2" s="38">
+      <c r="E2" s="39" t="s">
+        <v>743</v>
+      </c>
+      <c r="F2" s="40">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="36" t="s">
-        <v>738</v>
-      </c>
-      <c r="B3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>741</v>
       </c>
-      <c r="C3" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="37" t="s">
+      <c r="B3" s="39" t="s">
+        <v>744</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="37" t="s">
-        <v>742</v>
-      </c>
-      <c r="F3" s="38">
+      <c r="E3" s="39" t="s">
+        <v>745</v>
+      </c>
+      <c r="F3" s="40">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="36" t="s">
-        <v>738</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>743</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>744</v>
-      </c>
-      <c r="E4" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="39"/>
+      <c r="A4" s="38" t="s">
+        <v>741</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>746</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="39" t="s">
+        <v>747</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="41"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="36" t="s">
-        <v>738</v>
-      </c>
-      <c r="B5" s="37" t="s">
-        <v>745</v>
-      </c>
-      <c r="C5" s="37" t="s">
+      <c r="A5" s="38" t="s">
+        <v>741</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>748</v>
+      </c>
+      <c r="C5" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="37" t="s">
-        <v>746</v>
-      </c>
-      <c r="E5" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="38">
+      <c r="D5" s="39" t="s">
+        <v>749</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="40">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="36" t="s">
-        <v>738</v>
-      </c>
-      <c r="B6" s="37" t="s">
-        <v>747</v>
-      </c>
-      <c r="C6" s="37" t="s">
+      <c r="A6" s="38" t="s">
+        <v>741</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>750</v>
+      </c>
+      <c r="C6" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="37" t="s">
-        <v>748</v>
-      </c>
-      <c r="E6" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="38">
+      <c r="D6" s="39" t="s">
+        <v>751</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="40">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="36" t="s">
-        <v>738</v>
-      </c>
-      <c r="B7" s="37" t="s">
-        <v>749</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>750</v>
-      </c>
-      <c r="E7" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="39"/>
+      <c r="A7" s="38" t="s">
+        <v>741</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>752</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>753</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="41"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="36" t="s">
-        <v>738</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>751</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>752</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="39"/>
+      <c r="A8" s="38" t="s">
+        <v>741</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>754</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>755</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="41"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="36" t="s">
-        <v>738</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>753</v>
-      </c>
-      <c r="C9" s="37" t="s">
+      <c r="A9" s="38" t="s">
+        <v>741</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>756</v>
+      </c>
+      <c r="C9" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="37" t="s">
-        <v>754</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="38">
+      <c r="D9" s="39" t="s">
+        <v>757</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="40">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="36" t="s">
-        <v>738</v>
-      </c>
-      <c r="B10" s="37" t="s">
-        <v>755</v>
-      </c>
-      <c r="C10" s="37" t="s">
+      <c r="A10" s="38" t="s">
+        <v>741</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>758</v>
+      </c>
+      <c r="C10" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="37" t="s">
-        <v>756</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="38">
+      <c r="D10" s="39" t="s">
+        <v>759</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="40">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="36" t="s">
-        <v>738</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>486</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="37" t="s">
-        <v>757</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>487</v>
-      </c>
-      <c r="F11" s="38">
+      <c r="A11" s="38" t="s">
+        <v>741</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>489</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>760</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>490</v>
+      </c>
+      <c r="F11" s="40">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="36" t="s">
-        <v>738</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>488</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>757</v>
-      </c>
-      <c r="E12" s="37" t="s">
-        <v>489</v>
-      </c>
-      <c r="F12" s="38">
+      <c r="A12" s="38" t="s">
+        <v>741</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>491</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>760</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>492</v>
+      </c>
+      <c r="F12" s="40">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="36" t="s">
-        <v>738</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>758</v>
-      </c>
-      <c r="C13" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="37" t="s">
-        <v>759</v>
-      </c>
-      <c r="E13" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="39"/>
+      <c r="A13" s="38" t="s">
+        <v>741</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>761</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>762</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="41"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="36" t="s">
-        <v>738</v>
-      </c>
-      <c r="B14" s="36" t="s">
-        <v>760</v>
-      </c>
-      <c r="C14" s="36" t="s">
+      <c r="A14" s="38" t="s">
+        <v>741</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>763</v>
+      </c>
+      <c r="C14" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="36" t="s">
-        <v>761</v>
-      </c>
-      <c r="E14" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="40">
+      <c r="D14" s="38" t="s">
+        <v>764</v>
+      </c>
+      <c r="E14" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="42">
         <v>0</v>
       </c>
     </row>
@@ -12679,19 +12730,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="34" t="s">
         <v>30</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="F2" s="18">
         <v>0</v>
@@ -12699,7 +12750,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>7</v>
@@ -12707,7 +12758,7 @@
       <c r="C3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="34" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="17" t="s">
@@ -12717,7 +12768,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>271</v>
@@ -12725,7 +12776,7 @@
       <c r="C4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="34" t="s">
         <v>272</v>
       </c>
       <c r="E4" s="17" t="s">
@@ -12735,7 +12786,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>273</v>
@@ -12743,7 +12794,7 @@
       <c r="C5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="34" t="s">
         <v>77</v>
       </c>
       <c r="E5" s="17" t="s">
@@ -12755,7 +12806,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>105</v>
@@ -12763,7 +12814,7 @@
       <c r="C6" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="34" t="s">
         <v>106</v>
       </c>
       <c r="E6" s="17" t="s">
@@ -12773,7 +12824,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>13</v>
@@ -12781,7 +12832,7 @@
       <c r="C7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E7" s="17" t="s">
@@ -12791,7 +12842,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>170</v>
@@ -12799,7 +12850,7 @@
       <c r="C8" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="34" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="17" t="s">
@@ -12811,15 +12862,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="34" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="17" t="s">
@@ -12831,7 +12882,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>172</v>
@@ -12839,7 +12890,7 @@
       <c r="C10" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="34" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="17" t="s">
@@ -12849,7 +12900,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>174</v>
@@ -12857,7 +12908,7 @@
       <c r="C11" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="34" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="17" t="s">
@@ -12869,16 +12920,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="32" t="s">
-        <v>643</v>
+      <c r="D12" s="34" t="s">
+        <v>648</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>23</v>
@@ -12887,16 +12938,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="32" t="s">
-        <v>645</v>
+      <c r="D13" s="34" t="s">
+        <v>650</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>23</v>
@@ -12905,16 +12956,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="32" t="s">
-        <v>647</v>
+      <c r="D14" s="34" t="s">
+        <v>652</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>23</v>
@@ -12925,16 +12976,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="32" t="s">
-        <v>649</v>
+      <c r="D15" s="34" t="s">
+        <v>654</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>23</v>
@@ -12943,16 +12994,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="32" t="s">
-        <v>649</v>
+      <c r="D16" s="34" t="s">
+        <v>654</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>23</v>
@@ -12961,16 +13012,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="32" t="s">
-        <v>649</v>
+      <c r="D17" s="34" t="s">
+        <v>654</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>23</v>
@@ -12979,16 +13030,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="32" t="s">
-        <v>649</v>
+      <c r="D18" s="34" t="s">
+        <v>654</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>23</v>
@@ -12997,16 +13048,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="32" t="s">
-        <v>654</v>
+      <c r="D19" s="34" t="s">
+        <v>659</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>23</v>
@@ -13015,16 +13066,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="32" t="s">
-        <v>656</v>
+      <c r="D20" s="34" t="s">
+        <v>661</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>23</v>
@@ -13035,16 +13086,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="32" t="s">
-        <v>658</v>
+      <c r="D21" s="34" t="s">
+        <v>663</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>23</v>
@@ -13053,10 +13104,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>68</v>
@@ -13073,15 +13124,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="34" t="s">
         <v>381</v>
       </c>
       <c r="E23" s="17" t="s">
@@ -13091,7 +13142,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>165</v>
@@ -13099,7 +13150,7 @@
       <c r="C24" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="34" t="s">
         <v>382</v>
       </c>
       <c r="E24" s="17" t="s">
@@ -13109,16 +13160,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D25" s="32" t="s">
-        <v>662</v>
+      <c r="D25" s="34" t="s">
+        <v>667</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>23</v>
@@ -13127,16 +13178,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="32" t="s">
-        <v>664</v>
+      <c r="D26" s="34" t="s">
+        <v>669</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>23</v>
@@ -13145,7 +13196,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B27" s="17" t="s">
         <v>384</v>
@@ -13153,7 +13204,7 @@
       <c r="C27" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="34" t="s">
         <v>385</v>
       </c>
       <c r="E27" s="17" t="s">
@@ -13163,15 +13214,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="34" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="17" t="s">
@@ -13181,16 +13232,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="32" t="s">
-        <v>667</v>
+      <c r="D29" s="34" t="s">
+        <v>672</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>23</v>
@@ -13199,16 +13250,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="32" t="s">
-        <v>669</v>
+      <c r="D30" s="34" t="s">
+        <v>674</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>23</v>
@@ -13217,15 +13268,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="34" t="s">
         <v>77</v>
       </c>
       <c r="E31" s="17" t="s">
@@ -13237,16 +13288,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="32" t="s">
-        <v>672</v>
+      <c r="D32" s="34" t="s">
+        <v>677</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>23</v>
@@ -13255,16 +13306,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D33" s="32" t="s">
-        <v>674</v>
+      <c r="D33" s="34" t="s">
+        <v>679</v>
       </c>
       <c r="E33" s="17" t="s">
         <v>23</v>
@@ -13273,16 +13324,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="32" t="s">
-        <v>676</v>
+      <c r="D34" s="34" t="s">
+        <v>681</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>23</v>
@@ -13291,16 +13342,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="32" t="s">
-        <v>678</v>
+      <c r="D35" s="34" t="s">
+        <v>683</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>23</v>
@@ -13309,16 +13360,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D36" s="32" t="s">
-        <v>680</v>
+      <c r="D36" s="34" t="s">
+        <v>685</v>
       </c>
       <c r="E36" s="17" t="s">
         <v>23</v>
@@ -13327,7 +13378,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B37" s="17" t="s">
         <v>184</v>
@@ -13335,7 +13386,7 @@
       <c r="C37" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="34" t="s">
         <v>185</v>
       </c>
       <c r="E37" s="17" t="s">
@@ -13345,16 +13396,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="32" t="s">
-        <v>682</v>
+      <c r="D38" s="34" t="s">
+        <v>687</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>23</v>
@@ -13363,16 +13414,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="32" t="s">
-        <v>684</v>
+      <c r="D39" s="34" t="s">
+        <v>689</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>23</v>
@@ -13381,16 +13432,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="C40" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="32" t="s">
-        <v>686</v>
+      <c r="D40" s="34" t="s">
+        <v>691</v>
       </c>
       <c r="E40" s="17" t="s">
         <v>23</v>
@@ -13399,16 +13450,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="32" t="s">
-        <v>688</v>
+      <c r="D41" s="34" t="s">
+        <v>693</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>23</v>
@@ -13417,16 +13468,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="32" t="s">
-        <v>690</v>
+      <c r="D42" s="34" t="s">
+        <v>695</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>23</v>
@@ -13435,16 +13486,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D43" s="32" t="s">
-        <v>692</v>
+      <c r="D43" s="34" t="s">
+        <v>697</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>23</v>
@@ -13453,16 +13504,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D44" s="32" t="s">
-        <v>694</v>
+      <c r="D44" s="34" t="s">
+        <v>699</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>23</v>
@@ -13471,16 +13522,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>695</v>
+        <v>639</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="32" t="s">
-        <v>696</v>
+      <c r="D45" s="34" t="s">
+        <v>640</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>23</v>
@@ -13489,15 +13540,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="32" t="s">
+      <c r="D46" s="34" t="s">
         <v>77</v>
       </c>
       <c r="E46" s="17" t="s">
@@ -13509,16 +13560,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D47" s="32" t="s">
-        <v>699</v>
+      <c r="D47" s="34" t="s">
+        <v>702</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>23</v>
@@ -13527,16 +13578,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="32" t="s">
-        <v>701</v>
+      <c r="D48" s="34" t="s">
+        <v>704</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>23</v>
@@ -13547,16 +13598,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="32" t="s">
-        <v>703</v>
+      <c r="D49" s="34" t="s">
+        <v>706</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>23</v>
@@ -13567,160 +13618,160 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C50" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D50" s="32" t="s">
-        <v>705</v>
+      <c r="D50" s="34" t="s">
+        <v>708</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>162</v>
       </c>
       <c r="F50" s="16"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D51" s="32" t="s">
-        <v>707</v>
+      <c r="D51" s="34" t="s">
+        <v>710</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F51" s="32"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
+      <c r="F51" s="34"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D52" s="32" t="s">
-        <v>709</v>
+      <c r="D52" s="34" t="s">
+        <v>712</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>23</v>
       </c>
       <c r="F52" s="16"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="32" t="s">
-        <v>711</v>
+      <c r="D53" s="34" t="s">
+        <v>714</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>23</v>
       </c>
       <c r="F53" s="16"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D54" s="32" t="s">
-        <v>713</v>
+      <c r="D54" s="34" t="s">
+        <v>716</v>
       </c>
       <c r="E54" s="17" t="s">
         <v>23</v>
       </c>
       <c r="F54" s="16"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D55" s="32" t="s">
-        <v>711</v>
+      <c r="D55" s="34" t="s">
+        <v>714</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>23</v>
       </c>
       <c r="F55" s="16"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>716</v>
-      </c>
-      <c r="D56" s="32" t="s">
-        <v>717</v>
+        <v>719</v>
+      </c>
+      <c r="D56" s="34" t="s">
+        <v>720</v>
       </c>
       <c r="E56" s="17" t="s">
         <v>23</v>
       </c>
       <c r="F56" s="16"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C57" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="32" t="s">
-        <v>719</v>
+      <c r="D57" s="34" t="s">
+        <v>722</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>23</v>
       </c>
       <c r="F57" s="16"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="32" t="s">
-        <v>719</v>
+      <c r="D58" s="34" t="s">
+        <v>722</v>
       </c>
       <c r="E58" s="17" t="s">
         <v>23</v>
@@ -13729,36 +13780,36 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C59" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D59" s="32" t="s">
-        <v>711</v>
+      <c r="D59" s="34" t="s">
+        <v>714</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>23</v>
       </c>
       <c r="F59" s="16"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>716</v>
-      </c>
-      <c r="D60" s="32" t="s">
-        <v>723</v>
+        <v>719</v>
+      </c>
+      <c r="D60" s="34" t="s">
+        <v>726</v>
       </c>
       <c r="E60" s="17" t="s">
         <v>23</v>
@@ -13767,19 +13818,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
       <c r="A61" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D61" s="32" t="s">
+      <c r="D61" s="34" t="s">
         <v>14</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="F61" s="18">
         <v>1</v>
@@ -13787,16 +13838,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="19.5">
       <c r="A62" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C62" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D62" s="32" t="s">
-        <v>727</v>
+      <c r="D62" s="34" t="s">
+        <v>730</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>23</v>
@@ -13805,16 +13856,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C63" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D63" s="32" t="s">
-        <v>729</v>
+      <c r="D63" s="34" t="s">
+        <v>732</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>23</v>
@@ -13823,16 +13874,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="25" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B64" s="25" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C64" s="25" t="s">
         <v>25</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="E64" s="25" t="s">
         <v>23</v>
@@ -13841,16 +13892,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="25" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B65" s="25" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C65" s="25" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E65" s="25" t="s">
         <v>23</v>
@@ -13859,16 +13910,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="25" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C66" s="25" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E66" s="25" t="s">
         <v>23</v>
@@ -13877,16 +13928,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5">
       <c r="A67" s="17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="C67" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D67" s="32" t="s">
-        <v>737</v>
+      <c r="D67" s="34" t="s">
+        <v>740</v>
       </c>
       <c r="E67" s="17" t="s">
         <v>23</v>
@@ -13903,7 +13954,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -13936,16 +13987,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>23</v>
@@ -13954,16 +14005,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>23</v>
@@ -13972,16 +14023,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>23</v>
@@ -13990,16 +14041,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>23</v>
@@ -14008,16 +14059,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>23</v>
@@ -14026,16 +14077,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>23</v>
@@ -14044,16 +14095,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>23</v>
@@ -14064,19 +14115,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="F9" s="8">
         <v>0</v>
@@ -14084,16 +14135,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>23</v>
@@ -14102,16 +14153,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>23</v>
@@ -14122,19 +14173,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="F12" s="8">
         <v>0</v>
@@ -14142,16 +14193,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>23</v>
@@ -14160,7 +14211,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>320</v>
@@ -14169,10 +14220,10 @@
         <v>68</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="F14" s="8">
         <v>0</v>
@@ -14180,10 +14231,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>8</v>
@@ -14192,7 +14243,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
@@ -14200,10 +14251,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>68</v>
@@ -14212,34 +14263,36 @@
         <v>197</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="F16" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>626</v>
-      </c>
-      <c r="F17" s="8"/>
+        <v>629</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>68</v>
@@ -14248,22 +14301,22 @@
         <v>282</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="F18" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>23</v>
@@ -14272,10 +14325,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>68</v>
@@ -14284,13 +14337,13 @@
         <v>213</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="F20" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>7</v>
@@ -14310,7 +14363,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>11</v>
@@ -14330,7 +14383,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>13</v>
@@ -14350,7 +14403,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>76</v>
@@ -14370,37 +14423,39 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>632</v>
-      </c>
-      <c r="F25" s="8"/>
+        <v>635</v>
+      </c>
+      <c r="F25" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="F26" s="8">
         <v>1</v>
@@ -14408,21 +14463,39 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>636</v>
-      </c>
-      <c r="C27" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>639</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>640</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="16"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>637</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" s="8"/>
+      <c r="D28" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14467,16 +14540,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>23</v>
@@ -14487,16 +14560,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>144</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>23</v>
@@ -14505,16 +14578,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>23</v>
@@ -14525,19 +14598,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F5" s="8">
         <v>1</v>
@@ -14545,19 +14618,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>144</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F6" s="8">
         <v>1</v>
@@ -14565,10 +14638,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>8</v>
@@ -14577,7 +14650,7 @@
         <v>14</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F7" s="8">
         <v>0</v>
@@ -14585,16 +14658,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>23</v>
@@ -14603,10 +14676,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>8</v>
@@ -14615,7 +14688,7 @@
         <v>9</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="F9" s="8">
         <v>0</v>
@@ -14623,10 +14696,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>8</v>
@@ -14635,7 +14708,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F10" s="8">
         <v>0</v>
@@ -14643,10 +14716,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>8</v>
@@ -14655,7 +14728,7 @@
         <v>14</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
@@ -14663,16 +14736,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>23</v>
@@ -14683,16 +14756,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>23</v>
@@ -14703,10 +14776,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>8</v>
@@ -14715,7 +14788,7 @@
         <v>14</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F14" s="8">
         <v>10</v>
@@ -14723,10 +14796,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>8</v>
@@ -14735,7 +14808,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
@@ -14743,16 +14816,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>23</v>
@@ -14763,10 +14836,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>8</v>
@@ -14775,7 +14848,7 @@
         <v>9</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F17" s="8">
         <v>0</v>
@@ -14783,30 +14856,30 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>8</v>
@@ -14815,7 +14888,7 @@
         <v>14</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="F19" s="8">
         <v>0</v>
@@ -14823,19 +14896,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F20" s="8">
         <v>0</v>
@@ -14843,16 +14916,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>23</v>
@@ -14863,10 +14936,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>8</v>
@@ -14875,7 +14948,7 @@
         <v>14</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="F22" s="8">
         <v>0</v>
@@ -14883,19 +14956,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F23" s="8">
         <v>0</v>
@@ -14903,10 +14976,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>8</v>
@@ -14915,7 +14988,7 @@
         <v>14</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="F24" s="8">
         <v>10</v>
@@ -14923,7 +14996,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>32</v>
@@ -14935,7 +15008,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="F25" s="8">
         <v>0</v>
@@ -14943,19 +15016,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F26" s="8">
         <v>0</v>
@@ -14963,7 +15036,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>61</v>
@@ -14972,7 +15045,7 @@
         <v>21</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>23</v>
@@ -14983,10 +15056,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>21</v>
@@ -15003,7 +15076,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>76</v>
@@ -15023,16 +15096,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>23</v>
@@ -15043,10 +15116,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>8</v>
@@ -15055,7 +15128,7 @@
         <v>14</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="F31" s="8">
         <v>0</v>
@@ -15063,16 +15136,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>23</v>
@@ -15083,10 +15156,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>8</v>
@@ -15095,7 +15168,7 @@
         <v>9</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="F33" s="8">
         <v>0</v>
@@ -15103,19 +15176,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>144</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F34" s="8">
         <v>0</v>
@@ -15123,10 +15196,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>8</v>
@@ -15135,7 +15208,7 @@
         <v>14</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F35" s="8">
         <v>0</v>
@@ -15143,10 +15216,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>8</v>
@@ -15155,7 +15228,7 @@
         <v>9</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F36" s="8">
         <v>0</v>
@@ -15163,16 +15236,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>23</v>
@@ -15183,16 +15256,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>23</v>
@@ -15203,7 +15276,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>7</v>
@@ -15223,7 +15296,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>11</v>
@@ -15243,7 +15316,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>13</v>

--- a/src/global/utils/file-utils/locators(2).xlsx
+++ b/src/global/utils/file-utils/locators(2).xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="HomePage"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2898" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="841">
   <si>
     <t>page</t>
   </si>
@@ -1990,7 +1990,7 @@
     <t>myAccount</t>
   </si>
   <si>
-    <t>My Account</t>
+    <t>#My\ Profile-hamburger-menu-btn</t>
   </si>
   <si>
     <t>bettingRulesGHS</t>
@@ -2008,12 +2008,36 @@
     <t>bettingRulesMZ</t>
   </si>
   <si>
+    <t xml:space="preserve"> Betting Rules</t>
+  </si>
+  <si>
     <t>bettingRulesTips</t>
   </si>
   <si>
     <t>Betting Rules and Tips</t>
   </si>
   <si>
+    <t>insiderBlog</t>
+  </si>
+  <si>
+    <t>Insider Blog</t>
+  </si>
+  <si>
+    <t>betwayScoresApp</t>
+  </si>
+  <si>
+    <t>Betway Scores App</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>howTo</t>
+  </si>
+  <si>
+    <t>How To</t>
+  </si>
+  <si>
     <t>statistics</t>
   </si>
   <si>
@@ -2050,13 +2074,13 @@
     <t>depositFund</t>
   </si>
   <si>
-    <t>#Deposit\ funds-hamburger-menu-btn</t>
+    <t>{"name":"Deposit"}</t>
   </si>
   <si>
     <t>withdrawFund</t>
   </si>
   <si>
-    <t>#Withdraw\ funds-hamburger-menu-btn</t>
+    <t>{"name":"Withdraw"}</t>
   </si>
   <si>
     <t>closeWithdrawalAlert</t>
@@ -2107,7 +2131,7 @@
     <t>responsibleGaming</t>
   </si>
   <si>
-    <t>#Responsible\ Gaming-hamburger-menu-btn</t>
+    <t xml:space="preserve"> Responsible Gaming</t>
   </si>
   <si>
     <t>documentVerification</t>
@@ -2131,7 +2155,7 @@
     <t>changePassword</t>
   </si>
   <si>
-    <t>#Change\ password-hamburger-menu-btn</t>
+    <t>Change password details</t>
   </si>
   <si>
     <t>closeMyAccountOptions</t>
@@ -2218,9 +2242,6 @@
     <t>depositButton</t>
   </si>
   <si>
-    <t>{"name":"Deposit"}</t>
-  </si>
-  <si>
     <t>notificationBellIcon</t>
   </si>
   <si>
@@ -2248,7 +2269,7 @@
     <t>hide_closeDiveHam</t>
   </si>
   <si>
-    <t>//*[@id="__nuxt"]/div/div[1]/div[2]/div[1]/div[1]/div[1]/div[2]</t>
+    <t>/html/body/div[98]/div/div[2]/div/div/div[1]/div[1]/div[1]/div/details/summary/div/div[1]/div[2]</t>
   </si>
   <si>
     <t>liveChatIcon</t>
@@ -2541,7 +2562,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2611,6 +2632,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -2708,7 +2735,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2785,17 +2812,11 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2803,37 +2824,55 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="15" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="15" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="18" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="18" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="18" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
@@ -2842,7 +2881,7 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="18" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="19" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3174,16 +3213,16 @@
       <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="47" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>8</v>
@@ -3192,7 +3231,7 @@
         <v>30</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="F2" s="8">
         <v>1</v>
@@ -3200,10 +3239,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>8</v>
@@ -3212,22 +3251,22 @@
         <v>30</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="F3" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>23</v>
@@ -3236,10 +3275,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>8</v>
@@ -3248,16 +3287,16 @@
         <v>30</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="F5" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>8</v>
@@ -3266,16 +3305,16 @@
         <v>30</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="F6" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>8</v>
@@ -3284,22 +3323,22 @@
         <v>30</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="F7" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>23</v>
@@ -3308,16 +3347,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>23</v>
@@ -3326,16 +3365,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>23</v>
@@ -3344,10 +3383,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>8</v>
@@ -3356,22 +3395,22 @@
         <v>30</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="F11" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>23</v>
@@ -3380,16 +3419,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>23</v>
@@ -3398,16 +3437,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>23</v>
@@ -3416,16 +3455,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>23</v>
@@ -3434,16 +3473,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>23</v>
@@ -3452,16 +3491,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>23</v>
@@ -3470,16 +3509,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>23</v>
@@ -3488,16 +3527,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="45" t="s">
-        <v>832</v>
+      <c r="D19" s="49" t="s">
+        <v>839</v>
       </c>
       <c r="E19" s="25" t="s">
         <v>23</v>
@@ -3506,10 +3545,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>8</v>
@@ -3518,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="F20" s="8"/>
     </row>
@@ -10919,13 +10958,13 @@
       <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="47" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>176</v>
@@ -10945,7 +10984,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>187</v>
@@ -10957,7 +10996,7 @@
         <v>30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="F3" s="8">
         <v>0</v>
@@ -10965,7 +11004,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>189</v>
@@ -10985,7 +11024,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>191</v>
@@ -11005,7 +11044,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>193</v>
@@ -11025,7 +11064,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>195</v>
@@ -11045,7 +11084,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>197</v>
@@ -11057,7 +11096,7 @@
         <v>30</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="F8" s="8">
         <v>0</v>
@@ -11065,7 +11104,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>199</v>
@@ -11077,7 +11116,7 @@
         <v>30</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="F9" s="8">
         <v>0</v>
@@ -11085,7 +11124,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>201</v>
@@ -11097,7 +11136,7 @@
         <v>30</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="F10" s="8">
         <v>0</v>
@@ -11105,7 +11144,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>203</v>
@@ -11117,7 +11156,7 @@
         <v>30</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
@@ -11125,7 +11164,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>205</v>
@@ -11137,7 +11176,7 @@
         <v>30</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="F12" s="8">
         <v>0</v>
@@ -11145,7 +11184,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>207</v>
@@ -11157,7 +11196,7 @@
         <v>30</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="F13" s="8">
         <v>0</v>
@@ -11165,7 +11204,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>209</v>
@@ -11185,7 +11224,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>211</v>
@@ -11197,7 +11236,7 @@
         <v>30</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
@@ -11205,7 +11244,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>213</v>
@@ -11217,7 +11256,7 @@
         <v>30</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="F16" s="8">
         <v>0</v>
@@ -11225,7 +11264,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>215</v>
@@ -11237,7 +11276,7 @@
         <v>30</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="F17" s="8">
         <v>0</v>
@@ -11245,7 +11284,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>217</v>
@@ -11265,7 +11304,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>384</v>
@@ -11285,7 +11324,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>220</v>
@@ -11305,7 +11344,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>221</v>
@@ -11325,7 +11364,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>32</v>
@@ -11345,7 +11384,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>223</v>
@@ -11365,7 +11404,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>225</v>
@@ -11385,7 +11424,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>227</v>
@@ -11405,7 +11444,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="6" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>229</v>
@@ -11502,7 +11541,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>23</v>
@@ -11550,13 +11589,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="14" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>23</v>
@@ -11567,13 +11606,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="14" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>23</v>
@@ -11582,13 +11621,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="14" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>23</v>
@@ -11597,13 +11636,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="14" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>23</v>
@@ -11612,13 +11651,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="14" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>23</v>
@@ -11633,7 +11672,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>23</v>
@@ -11642,13 +11681,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>23</v>
@@ -11657,13 +11696,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="44" t="s">
-        <v>780</v>
+      <c r="C9" s="48" t="s">
+        <v>787</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>23</v>
@@ -11672,13 +11711,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>23</v>
@@ -11687,7 +11726,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>8</v>
@@ -11696,7 +11735,7 @@
         <v>14</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="E11" s="8"/>
     </row>
@@ -11733,7 +11772,7 @@
       <c r="D1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="47" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11765,7 +11804,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="E3" s="15">
         <v>0</v>
@@ -12416,274 +12455,274 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="36" t="s">
+      <c r="A1" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="38" t="s">
-        <v>741</v>
-      </c>
-      <c r="B2" s="39" t="s">
-        <v>742</v>
-      </c>
-      <c r="C2" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="39" t="s">
+      <c r="A2" s="42" t="s">
+        <v>748</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>749</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="39" t="s">
-        <v>743</v>
-      </c>
-      <c r="F2" s="40">
+      <c r="E2" s="43" t="s">
+        <v>750</v>
+      </c>
+      <c r="F2" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="38" t="s">
-        <v>741</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>744</v>
-      </c>
-      <c r="C3" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="39" t="s">
+      <c r="A3" s="42" t="s">
+        <v>748</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>751</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="39" t="s">
-        <v>745</v>
-      </c>
-      <c r="F3" s="40">
+      <c r="E3" s="43" t="s">
+        <v>752</v>
+      </c>
+      <c r="F3" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="38" t="s">
-        <v>741</v>
-      </c>
-      <c r="B4" s="39" t="s">
-        <v>746</v>
-      </c>
-      <c r="C4" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>747</v>
-      </c>
-      <c r="E4" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="41"/>
+      <c r="A4" s="42" t="s">
+        <v>748</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>753</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>754</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="45"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="38" t="s">
-        <v>741</v>
-      </c>
-      <c r="B5" s="39" t="s">
+      <c r="A5" s="42" t="s">
         <v>748</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="B5" s="43" t="s">
+        <v>755</v>
+      </c>
+      <c r="C5" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="39" t="s">
-        <v>749</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="40">
+      <c r="D5" s="43" t="s">
+        <v>756</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="38" t="s">
-        <v>741</v>
-      </c>
-      <c r="B6" s="39" t="s">
-        <v>750</v>
-      </c>
-      <c r="C6" s="39" t="s">
+      <c r="A6" s="42" t="s">
+        <v>748</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>757</v>
+      </c>
+      <c r="C6" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="39" t="s">
-        <v>751</v>
-      </c>
-      <c r="E6" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="40">
+      <c r="D6" s="43" t="s">
+        <v>758</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="38" t="s">
-        <v>741</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>752</v>
-      </c>
-      <c r="C7" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>753</v>
-      </c>
-      <c r="E7" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="41"/>
+      <c r="A7" s="42" t="s">
+        <v>748</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>759</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>760</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="45"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="38" t="s">
-        <v>741</v>
-      </c>
-      <c r="B8" s="39" t="s">
-        <v>754</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>755</v>
-      </c>
-      <c r="E8" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="41"/>
+      <c r="A8" s="42" t="s">
+        <v>748</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>761</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>762</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="45"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="38" t="s">
-        <v>741</v>
-      </c>
-      <c r="B9" s="39" t="s">
-        <v>756</v>
-      </c>
-      <c r="C9" s="39" t="s">
+      <c r="A9" s="42" t="s">
+        <v>748</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>763</v>
+      </c>
+      <c r="C9" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="39" t="s">
-        <v>757</v>
-      </c>
-      <c r="E9" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="40">
+      <c r="D9" s="43" t="s">
+        <v>764</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="38" t="s">
-        <v>741</v>
-      </c>
-      <c r="B10" s="39" t="s">
-        <v>758</v>
-      </c>
-      <c r="C10" s="39" t="s">
+      <c r="A10" s="42" t="s">
+        <v>748</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>765</v>
+      </c>
+      <c r="C10" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="39" t="s">
-        <v>759</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="40">
+      <c r="D10" s="43" t="s">
+        <v>766</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="38" t="s">
-        <v>741</v>
-      </c>
-      <c r="B11" s="39" t="s">
+      <c r="A11" s="42" t="s">
+        <v>748</v>
+      </c>
+      <c r="B11" s="43" t="s">
         <v>489</v>
       </c>
-      <c r="C11" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>760</v>
-      </c>
-      <c r="E11" s="39" t="s">
+      <c r="C11" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>767</v>
+      </c>
+      <c r="E11" s="43" t="s">
         <v>490</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="38" t="s">
-        <v>741</v>
-      </c>
-      <c r="B12" s="39" t="s">
+      <c r="A12" s="42" t="s">
+        <v>748</v>
+      </c>
+      <c r="B12" s="43" t="s">
         <v>491</v>
       </c>
-      <c r="C12" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>760</v>
-      </c>
-      <c r="E12" s="39" t="s">
+      <c r="C12" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>767</v>
+      </c>
+      <c r="E12" s="43" t="s">
         <v>492</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="38" t="s">
-        <v>741</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>761</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>762</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="41"/>
+      <c r="A13" s="42" t="s">
+        <v>748</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>768</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>769</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="45"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="38" t="s">
-        <v>741</v>
-      </c>
-      <c r="B14" s="38" t="s">
-        <v>763</v>
-      </c>
-      <c r="C14" s="38" t="s">
+      <c r="A14" s="42" t="s">
+        <v>748</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>770</v>
+      </c>
+      <c r="C14" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="38" t="s">
-        <v>764</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="42">
+      <c r="D14" s="42" t="s">
+        <v>771</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="46">
         <v>0</v>
       </c>
     </row>
@@ -12697,7 +12736,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="4" width="12.290714285714287" customWidth="1" bestFit="1"/>
@@ -12952,7 +12991,9 @@
       <c r="E13" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="16"/>
+      <c r="F13" s="16">
+        <v>0</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="17" t="s">
@@ -12962,7 +13003,7 @@
         <v>651</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D14" s="34" t="s">
         <v>652</v>
@@ -13039,25 +13080,27 @@
         <v>68</v>
       </c>
       <c r="D18" s="34" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="16"/>
+      <c r="F18" s="16">
+        <v>0</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>23</v>
@@ -13068,57 +13111,53 @@
       <c r="A20" s="17" t="s">
         <v>643</v>
       </c>
-      <c r="B20" s="17" t="s">
-        <v>660</v>
+      <c r="B20" s="35" t="s">
+        <v>661</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="34" t="s">
-        <v>661</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" s="18">
-        <v>0</v>
-      </c>
+      <c r="D20" s="36" t="s">
+        <v>662</v>
+      </c>
+      <c r="E20" s="35"/>
+      <c r="F20" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="17" t="s">
         <v>643</v>
       </c>
-      <c r="B21" s="17" t="s">
-        <v>662</v>
+      <c r="B21" s="35" t="s">
+        <v>663</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="34" t="s">
-        <v>663</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" s="16"/>
+      <c r="D21" s="36" t="s">
+        <v>664</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>665</v>
+      </c>
+      <c r="F21" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D22" s="18">
-        <v>27</v>
+      <c r="D22" s="34" t="s">
+        <v>667</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="18">
         <v>0</v>
       </c>
     </row>
@@ -13127,31 +13166,33 @@
         <v>643</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>381</v>
+        <v>669</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="16"/>
+      <c r="F23" s="18">
+        <v>0</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>165</v>
+        <v>670</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>382</v>
+        <v>671</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>23</v>
@@ -13163,31 +13204,33 @@
         <v>643</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="34" t="s">
-        <v>667</v>
+        <v>68</v>
+      </c>
+      <c r="D25" s="18">
+        <v>27</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F25" s="16"/>
+      <c r="F25" s="16">
+        <v>0</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D26" s="34" t="s">
-        <v>669</v>
+        <v>381</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>23</v>
@@ -13199,13 +13242,13 @@
         <v>643</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>384</v>
+        <v>165</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D27" s="34" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>23</v>
@@ -13217,16 +13260,16 @@
         <v>643</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D28" s="34" t="s">
-        <v>14</v>
+        <v>675</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F28" s="16"/>
     </row>
@@ -13235,31 +13278,33 @@
         <v>643</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F29" s="16"/>
+      <c r="F29" s="38" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>673</v>
+        <v>384</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D30" s="34" t="s">
-        <v>674</v>
+        <v>385</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>23</v>
@@ -13271,54 +13316,54 @@
         <v>643</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D31" s="34" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" s="18">
-        <v>1</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F31" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D32" s="34" t="s">
-        <v>677</v>
+        <v>14</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F32" s="16"/>
+        <v>680</v>
+      </c>
+      <c r="F32" s="16">
+        <v>1</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>679</v>
+        <v>14</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>23</v>
+        <v>682</v>
       </c>
       <c r="F33" s="16"/>
     </row>
@@ -13327,31 +13372,33 @@
         <v>643</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D34" s="34" t="s">
-        <v>681</v>
+        <v>77</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="16"/>
+      <c r="F34" s="18">
+        <v>1</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D35" s="34" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>23</v>
@@ -13363,13 +13410,13 @@
         <v>643</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D36" s="34" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E36" s="17" t="s">
         <v>23</v>
@@ -13381,13 +13428,13 @@
         <v>643</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>184</v>
+        <v>688</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D37" s="34" t="s">
-        <v>185</v>
+        <v>689</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>23</v>
@@ -13399,13 +13446,13 @@
         <v>643</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D38" s="34" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>23</v>
@@ -13417,13 +13464,13 @@
         <v>643</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>23</v>
@@ -13435,13 +13482,13 @@
         <v>643</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>690</v>
+        <v>184</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D40" s="34" t="s">
-        <v>691</v>
+        <v>185</v>
       </c>
       <c r="E40" s="17" t="s">
         <v>23</v>
@@ -13453,13 +13500,13 @@
         <v>643</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>23</v>
@@ -13471,13 +13518,13 @@
         <v>643</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D42" s="34" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>23</v>
@@ -13489,31 +13536,33 @@
         <v>643</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D43" s="34" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F43" s="16"/>
+      <c r="F43" s="16">
+        <v>0</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D44" s="34" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>23</v>
@@ -13525,13 +13574,13 @@
         <v>643</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>639</v>
+        <v>702</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>640</v>
+        <v>703</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>23</v>
@@ -13543,33 +13592,31 @@
         <v>643</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D46" s="34" t="s">
-        <v>77</v>
+        <v>705</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F46" s="18">
-        <v>1</v>
-      </c>
+      <c r="F46" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D47" s="34" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>23</v>
@@ -13581,39 +13628,37 @@
         <v>643</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>703</v>
+        <v>639</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D48" s="34" t="s">
-        <v>704</v>
+        <v>640</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F48" s="18">
-        <v>0</v>
-      </c>
+      <c r="F48" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D49" s="34" t="s">
-        <v>706</v>
+        <v>77</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>23</v>
       </c>
       <c r="F49" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
@@ -13621,16 +13666,16 @@
         <v>643</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D50" s="34" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>162</v>
+        <v>23</v>
       </c>
       <c r="F50" s="16"/>
     </row>
@@ -13639,52 +13684,56 @@
         <v>643</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D51" s="34" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F51" s="34"/>
+      <c r="F51" s="18">
+        <v>0</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D52" s="34" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F52" s="16"/>
+      <c r="F52" s="18">
+        <v>0</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D53" s="34" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="F53" s="16"/>
     </row>
@@ -13693,31 +13742,31 @@
         <v>643</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D54" s="34" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E54" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F54" s="16"/>
+      <c r="F54" s="34"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D55" s="34" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>23</v>
@@ -13729,13 +13778,13 @@
         <v>643</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>719</v>
+        <v>68</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E56" s="17" t="s">
         <v>23</v>
@@ -13747,13 +13796,13 @@
         <v>643</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C57" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D57" s="34" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>23</v>
@@ -13765,7 +13814,7 @@
         <v>643</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>68</v>
@@ -13776,22 +13825,20 @@
       <c r="E58" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F58" s="18">
-        <v>1</v>
-      </c>
+      <c r="F58" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>68</v>
+        <v>727</v>
       </c>
       <c r="D59" s="34" t="s">
-        <v>714</v>
+        <v>728</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>23</v>
@@ -13803,51 +13850,51 @@
         <v>643</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>719</v>
+        <v>68</v>
       </c>
       <c r="D60" s="34" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E60" s="17" t="s">
         <v>23</v>
       </c>
       <c r="F60" s="16"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="D61" s="34" t="s">
-        <v>14</v>
+        <v>730</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>728</v>
+        <v>23</v>
       </c>
       <c r="F61" s="18">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="D62" s="34" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>23</v>
@@ -13859,90 +13906,146 @@
         <v>643</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C63" s="17" t="s">
+        <v>727</v>
+      </c>
+      <c r="D63" s="34" t="s">
+        <v>734</v>
+      </c>
+      <c r="E63" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63" s="16"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5">
+      <c r="A64" s="17" t="s">
+        <v>643</v>
+      </c>
+      <c r="B64" s="17" t="s">
+        <v>735</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="17" t="s">
+        <v>680</v>
+      </c>
+      <c r="F64" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
+      <c r="A65" s="17" t="s">
+        <v>643</v>
+      </c>
+      <c r="B65" s="17" t="s">
+        <v>736</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D65" s="34" t="s">
+        <v>737</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F65" s="16"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+      <c r="A66" s="17" t="s">
+        <v>643</v>
+      </c>
+      <c r="B66" s="17" t="s">
+        <v>738</v>
+      </c>
+      <c r="C66" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D63" s="34" t="s">
-        <v>732</v>
-      </c>
-      <c r="E63" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F63" s="16"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
-      <c r="A64" s="25" t="s">
+      <c r="D66" s="34" t="s">
+        <v>739</v>
+      </c>
+      <c r="E66" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66" s="16"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+      <c r="A67" s="25" t="s">
         <v>643</v>
       </c>
-      <c r="B64" s="25" t="s">
-        <v>733</v>
-      </c>
-      <c r="C64" s="25" t="s">
+      <c r="B67" s="25" t="s">
+        <v>740</v>
+      </c>
+      <c r="C67" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D64" s="7" t="s">
-        <v>734</v>
-      </c>
-      <c r="E64" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F64" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
-      <c r="A65" s="25" t="s">
+      <c r="D67" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="E67" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F67" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+      <c r="A68" s="25" t="s">
         <v>643</v>
       </c>
-      <c r="B65" s="25" t="s">
-        <v>735</v>
-      </c>
-      <c r="C65" s="25" t="s">
+      <c r="B68" s="25" t="s">
+        <v>742</v>
+      </c>
+      <c r="C68" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D65" s="7" t="s">
-        <v>736</v>
-      </c>
-      <c r="E65" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F65" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
-      <c r="A66" s="25" t="s">
+      <c r="D68" s="7" t="s">
+        <v>743</v>
+      </c>
+      <c r="E68" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F68" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
+      <c r="A69" s="25" t="s">
         <v>643</v>
       </c>
-      <c r="B66" s="25" t="s">
-        <v>737</v>
-      </c>
-      <c r="C66" s="25" t="s">
+      <c r="B69" s="25" t="s">
+        <v>744</v>
+      </c>
+      <c r="C69" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D66" s="7" t="s">
-        <v>738</v>
-      </c>
-      <c r="E66" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F66" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5">
-      <c r="A67" s="17" t="s">
+      <c r="D69" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="E69" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F69" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="19.5">
+      <c r="A70" s="17" t="s">
         <v>643</v>
       </c>
-      <c r="B67" s="17" t="s">
-        <v>739</v>
-      </c>
-      <c r="C67" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D67" s="34" t="s">
-        <v>740</v>
-      </c>
-      <c r="E67" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F67" s="16"/>
+      <c r="B70" s="17" t="s">
+        <v>746</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="34" t="s">
+        <v>747</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F70" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/global/utils/file-utils/locators(2).xlsx
+++ b/src/global/utils/file-utils/locators(2).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2911" uniqueCount="840">
   <si>
     <t>page</t>
   </si>
@@ -1081,13 +1081,13 @@
     <t>jackpotsBtn</t>
   </si>
   <si>
-    <t>#transaction-history-jackpot-btn</t>
+    <t>//*[@id="date"]</t>
   </si>
   <si>
     <t>accountMain</t>
   </si>
   <si>
-    <t>div#my-account-main</t>
+    <t>#my-account-main</t>
   </si>
   <si>
     <t>transactionIdInput</t>
@@ -1099,432 +1099,432 @@
     <t>datePicker</t>
   </si>
   <si>
+    <t>#date</t>
+  </si>
+  <si>
+    <t>previousMonthBtn</t>
+  </si>
+  <si>
+    <t>{"name":"Previous Month"}</t>
+  </si>
+  <si>
+    <t>dateOkBtn</t>
+  </si>
+  <si>
+    <t>{"name":"Ok","exact":true}</t>
+  </si>
+  <si>
+    <t>dateClearBtn</t>
+  </si>
+  <si>
+    <t>{"name":"Clear"}</t>
+  </si>
+  <si>
+    <t>dateDialog</t>
+  </si>
+  <si>
+    <t>dialog</t>
+  </si>
+  <si>
+    <t>{"name":"Choose Date"}</t>
+  </si>
+  <si>
+    <t>exportBtn</t>
+  </si>
+  <si>
+    <t>#transaction-history-export-btn</t>
+  </si>
+  <si>
+    <t>transactionIDButton</t>
+  </si>
+  <si>
+    <t>span.underline.cursor-pointer</t>
+  </si>
+  <si>
+    <t>transactionDetailView</t>
+  </si>
+  <si>
+    <t>svg.w-6.h-6.cursor-pointer.fill-dark-600</t>
+  </si>
+  <si>
+    <t>{"name":"Back"}</t>
+  </si>
+  <si>
+    <t>betslipBackButton</t>
+  </si>
+  <si>
+    <t>#detail-view-back-btn</t>
+  </si>
+  <si>
+    <t>prevPageButton</t>
+  </si>
+  <si>
+    <t>#transaction-history-prev</t>
+  </si>
+  <si>
+    <t>nextPageButton</t>
+  </si>
+  <si>
+    <t>multipleBetsButton</t>
+  </si>
+  <si>
+    <t>BetslipPage</t>
+  </si>
+  <si>
+    <t>usernameInput</t>
+  </si>
+  <si>
+    <t>#header-username</t>
+  </si>
+  <si>
+    <t>#header-password</t>
+  </si>
+  <si>
+    <t>img[alt="Sport"]</t>
+  </si>
+  <si>
+    <t>betslipButton</t>
+  </si>
+  <si>
+    <t>Betslip 0</t>
+  </si>
+  <si>
+    <t>betslipCount</t>
+  </si>
+  <si>
+    <t>[data-testid="betslip-count"]</t>
+  </si>
+  <si>
+    <t>singleTab</t>
+  </si>
+  <si>
+    <t>multiTab</t>
+  </si>
+  <si>
+    <t>bookingCodeInput</t>
+  </si>
+  <si>
+    <t>settingsButton</t>
+  </si>
+  <si>
+    <t>#betslip-setting-btn</t>
+  </si>
+  <si>
+    <t>warningText</t>
+  </si>
+  <si>
+    <t>No selected betsYou don't</t>
+  </si>
+  <si>
+    <t>loadButton</t>
+  </si>
+  <si>
+    <t>{"name":"load"}</t>
+  </si>
+  <si>
+    <t>settingsText</t>
+  </si>
+  <si>
+    <t>Betslip Settings</t>
+  </si>
+  <si>
+    <t>acceptOddsToggleLabel</t>
+  </si>
+  <si>
+    <t>Accept all odds &amp; line changes</t>
+  </si>
+  <si>
+    <t>acceptOddsToggle</t>
+  </si>
+  <si>
+    <t>#settings-accept-odds-toggle</t>
+  </si>
+  <si>
+    <t>keepBetsToggleLabel</t>
+  </si>
+  <si>
+    <t>Keep bets in betslip</t>
+  </si>
+  <si>
+    <t>keepBetsToggle</t>
+  </si>
+  <si>
+    <t>#settings-keep-bets-in-betslip-toggle</t>
+  </si>
+  <si>
+    <t>continueButton</t>
+  </si>
+  <si>
+    <t>#settings-continue-btn</t>
+  </si>
+  <si>
+    <t>closeIcon</t>
+  </si>
+  <si>
+    <t>simpleViewToggle</t>
+  </si>
+  <si>
+    <t>#simple-view-toggle</t>
+  </si>
+  <si>
+    <t>deleteIcon</t>
+  </si>
+  <si>
+    <t>selectAllCheckbox</t>
+  </si>
+  <si>
+    <t>#betslip-select-all</t>
+  </si>
+  <si>
+    <t>removeLegIcon</t>
+  </si>
+  <si>
+    <t>#remove-event-betslip</t>
+  </si>
+  <si>
+    <t>loginBtnBetslip</t>
+  </si>
+  <si>
+    <t>betNowBtn</t>
+  </si>
+  <si>
+    <t>shareBtn</t>
+  </si>
+  <si>
+    <t>cashBtnSingle</t>
+  </si>
+  <si>
+    <t>#single-cash-tab</t>
+  </si>
+  <si>
+    <t>freebetBtnSingle</t>
+  </si>
+  <si>
+    <t>#single-free-tab</t>
+  </si>
+  <si>
+    <t>cashBtnMulti</t>
+  </si>
+  <si>
+    <t>#multi-cash-balance-tab</t>
+  </si>
+  <si>
+    <t>freebetBtnMulti</t>
+  </si>
+  <si>
+    <t>#multi-freebet-tab</t>
+  </si>
+  <si>
+    <t>cashOutIcon</t>
+  </si>
+  <si>
+    <t>.w-4.h-4.fill-primary-300 &gt; path</t>
+  </si>
+  <si>
+    <t>winBoostToolTipTZ</t>
+  </si>
+  <si>
+    <t>Win Boost 3%. 1 more for 5% (Min odds 1.2)</t>
+  </si>
+  <si>
+    <t>winBoostToolTipNG</t>
+  </si>
+  <si>
+    <t>winBoostToolTipMZ</t>
+  </si>
+  <si>
+    <t>Win Boost 2%. 1 more for 3% (Min odds 1.2)</t>
+  </si>
+  <si>
+    <t>winBoostToolTipGHS</t>
+  </si>
+  <si>
+    <t>winBoostToolTipZM</t>
+  </si>
+  <si>
+    <t>winBoostToolTipMW</t>
+  </si>
+  <si>
+    <t>winBoostToolTipBW</t>
+  </si>
+  <si>
+    <t>winBoostToolTip</t>
+  </si>
+  <si>
+    <t>winBoostValueNG</t>
+  </si>
+  <si>
+    <t>Win Boost (3%): N</t>
+  </si>
+  <si>
+    <t>winBoostValueGHS</t>
+  </si>
+  <si>
+    <t>Win Boost (3%): GHS</t>
+  </si>
+  <si>
+    <t>winBoostValueTZ</t>
+  </si>
+  <si>
+    <t>Win Boost (3%): TSh</t>
+  </si>
+  <si>
+    <t>winBoostValueMZ</t>
+  </si>
+  <si>
+    <t>Win Boost (2%): MT</t>
+  </si>
+  <si>
+    <t>winBoostValueZM</t>
+  </si>
+  <si>
+    <t>Win Boost (3%): K</t>
+  </si>
+  <si>
+    <t>winBoostValueMW</t>
+  </si>
+  <si>
+    <t>Win Boost (2%): MK</t>
+  </si>
+  <si>
+    <t>winBoostValueBW</t>
+  </si>
+  <si>
+    <t>Win Boost (2%): BWP</t>
+  </si>
+  <si>
+    <t>winBoostValue</t>
+  </si>
+  <si>
+    <t>Win Boost (2%): R</t>
+  </si>
+  <si>
+    <t>betSaverText</t>
+  </si>
+  <si>
+    <t>totalBetwayReturnMulti</t>
+  </si>
+  <si>
+    <t>Total Betway Return</t>
+  </si>
+  <si>
+    <t>totalBetwayReturnSingle</t>
+  </si>
+  <si>
+    <t>Total Betway Return:</t>
+  </si>
+  <si>
+    <t>potentialReturnSingle</t>
+  </si>
+  <si>
+    <t>Potential Return:</t>
+  </si>
+  <si>
+    <t>potentialReturnMulti</t>
+  </si>
+  <si>
+    <t>soccerLink</t>
+  </si>
+  <si>
+    <t>Soccer</t>
+  </si>
+  <si>
+    <t>firstMatchOdds</t>
+  </si>
+  <si>
+    <t>[data-testid="market-odd-button"]</t>
+  </si>
+  <si>
+    <t>secondMatchOdds</t>
+  </si>
+  <si>
+    <t>thirdMatchOdds</t>
+  </si>
+  <si>
+    <t>betslipContainer</t>
+  </si>
+  <si>
+    <t>emptyBetslipMessage</t>
+  </si>
+  <si>
+    <t>No selected bets</t>
+  </si>
+  <si>
+    <t>betslipCloseBtn</t>
+  </si>
+  <si>
+    <t>#betslip-close-btn</t>
+  </si>
+  <si>
+    <t>multiTabInactive</t>
+  </si>
+  <si>
+    <t>#betslip-multi-tab.inactive</t>
+  </si>
+  <si>
+    <t>totalOdds</t>
+  </si>
+  <si>
+    <t>.total-odds</t>
+  </si>
+  <si>
+    <t>totalStake</t>
+  </si>
+  <si>
+    <t>.total-stake</t>
+  </si>
+  <si>
+    <t>SignUpPage</t>
+  </si>
+  <si>
+    <t>{"name":"MobileNumber"}</t>
+  </si>
+  <si>
+    <t>firstNameInput</t>
+  </si>
+  <si>
+    <t>{"name":"First Name"}</t>
+  </si>
+  <si>
+    <t>lastNameInput</t>
+  </si>
+  <si>
+    <t>{"name":"Surname"}</t>
+  </si>
+  <si>
+    <t>emailInput</t>
+  </si>
+  <si>
+    <t>{"name":"Email"}</t>
+  </si>
+  <si>
+    <t>nextButton</t>
+  </si>
+  <si>
+    <t>{"name":"Next"}</t>
+  </si>
+  <si>
+    <t>previousButton</t>
+  </si>
+  <si>
+    <t>{"name":"Previous"}</t>
+  </si>
+  <si>
+    <t>registerButton</t>
+  </si>
+  <si>
+    <t>{"name":"Register"}</t>
+  </si>
+  <si>
+    <t>hamburgerSignupBtn</t>
+  </si>
+  <si>
+    <t>idDropdownBase</t>
+  </si>
+  <si>
     <t>combobox</t>
   </si>
   <si>
-    <t>{"name":"Date"}</t>
-  </si>
-  <si>
-    <t>previousMonthBtn</t>
-  </si>
-  <si>
-    <t>{"name":"Previous Month"}</t>
-  </si>
-  <si>
-    <t>dateOkBtn</t>
-  </si>
-  <si>
-    <t>{"name":"Ok","exact":true}</t>
-  </si>
-  <si>
-    <t>dateClearBtn</t>
-  </si>
-  <si>
-    <t>{"name":"Clear"}</t>
-  </si>
-  <si>
-    <t>dateDialog</t>
-  </si>
-  <si>
-    <t>dialog</t>
-  </si>
-  <si>
-    <t>{"name":"Choose Date"}</t>
-  </si>
-  <si>
-    <t>exportBtn</t>
-  </si>
-  <si>
-    <t>#transaction-history-export-btn</t>
-  </si>
-  <si>
-    <t>transactionIDButton</t>
-  </si>
-  <si>
-    <t>span.underline.cursor-pointer</t>
-  </si>
-  <si>
-    <t>transactionDetailView</t>
-  </si>
-  <si>
-    <t>svg.w-6.h-6.cursor-pointer.fill-dark-600</t>
-  </si>
-  <si>
-    <t>{"name":"Back"}</t>
-  </si>
-  <si>
-    <t>betslipBackButton</t>
-  </si>
-  <si>
-    <t>#detail-view-back-btn</t>
-  </si>
-  <si>
-    <t>prevPageButton</t>
-  </si>
-  <si>
-    <t>#transaction-history-prev</t>
-  </si>
-  <si>
-    <t>nextPageButton</t>
-  </si>
-  <si>
-    <t>multipleBetsButton</t>
-  </si>
-  <si>
-    <t>BetslipPage</t>
-  </si>
-  <si>
-    <t>usernameInput</t>
-  </si>
-  <si>
-    <t>#header-username</t>
-  </si>
-  <si>
-    <t>#header-password</t>
-  </si>
-  <si>
-    <t>img[alt="Sport"]</t>
-  </si>
-  <si>
-    <t>betslipButton</t>
-  </si>
-  <si>
-    <t>Betslip 0</t>
-  </si>
-  <si>
-    <t>betslipCount</t>
-  </si>
-  <si>
-    <t>[data-testid="betslip-count"]</t>
-  </si>
-  <si>
-    <t>singleTab</t>
-  </si>
-  <si>
-    <t>multiTab</t>
-  </si>
-  <si>
-    <t>bookingCodeInput</t>
-  </si>
-  <si>
-    <t>settingsButton</t>
-  </si>
-  <si>
-    <t>#betslip-setting-btn</t>
-  </si>
-  <si>
-    <t>warningText</t>
-  </si>
-  <si>
-    <t>No selected betsYou don't</t>
-  </si>
-  <si>
-    <t>loadButton</t>
-  </si>
-  <si>
-    <t>{"name":"load"}</t>
-  </si>
-  <si>
-    <t>settingsText</t>
-  </si>
-  <si>
-    <t>Betslip Settings</t>
-  </si>
-  <si>
-    <t>acceptOddsToggleLabel</t>
-  </si>
-  <si>
-    <t>Accept all odds &amp; line changes</t>
-  </si>
-  <si>
-    <t>acceptOddsToggle</t>
-  </si>
-  <si>
-    <t>#settings-accept-odds-toggle</t>
-  </si>
-  <si>
-    <t>keepBetsToggleLabel</t>
-  </si>
-  <si>
-    <t>Keep bets in betslip</t>
-  </si>
-  <si>
-    <t>keepBetsToggle</t>
-  </si>
-  <si>
-    <t>#settings-keep-bets-in-betslip-toggle</t>
-  </si>
-  <si>
-    <t>continueButton</t>
-  </si>
-  <si>
-    <t>#settings-continue-btn</t>
-  </si>
-  <si>
-    <t>closeIcon</t>
-  </si>
-  <si>
-    <t>simpleViewToggle</t>
-  </si>
-  <si>
-    <t>#simple-view-toggle</t>
-  </si>
-  <si>
-    <t>deleteIcon</t>
-  </si>
-  <si>
-    <t>selectAllCheckbox</t>
-  </si>
-  <si>
-    <t>#betslip-select-all</t>
-  </si>
-  <si>
-    <t>removeLegIcon</t>
-  </si>
-  <si>
-    <t>#remove-event-betslip</t>
-  </si>
-  <si>
-    <t>loginBtnBetslip</t>
-  </si>
-  <si>
-    <t>betNowBtn</t>
-  </si>
-  <si>
-    <t>shareBtn</t>
-  </si>
-  <si>
-    <t>cashBtnSingle</t>
-  </si>
-  <si>
-    <t>#single-cash-tab</t>
-  </si>
-  <si>
-    <t>freebetBtnSingle</t>
-  </si>
-  <si>
-    <t>#single-free-tab</t>
-  </si>
-  <si>
-    <t>cashBtnMulti</t>
-  </si>
-  <si>
-    <t>#multi-cash-balance-tab</t>
-  </si>
-  <si>
-    <t>freebetBtnMulti</t>
-  </si>
-  <si>
-    <t>#multi-freebet-tab</t>
-  </si>
-  <si>
-    <t>cashOutIcon</t>
-  </si>
-  <si>
-    <t>.w-4.h-4.fill-primary-300 &gt; path</t>
-  </si>
-  <si>
-    <t>winBoostToolTipTZ</t>
-  </si>
-  <si>
-    <t>Win Boost 3%. 1 more for 5% (Min odds 1.2)</t>
-  </si>
-  <si>
-    <t>winBoostToolTipNG</t>
-  </si>
-  <si>
-    <t>winBoostToolTipMZ</t>
-  </si>
-  <si>
-    <t>Win Boost 2%. 1 more for 3% (Min odds 1.2)</t>
-  </si>
-  <si>
-    <t>winBoostToolTipGHS</t>
-  </si>
-  <si>
-    <t>winBoostToolTipZM</t>
-  </si>
-  <si>
-    <t>winBoostToolTipMW</t>
-  </si>
-  <si>
-    <t>winBoostToolTipBW</t>
-  </si>
-  <si>
-    <t>winBoostToolTip</t>
-  </si>
-  <si>
-    <t>winBoostValueNG</t>
-  </si>
-  <si>
-    <t>Win Boost (3%): N</t>
-  </si>
-  <si>
-    <t>winBoostValueGHS</t>
-  </si>
-  <si>
-    <t>Win Boost (3%): GHS</t>
-  </si>
-  <si>
-    <t>winBoostValueTZ</t>
-  </si>
-  <si>
-    <t>Win Boost (3%): TSh</t>
-  </si>
-  <si>
-    <t>winBoostValueMZ</t>
-  </si>
-  <si>
-    <t>Win Boost (2%): MT</t>
-  </si>
-  <si>
-    <t>winBoostValueZM</t>
-  </si>
-  <si>
-    <t>Win Boost (3%): K</t>
-  </si>
-  <si>
-    <t>winBoostValueMW</t>
-  </si>
-  <si>
-    <t>Win Boost (2%): MK</t>
-  </si>
-  <si>
-    <t>winBoostValueBW</t>
-  </si>
-  <si>
-    <t>Win Boost (2%): BWP</t>
-  </si>
-  <si>
-    <t>winBoostValue</t>
-  </si>
-  <si>
-    <t>Win Boost (2%): R</t>
-  </si>
-  <si>
-    <t>betSaverText</t>
-  </si>
-  <si>
-    <t>totalBetwayReturnMulti</t>
-  </si>
-  <si>
-    <t>Total Betway Return</t>
-  </si>
-  <si>
-    <t>totalBetwayReturnSingle</t>
-  </si>
-  <si>
-    <t>Total Betway Return:</t>
-  </si>
-  <si>
-    <t>potentialReturnSingle</t>
-  </si>
-  <si>
-    <t>Potential Return:</t>
-  </si>
-  <si>
-    <t>potentialReturnMulti</t>
-  </si>
-  <si>
-    <t>soccerLink</t>
-  </si>
-  <si>
-    <t>Soccer</t>
-  </si>
-  <si>
-    <t>firstMatchOdds</t>
-  </si>
-  <si>
-    <t>[data-testid="market-odd-button"]</t>
-  </si>
-  <si>
-    <t>secondMatchOdds</t>
-  </si>
-  <si>
-    <t>thirdMatchOdds</t>
-  </si>
-  <si>
-    <t>betslipContainer</t>
-  </si>
-  <si>
-    <t>emptyBetslipMessage</t>
-  </si>
-  <si>
-    <t>No selected bets</t>
-  </si>
-  <si>
-    <t>betslipCloseBtn</t>
-  </si>
-  <si>
-    <t>#betslip-close-btn</t>
-  </si>
-  <si>
-    <t>multiTabInactive</t>
-  </si>
-  <si>
-    <t>#betslip-multi-tab.inactive</t>
-  </si>
-  <si>
-    <t>totalOdds</t>
-  </si>
-  <si>
-    <t>.total-odds</t>
-  </si>
-  <si>
-    <t>totalStake</t>
-  </si>
-  <si>
-    <t>.total-stake</t>
-  </si>
-  <si>
-    <t>SignUpPage</t>
-  </si>
-  <si>
-    <t>{"name":"MobileNumber"}</t>
-  </si>
-  <si>
-    <t>firstNameInput</t>
-  </si>
-  <si>
-    <t>{"name":"First Name"}</t>
-  </si>
-  <si>
-    <t>lastNameInput</t>
-  </si>
-  <si>
-    <t>{"name":"Surname"}</t>
-  </si>
-  <si>
-    <t>emailInput</t>
-  </si>
-  <si>
-    <t>{"name":"Email"}</t>
-  </si>
-  <si>
-    <t>nextButton</t>
-  </si>
-  <si>
-    <t>{"name":"Next"}</t>
-  </si>
-  <si>
-    <t>previousButton</t>
-  </si>
-  <si>
-    <t>{"name":"Previous"}</t>
-  </si>
-  <si>
-    <t>registerButton</t>
-  </si>
-  <si>
-    <t>{"name":"Register"}</t>
-  </si>
-  <si>
-    <t>hamburgerSignupBtn</t>
-  </si>
-  <si>
-    <t>idDropdownBase</t>
-  </si>
-  <si>
     <t>{"name":"South African ID"}</t>
   </si>
   <si>
@@ -2002,15 +2002,15 @@
     <t>bettingRules</t>
   </si>
   <si>
+    <t xml:space="preserve"> Betting Rules</t>
+  </si>
+  <si>
     <t>bettingRulesZM</t>
   </si>
   <si>
     <t>bettingRulesMZ</t>
   </si>
   <si>
-    <t xml:space="preserve"> Betting Rules</t>
-  </si>
-  <si>
     <t>bettingRulesTips</t>
   </si>
   <si>
@@ -2027,9 +2027,6 @@
   </si>
   <si>
     <t>Betway Scores App</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>howTo</t>
@@ -2635,12 +2632,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1b1c1d"/>
@@ -2657,6 +2648,12 @@
       <sz val="11"/>
       <color rgb="FF1b1c1d"/>
       <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -2735,7 +2732,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="46">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2812,11 +2809,11 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2824,31 +2821,19 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="15" applyFont="1" fillId="0" applyAlignment="1">
@@ -3213,16 +3198,16 @@
       <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="43" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>804</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>805</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>8</v>
@@ -3231,7 +3216,7 @@
         <v>30</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="F2" s="8">
         <v>1</v>
@@ -3239,10 +3224,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>8</v>
@@ -3251,22 +3236,22 @@
         <v>30</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F3" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>23</v>
@@ -3275,10 +3260,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>8</v>
@@ -3287,16 +3272,16 @@
         <v>30</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F5" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>8</v>
@@ -3305,16 +3290,16 @@
         <v>30</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F6" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>8</v>
@@ -3323,22 +3308,22 @@
         <v>30</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F7" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>23</v>
@@ -3347,16 +3332,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>23</v>
@@ -3365,16 +3350,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>23</v>
@@ -3383,10 +3368,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>8</v>
@@ -3395,22 +3380,22 @@
         <v>30</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F11" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>824</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>825</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>826</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>23</v>
@@ -3419,16 +3404,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>23</v>
@@ -3437,16 +3422,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>828</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>829</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>23</v>
@@ -3455,16 +3440,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>23</v>
@@ -3473,16 +3458,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>23</v>
@@ -3491,16 +3476,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>23</v>
@@ -3509,16 +3494,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>836</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>837</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>23</v>
@@ -3527,16 +3512,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="45" t="s">
         <v>838</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="49" t="s">
-        <v>839</v>
       </c>
       <c r="E19" s="25" t="s">
         <v>23</v>
@@ -3545,10 +3530,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>8</v>
@@ -3557,7 +3542,7 @@
         <v>30</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="F20" s="8"/>
     </row>
@@ -4319,820 +4304,820 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="28" t="s">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="27" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="28" t="s">
         <v>481</v>
       </c>
-      <c r="B2" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="31" t="s">
+      <c r="F2" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E3" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B4" s="28" t="s">
         <v>482</v>
       </c>
-      <c r="F2" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B3" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="31" t="s">
+      <c r="C4" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="F3" s="32">
+      <c r="E4" s="28" t="s">
+        <v>483</v>
+      </c>
+      <c r="F4" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>485</v>
+      </c>
+      <c r="F5" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>486</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>487</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>488</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>489</v>
+      </c>
+      <c r="F9" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>490</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>491</v>
+      </c>
+      <c r="F10" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>492</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>493</v>
+      </c>
+      <c r="F11" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>494</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="F13" s="30">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>483</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="31" t="s">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>495</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>496</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>497</v>
+      </c>
+      <c r="F14" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>498</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>499</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>497</v>
+      </c>
+      <c r="F15" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>500</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>501</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>502</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="30" t="s">
-        <v>484</v>
-      </c>
-      <c r="F4" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>485</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="31" t="s">
+      <c r="E17" s="28" t="s">
+        <v>497</v>
+      </c>
+      <c r="F17" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>503</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="30" t="s">
-        <v>486</v>
-      </c>
-      <c r="F5" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>487</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="31" t="s">
+      <c r="E18" s="28" t="s">
+        <v>504</v>
+      </c>
+      <c r="F18" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="29" t="s">
+        <v>496</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="F19" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>507</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>508</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>509</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="30" t="s">
-        <v>488</v>
-      </c>
-      <c r="F6" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="F8" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>489</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>490</v>
-      </c>
-      <c r="F9" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>491</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>492</v>
-      </c>
-      <c r="F10" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>493</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>494</v>
-      </c>
-      <c r="F11" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>495</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="F13" s="32">
+      <c r="E21" s="28" t="s">
+        <v>510</v>
+      </c>
+      <c r="F21" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>511</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>512</v>
+      </c>
+      <c r="F22" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" s="29" t="s">
+        <v>514</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="F23" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>516</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="29">
+        <v>27</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="30">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>496</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>355</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>497</v>
-      </c>
-      <c r="F14" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>498</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>499</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>497</v>
-      </c>
-      <c r="F15" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>500</v>
-      </c>
-      <c r="C16" s="30" t="s">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="29" t="s">
+        <v>518</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>519</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>520</v>
+      </c>
+      <c r="F26" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>521</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>522</v>
+      </c>
+      <c r="F27" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>417</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="30"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>418</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" s="30"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="29" t="s">
+        <v>420</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" s="30"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>421</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="29" t="s">
+        <v>422</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" s="30"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>423</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="29" t="s">
+        <v>424</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" s="30"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>425</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="29" t="s">
+        <v>426</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="30"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+      <c r="A34" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>427</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>428</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" s="30"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+      <c r="A35" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>438</v>
+      </c>
+      <c r="C35" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="31" t="s">
-        <v>501</v>
-      </c>
-      <c r="E16" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B17" s="30" t="s">
-        <v>502</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="30" t="s">
-        <v>497</v>
-      </c>
-      <c r="F17" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B18" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>504</v>
-      </c>
-      <c r="F18" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B19" s="30" t="s">
-        <v>505</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>355</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>506</v>
-      </c>
-      <c r="F19" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B20" s="30" t="s">
-        <v>507</v>
-      </c>
-      <c r="C20" s="30" t="s">
+      <c r="D35" s="29" t="s">
+        <v>523</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" s="30"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+      <c r="A36" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>453</v>
+      </c>
+      <c r="C36" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="31" t="s">
-        <v>508</v>
-      </c>
-      <c r="E20" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B21" s="30" t="s">
-        <v>509</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="30" t="s">
-        <v>510</v>
-      </c>
-      <c r="F21" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B22" s="30" t="s">
-        <v>511</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="30" t="s">
-        <v>512</v>
-      </c>
-      <c r="F22" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>513</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="D23" s="31" t="s">
-        <v>514</v>
-      </c>
-      <c r="E23" s="30" t="s">
-        <v>515</v>
-      </c>
-      <c r="F23" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>516</v>
-      </c>
-      <c r="C24" s="30" t="s">
+      <c r="D36" s="29" t="s">
+        <v>524</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" s="30"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+      <c r="A37" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>525</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="29" t="s">
+        <v>526</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>527</v>
+      </c>
+      <c r="F37" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+      <c r="A38" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>455</v>
+      </c>
+      <c r="C38" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="31">
-        <v>27</v>
-      </c>
-      <c r="E24" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24" s="32">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B25" s="30" t="s">
-        <v>517</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>518</v>
-      </c>
-      <c r="E25" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>519</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="30" t="s">
-        <v>520</v>
-      </c>
-      <c r="F26" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B27" s="30" t="s">
-        <v>521</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="30" t="s">
-        <v>522</v>
-      </c>
-      <c r="F27" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B28" s="30" t="s">
-        <v>418</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" s="32"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B29" s="30" t="s">
-        <v>419</v>
-      </c>
-      <c r="C29" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D29" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="E29" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F29" s="32"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B30" s="30" t="s">
-        <v>420</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" s="31" t="s">
-        <v>421</v>
-      </c>
-      <c r="E30" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30" s="32"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>422</v>
-      </c>
-      <c r="C31" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="31" t="s">
-        <v>423</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" s="32"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B32" s="30" t="s">
-        <v>424</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="31" t="s">
-        <v>425</v>
-      </c>
-      <c r="E32" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F32" s="32"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B33" s="30" t="s">
-        <v>426</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="31" t="s">
-        <v>427</v>
-      </c>
-      <c r="E33" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33" s="32"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B34" s="30" t="s">
-        <v>428</v>
-      </c>
-      <c r="C34" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="31" t="s">
-        <v>429</v>
-      </c>
-      <c r="E34" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34" s="32"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B35" s="30" t="s">
-        <v>439</v>
-      </c>
-      <c r="C35" s="30" t="s">
+      <c r="D38" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38" s="30"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+      <c r="A39" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>456</v>
+      </c>
+      <c r="C39" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="31" t="s">
-        <v>523</v>
-      </c>
-      <c r="E35" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F35" s="32"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B36" s="30" t="s">
-        <v>454</v>
-      </c>
-      <c r="C36" s="30" t="s">
+      <c r="D39" s="29" t="s">
+        <v>457</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+      <c r="A40" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>458</v>
+      </c>
+      <c r="C40" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D36" s="31" t="s">
-        <v>524</v>
-      </c>
-      <c r="E36" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F36" s="32"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B37" s="30" t="s">
-        <v>525</v>
-      </c>
-      <c r="C37" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" s="31" t="s">
-        <v>526</v>
-      </c>
-      <c r="E37" s="30" t="s">
-        <v>527</v>
-      </c>
-      <c r="F37" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B38" s="30" t="s">
-        <v>456</v>
-      </c>
-      <c r="C38" s="30" t="s">
+      <c r="D40" s="29" t="s">
+        <v>459</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+      <c r="A41" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>460</v>
+      </c>
+      <c r="C41" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="E38" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F38" s="32"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B39" s="30" t="s">
-        <v>457</v>
-      </c>
-      <c r="C39" s="30" t="s">
+      <c r="D41" s="29" t="s">
+        <v>461</v>
+      </c>
+      <c r="E41" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41" s="30"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+      <c r="A42" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>462</v>
+      </c>
+      <c r="C42" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="31" t="s">
-        <v>458</v>
-      </c>
-      <c r="E39" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F39" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B40" s="30" t="s">
-        <v>459</v>
-      </c>
-      <c r="C40" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" s="31" t="s">
-        <v>460</v>
-      </c>
-      <c r="E40" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F40" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B41" s="30" t="s">
+      <c r="D42" s="29" t="s">
         <v>461</v>
       </c>
-      <c r="C41" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="D41" s="31" t="s">
-        <v>462</v>
-      </c>
-      <c r="E41" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F41" s="32"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B42" s="30" t="s">
-        <v>463</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="D42" s="31" t="s">
-        <v>462</v>
-      </c>
-      <c r="E42" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F42" s="32"/>
+      <c r="E42" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5175,16 +5160,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="C2" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="17" t="s">
         <v>380</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>381</v>
       </c>
       <c r="E2" s="17" t="s">
         <v>23</v>
@@ -5193,7 +5178,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>165</v>
@@ -5202,7 +5187,7 @@
         <v>21</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>23</v>
@@ -5211,7 +5196,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>271</v>
@@ -5229,7 +5214,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>273</v>
@@ -5247,7 +5232,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>29</v>
@@ -5256,7 +5241,7 @@
         <v>21</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>23</v>
@@ -5265,16 +5250,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>23</v>
@@ -5283,16 +5268,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B8" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>386</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>387</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>23</v>
@@ -5301,10 +5286,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>21</v>
@@ -5319,10 +5304,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>21</v>
@@ -5337,10 +5322,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>8</v>
@@ -5355,16 +5340,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B12" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="17" t="s">
         <v>391</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>392</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>23</v>
@@ -5373,16 +5358,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>23</v>
@@ -5391,10 +5376,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>8</v>
@@ -5403,22 +5388,22 @@
         <v>14</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F14" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>23</v>
@@ -5427,16 +5412,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>23</v>
@@ -5445,16 +5430,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B17" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>401</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>402</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>23</v>
@@ -5463,16 +5448,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>23</v>
@@ -5481,16 +5466,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B19" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>405</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>406</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>23</v>
@@ -5499,16 +5484,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B20" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="17" t="s">
         <v>407</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>408</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>23</v>
@@ -5517,10 +5502,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>21</v>
@@ -5535,16 +5520,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B22" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="17" t="s">
         <v>410</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>411</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>23</v>
@@ -5553,10 +5538,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>21</v>
@@ -5571,16 +5556,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B24" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="17" t="s">
         <v>413</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>414</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>23</v>
@@ -5589,16 +5574,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B25" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="17" t="s">
         <v>415</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>416</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>23</v>
@@ -5607,7 +5592,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B26" s="17" t="s">
         <v>140</v>
@@ -5625,10 +5610,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>21</v>
@@ -5643,10 +5628,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>21</v>
@@ -5661,10 +5646,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>21</v>
@@ -5679,16 +5664,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B30" s="17" t="s">
+        <v>419</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="17" t="s">
         <v>420</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>421</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>23</v>
@@ -5697,16 +5682,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B31" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="17" t="s">
         <v>422</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>423</v>
       </c>
       <c r="E31" s="17" t="s">
         <v>23</v>
@@ -5715,16 +5700,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B32" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="17" t="s">
         <v>424</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>425</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>23</v>
@@ -5733,16 +5718,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B33" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="17" t="s">
         <v>426</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>427</v>
       </c>
       <c r="E33" s="17" t="s">
         <v>23</v>
@@ -5751,16 +5736,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B34" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="17" t="s">
         <v>428</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>429</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>23</v>
@@ -5769,16 +5754,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>23</v>
@@ -5787,16 +5772,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="25" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C36" s="25" t="s">
         <v>68</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E36" s="25" t="s">
         <v>23</v>
@@ -5805,16 +5790,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>23</v>
@@ -5823,16 +5808,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>23</v>
@@ -5841,52 +5826,52 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>23</v>
       </c>
       <c r="F39" s="16"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="B40" s="26" t="s">
-        <v>437</v>
-      </c>
-      <c r="C40" s="26" t="s">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
+      <c r="A40" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>436</v>
+      </c>
+      <c r="C40" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="26" t="s">
-        <v>434</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="F40" s="27"/>
+      <c r="D40" s="25" t="s">
+        <v>433</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>23</v>
@@ -5895,16 +5880,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>23</v>
@@ -5913,16 +5898,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>23</v>
@@ -5931,16 +5916,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>23</v>
@@ -5949,16 +5934,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>23</v>
@@ -5967,16 +5952,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>23</v>
@@ -5985,16 +5970,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>23</v>
@@ -6003,16 +5988,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>23</v>
@@ -6021,16 +6006,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>23</v>
@@ -6039,16 +6024,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C50" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>23</v>
@@ -6057,10 +6042,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>68</v>
@@ -6075,16 +6060,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>23</v>
@@ -6095,16 +6080,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>23</v>
@@ -6115,16 +6100,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E54" s="17" t="s">
         <v>23</v>
@@ -6133,16 +6118,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>23</v>
@@ -6151,16 +6136,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C56" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E56" s="17" t="s">
         <v>23</v>
@@ -6169,16 +6154,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B57" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="C57" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" s="17" t="s">
         <v>466</v>
-      </c>
-      <c r="C57" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D57" s="17" t="s">
-        <v>467</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>23</v>
@@ -6189,16 +6174,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E58" s="17" t="s">
         <v>23</v>
@@ -6209,16 +6194,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C59" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>23</v>
@@ -6229,10 +6214,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C60" s="17" t="s">
         <v>21</v>
@@ -6247,16 +6232,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>23</v>
@@ -6265,16 +6250,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="25" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B62" s="25" t="s">
+        <v>472</v>
+      </c>
+      <c r="C62" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="25" t="s">
         <v>473</v>
-      </c>
-      <c r="C62" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>474</v>
       </c>
       <c r="E62" s="25" t="s">
         <v>23</v>
@@ -6283,16 +6268,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="25" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B63" s="25" t="s">
+        <v>474</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="25" t="s">
         <v>475</v>
-      </c>
-      <c r="C63" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D63" s="25" t="s">
-        <v>476</v>
       </c>
       <c r="E63" s="25" t="s">
         <v>23</v>
@@ -6301,16 +6286,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="25" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B64" s="25" t="s">
+        <v>476</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" s="25" t="s">
         <v>477</v>
-      </c>
-      <c r="C64" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D64" s="25" t="s">
-        <v>478</v>
       </c>
       <c r="E64" s="25" t="s">
         <v>23</v>
@@ -6319,16 +6304,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="25" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B65" s="25" t="s">
+        <v>478</v>
+      </c>
+      <c r="C65" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D65" s="25" t="s">
         <v>479</v>
-      </c>
-      <c r="C65" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D65" s="25" t="s">
-        <v>480</v>
       </c>
       <c r="E65" s="25" t="s">
         <v>23</v>
@@ -6698,13 +6683,13 @@
         <v>354</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>355</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>356</v>
+        <v>23</v>
       </c>
       <c r="F19" s="15">
         <v>0</v>
@@ -6715,7 +6700,7 @@
         <v>328</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C20" s="14" t="s">
         <v>8</v>
@@ -6724,7 +6709,7 @@
         <v>14</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F20" s="15">
         <v>0</v>
@@ -6735,7 +6720,7 @@
         <v>328</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>8</v>
@@ -6744,7 +6729,7 @@
         <v>30</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F21" s="15">
         <v>0</v>
@@ -6755,7 +6740,7 @@
         <v>328</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C22" s="14" t="s">
         <v>8</v>
@@ -6764,7 +6749,7 @@
         <v>30</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F22" s="15">
         <v>0</v>
@@ -6775,16 +6760,16 @@
         <v>328</v>
       </c>
       <c r="B23" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="14" t="s">
+      <c r="E23" s="14" t="s">
         <v>364</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>365</v>
       </c>
       <c r="F23" s="15">
         <v>0</v>
@@ -6795,13 +6780,13 @@
         <v>328</v>
       </c>
       <c r="B24" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="14" t="s">
         <v>366</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>367</v>
       </c>
       <c r="E24" s="14" t="s">
         <v>23</v>
@@ -6813,13 +6798,13 @@
         <v>328</v>
       </c>
       <c r="B25" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="14" t="s">
         <v>368</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>369</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>23</v>
@@ -6833,13 +6818,13 @@
         <v>328</v>
       </c>
       <c r="B26" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="14" t="s">
         <v>370</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>371</v>
       </c>
       <c r="E26" s="14" t="s">
         <v>23</v>
@@ -6862,7 +6847,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F27" s="15"/>
     </row>
@@ -6871,13 +6856,13 @@
         <v>328</v>
       </c>
       <c r="B28" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="14" t="s">
         <v>373</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>374</v>
       </c>
       <c r="E28" s="14" t="s">
         <v>23</v>
@@ -6911,13 +6896,13 @@
         <v>328</v>
       </c>
       <c r="B30" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="14" t="s">
         <v>375</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>376</v>
       </c>
       <c r="E30" s="14" t="s">
         <v>23</v>
@@ -6929,7 +6914,7 @@
         <v>328</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>21</v>
@@ -7005,7 +6990,7 @@
         <v>328</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>21</v>
@@ -10958,13 +10943,13 @@
       <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="43" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>176</v>
@@ -10984,7 +10969,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>187</v>
@@ -10996,7 +10981,7 @@
         <v>30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="F3" s="8">
         <v>0</v>
@@ -11004,7 +10989,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>189</v>
@@ -11024,7 +11009,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>191</v>
@@ -11044,7 +11029,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>193</v>
@@ -11064,7 +11049,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>195</v>
@@ -11084,7 +11069,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>197</v>
@@ -11096,7 +11081,7 @@
         <v>30</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F8" s="8">
         <v>0</v>
@@ -11104,7 +11089,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>199</v>
@@ -11116,7 +11101,7 @@
         <v>30</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F9" s="8">
         <v>0</v>
@@ -11124,7 +11109,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>201</v>
@@ -11136,7 +11121,7 @@
         <v>30</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="F10" s="8">
         <v>0</v>
@@ -11144,7 +11129,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>203</v>
@@ -11156,7 +11141,7 @@
         <v>30</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
@@ -11164,7 +11149,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>205</v>
@@ -11176,7 +11161,7 @@
         <v>30</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="F12" s="8">
         <v>0</v>
@@ -11184,7 +11169,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>207</v>
@@ -11196,7 +11181,7 @@
         <v>30</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F13" s="8">
         <v>0</v>
@@ -11204,7 +11189,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>209</v>
@@ -11224,7 +11209,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>211</v>
@@ -11236,7 +11221,7 @@
         <v>30</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
@@ -11244,7 +11229,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>213</v>
@@ -11256,7 +11241,7 @@
         <v>30</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F16" s="8">
         <v>0</v>
@@ -11264,7 +11249,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>215</v>
@@ -11276,7 +11261,7 @@
         <v>30</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F17" s="8">
         <v>0</v>
@@ -11284,7 +11269,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>217</v>
@@ -11304,16 +11289,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>23</v>
@@ -11324,7 +11309,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>220</v>
@@ -11344,7 +11329,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>221</v>
@@ -11364,7 +11349,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>32</v>
@@ -11384,7 +11369,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>223</v>
@@ -11404,7 +11389,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>225</v>
@@ -11424,7 +11409,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>227</v>
@@ -11444,7 +11429,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>229</v>
@@ -11541,7 +11526,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>23</v>
@@ -11589,13 +11574,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="14" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>23</v>
@@ -11606,13 +11591,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="14" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>23</v>
@@ -11621,13 +11606,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="14" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>23</v>
@@ -11636,13 +11621,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="14" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>23</v>
@@ -11651,13 +11636,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="14" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>23</v>
@@ -11672,7 +11657,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>23</v>
@@ -11681,13 +11666,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>784</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>785</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>23</v>
@@ -11696,13 +11681,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="44" t="s">
         <v>786</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>787</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>23</v>
@@ -11711,13 +11696,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>23</v>
@@ -11726,7 +11711,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>8</v>
@@ -11735,7 +11720,7 @@
         <v>14</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E11" s="8"/>
     </row>
@@ -11772,7 +11757,7 @@
       <c r="D1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="43" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11804,7 +11789,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E3" s="15">
         <v>0</v>
@@ -12455,274 +12440,274 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="40" t="s">
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="37" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="38" t="s">
+        <v>747</v>
+      </c>
+      <c r="B2" s="39" t="s">
         <v>748</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="C2" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="39" t="s">
         <v>749</v>
       </c>
-      <c r="C2" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="43" t="s">
+      <c r="F2" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="38" t="s">
+        <v>747</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>750</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="43" t="s">
-        <v>750</v>
-      </c>
-      <c r="F2" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="42" t="s">
-        <v>748</v>
-      </c>
-      <c r="B3" s="43" t="s">
+      <c r="E3" s="39" t="s">
         <v>751</v>
       </c>
-      <c r="C3" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="43" t="s">
+      <c r="F3" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="38" t="s">
+        <v>747</v>
+      </c>
+      <c r="B4" s="39" t="s">
         <v>752</v>
       </c>
-      <c r="F3" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="42" t="s">
-        <v>748</v>
-      </c>
-      <c r="B4" s="43" t="s">
+      <c r="C4" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="39" t="s">
         <v>753</v>
       </c>
-      <c r="C4" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="43" t="s">
+      <c r="E4" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="41"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="38" t="s">
+        <v>747</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="E4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="45"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="42" t="s">
-        <v>748</v>
-      </c>
-      <c r="B5" s="43" t="s">
+      <c r="C5" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="39" t="s">
         <v>755</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="E5" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="38" t="s">
+        <v>747</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>756</v>
+      </c>
+      <c r="C6" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="43" t="s">
-        <v>756</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="42" t="s">
-        <v>748</v>
-      </c>
-      <c r="B6" s="43" t="s">
+      <c r="D6" s="39" t="s">
         <v>757</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="E6" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="38" t="s">
+        <v>747</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>758</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>759</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="41"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="38" t="s">
+        <v>747</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>760</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>761</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="41"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="38" t="s">
+        <v>747</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>762</v>
+      </c>
+      <c r="C9" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="43" t="s">
-        <v>758</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="42" t="s">
-        <v>748</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>759</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>760</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="45"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="42" t="s">
-        <v>748</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>761</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>762</v>
-      </c>
-      <c r="E8" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="45"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="42" t="s">
-        <v>748</v>
-      </c>
-      <c r="B9" s="43" t="s">
+      <c r="D9" s="39" t="s">
         <v>763</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="E9" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="38" t="s">
+        <v>747</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>764</v>
+      </c>
+      <c r="C10" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="43" t="s">
-        <v>764</v>
-      </c>
-      <c r="E9" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="42" t="s">
-        <v>748</v>
-      </c>
-      <c r="B10" s="43" t="s">
+      <c r="D10" s="39" t="s">
         <v>765</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="E10" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="38" t="s">
+        <v>747</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>488</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>766</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>489</v>
+      </c>
+      <c r="F11" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="38" t="s">
+        <v>747</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>490</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>766</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>491</v>
+      </c>
+      <c r="F12" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="38" t="s">
+        <v>747</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>767</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>768</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="41"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="38" t="s">
+        <v>747</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>769</v>
+      </c>
+      <c r="C14" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="43" t="s">
-        <v>766</v>
-      </c>
-      <c r="E10" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="42" t="s">
-        <v>748</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>489</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="E11" s="43" t="s">
-        <v>490</v>
-      </c>
-      <c r="F11" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="42" t="s">
-        <v>748</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>491</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="43" t="s">
-        <v>767</v>
-      </c>
-      <c r="E12" s="43" t="s">
-        <v>492</v>
-      </c>
-      <c r="F12" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="42" t="s">
-        <v>748</v>
-      </c>
-      <c r="B13" s="43" t="s">
-        <v>768</v>
-      </c>
-      <c r="C13" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="43" t="s">
-        <v>769</v>
-      </c>
-      <c r="E13" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="45"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="42" t="s">
-        <v>748</v>
-      </c>
-      <c r="B14" s="42" t="s">
+      <c r="D14" s="38" t="s">
         <v>770</v>
       </c>
-      <c r="C14" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="42" t="s">
-        <v>771</v>
-      </c>
-      <c r="E14" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="46">
+      <c r="E14" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="42">
         <v>0</v>
       </c>
     </row>
@@ -12777,7 +12762,7 @@
       <c r="C2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="32" t="s">
         <v>30</v>
       </c>
       <c r="E2" s="17" t="s">
@@ -12797,7 +12782,7 @@
       <c r="C3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="32" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="17" t="s">
@@ -12815,7 +12800,7 @@
       <c r="C4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="32" t="s">
         <v>272</v>
       </c>
       <c r="E4" s="17" t="s">
@@ -12833,7 +12818,7 @@
       <c r="C5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="32" t="s">
         <v>77</v>
       </c>
       <c r="E5" s="17" t="s">
@@ -12853,7 +12838,7 @@
       <c r="C6" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="32" t="s">
         <v>106</v>
       </c>
       <c r="E6" s="17" t="s">
@@ -12871,7 +12856,7 @@
       <c r="C7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="32" t="s">
         <v>169</v>
       </c>
       <c r="E7" s="17" t="s">
@@ -12889,7 +12874,7 @@
       <c r="C8" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="32" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="17" t="s">
@@ -12909,7 +12894,7 @@
       <c r="C9" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="32" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="17" t="s">
@@ -12929,7 +12914,7 @@
       <c r="C10" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="D10" s="32" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="17" t="s">
@@ -12947,7 +12932,7 @@
       <c r="C11" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="32" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="17" t="s">
@@ -12967,7 +12952,7 @@
       <c r="C12" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="32" t="s">
         <v>648</v>
       </c>
       <c r="E12" s="17" t="s">
@@ -12985,7 +12970,7 @@
       <c r="C13" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="32" t="s">
         <v>650</v>
       </c>
       <c r="E13" s="17" t="s">
@@ -13005,7 +12990,7 @@
       <c r="C14" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="32" t="s">
         <v>652</v>
       </c>
       <c r="E14" s="17" t="s">
@@ -13025,7 +13010,7 @@
       <c r="C15" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="32" t="s">
         <v>654</v>
       </c>
       <c r="E15" s="17" t="s">
@@ -13043,8 +13028,8 @@
       <c r="C16" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="34" t="s">
-        <v>654</v>
+      <c r="D16" s="32" t="s">
+        <v>656</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>23</v>
@@ -13056,12 +13041,12 @@
         <v>643</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="34" t="s">
+      <c r="D17" s="32" t="s">
         <v>654</v>
       </c>
       <c r="E17" s="17" t="s">
@@ -13074,13 +13059,13 @@
         <v>643</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="34" t="s">
-        <v>658</v>
+      <c r="D18" s="32" t="s">
+        <v>656</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>23</v>
@@ -13099,7 +13084,7 @@
       <c r="C19" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="D19" s="32" t="s">
         <v>660</v>
       </c>
       <c r="E19" s="17" t="s">
@@ -13111,68 +13096,64 @@
       <c r="A20" s="17" t="s">
         <v>643</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="33" t="s">
         <v>661</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="D20" s="34" t="s">
         <v>662</v>
       </c>
-      <c r="E20" s="35"/>
-      <c r="F20" s="36"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="34"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="17" t="s">
         <v>643</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="33" t="s">
         <v>663</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="34" t="s">
         <v>664</v>
       </c>
-      <c r="E21" s="37" t="s">
-        <v>665</v>
-      </c>
-      <c r="F21" s="36"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="34"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D22" s="34" t="s">
-        <v>667</v>
+      <c r="D22" s="32" t="s">
+        <v>666</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="18">
-        <v>0</v>
-      </c>
+      <c r="F22" s="18"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="34" t="s">
-        <v>669</v>
+      <c r="D23" s="32" t="s">
+        <v>668</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>23</v>
@@ -13186,13 +13167,13 @@
         <v>643</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="34" t="s">
-        <v>671</v>
+      <c r="D24" s="32" t="s">
+        <v>670</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>23</v>
@@ -13204,7 +13185,7 @@
         <v>643</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>68</v>
@@ -13224,13 +13205,13 @@
         <v>643</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="34" t="s">
-        <v>381</v>
+      <c r="D26" s="32" t="s">
+        <v>380</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>23</v>
@@ -13247,8 +13228,8 @@
       <c r="C27" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="34" t="s">
-        <v>382</v>
+      <c r="D27" s="32" t="s">
+        <v>381</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>23</v>
@@ -13260,13 +13241,13 @@
         <v>643</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="34" t="s">
-        <v>675</v>
+      <c r="D28" s="32" t="s">
+        <v>674</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>23</v>
@@ -13278,33 +13259,31 @@
         <v>643</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="34" t="s">
-        <v>677</v>
+      <c r="D29" s="32" t="s">
+        <v>676</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F29" s="38" t="s">
-        <v>665</v>
-      </c>
+      <c r="F29" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D30" s="34" t="s">
-        <v>385</v>
+      <c r="D30" s="32" t="s">
+        <v>384</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>23</v>
@@ -13316,12 +13295,12 @@
         <v>643</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="34" t="s">
+      <c r="D31" s="32" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="17" t="s">
@@ -13334,16 +13313,16 @@
         <v>643</v>
       </c>
       <c r="B32" s="17" t="s">
+        <v>678</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="17" t="s">
         <v>679</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>680</v>
       </c>
       <c r="F32" s="16">
         <v>1</v>
@@ -13354,16 +13333,16 @@
         <v>643</v>
       </c>
       <c r="B33" s="17" t="s">
+        <v>680</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="17" t="s">
         <v>681</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>682</v>
       </c>
       <c r="F33" s="16"/>
     </row>
@@ -13372,12 +13351,12 @@
         <v>643</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="34" t="s">
+      <c r="D34" s="32" t="s">
         <v>77</v>
       </c>
       <c r="E34" s="17" t="s">
@@ -13392,13 +13371,13 @@
         <v>643</v>
       </c>
       <c r="B35" s="17" t="s">
+        <v>683</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="32" t="s">
         <v>684</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" s="34" t="s">
-        <v>685</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>23</v>
@@ -13410,13 +13389,13 @@
         <v>643</v>
       </c>
       <c r="B36" s="17" t="s">
+        <v>685</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="32" t="s">
         <v>686</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" s="34" t="s">
-        <v>687</v>
       </c>
       <c r="E36" s="17" t="s">
         <v>23</v>
@@ -13428,13 +13407,13 @@
         <v>643</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D37" s="34" t="s">
-        <v>689</v>
+      <c r="D37" s="32" t="s">
+        <v>688</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>23</v>
@@ -13446,13 +13425,13 @@
         <v>643</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="34" t="s">
-        <v>691</v>
+      <c r="D38" s="32" t="s">
+        <v>690</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>23</v>
@@ -13464,13 +13443,13 @@
         <v>643</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="34" t="s">
-        <v>693</v>
+      <c r="D39" s="32" t="s">
+        <v>692</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>23</v>
@@ -13487,7 +13466,7 @@
       <c r="C40" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="34" t="s">
+      <c r="D40" s="32" t="s">
         <v>185</v>
       </c>
       <c r="E40" s="17" t="s">
@@ -13500,13 +13479,13 @@
         <v>643</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="34" t="s">
-        <v>695</v>
+      <c r="D41" s="32" t="s">
+        <v>694</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>23</v>
@@ -13518,13 +13497,13 @@
         <v>643</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D42" s="34" t="s">
-        <v>697</v>
+      <c r="D42" s="32" t="s">
+        <v>696</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>23</v>
@@ -13536,13 +13515,13 @@
         <v>643</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D43" s="34" t="s">
-        <v>699</v>
+      <c r="D43" s="32" t="s">
+        <v>698</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>23</v>
@@ -13556,13 +13535,13 @@
         <v>643</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D44" s="34" t="s">
-        <v>701</v>
+      <c r="D44" s="32" t="s">
+        <v>700</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>23</v>
@@ -13574,13 +13553,13 @@
         <v>643</v>
       </c>
       <c r="B45" s="17" t="s">
+        <v>701</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="32" t="s">
         <v>702</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" s="34" t="s">
-        <v>703</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>23</v>
@@ -13592,13 +13571,13 @@
         <v>643</v>
       </c>
       <c r="B46" s="17" t="s">
+        <v>703</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="32" t="s">
         <v>704</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D46" s="34" t="s">
-        <v>705</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>23</v>
@@ -13610,13 +13589,13 @@
         <v>643</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D47" s="34" t="s">
-        <v>707</v>
+      <c r="D47" s="32" t="s">
+        <v>706</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>23</v>
@@ -13633,7 +13612,7 @@
       <c r="C48" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="34" t="s">
+      <c r="D48" s="32" t="s">
         <v>640</v>
       </c>
       <c r="E48" s="17" t="s">
@@ -13646,12 +13625,12 @@
         <v>643</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="34" t="s">
+      <c r="D49" s="32" t="s">
         <v>77</v>
       </c>
       <c r="E49" s="17" t="s">
@@ -13666,13 +13645,13 @@
         <v>643</v>
       </c>
       <c r="B50" s="17" t="s">
+        <v>708</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="32" t="s">
         <v>709</v>
-      </c>
-      <c r="C50" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D50" s="34" t="s">
-        <v>710</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>23</v>
@@ -13684,13 +13663,13 @@
         <v>643</v>
       </c>
       <c r="B51" s="17" t="s">
+        <v>710</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="32" t="s">
         <v>711</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D51" s="34" t="s">
-        <v>712</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>23</v>
@@ -13704,13 +13683,13 @@
         <v>643</v>
       </c>
       <c r="B52" s="17" t="s">
+        <v>712</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" s="32" t="s">
         <v>713</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D52" s="34" t="s">
-        <v>714</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>23</v>
@@ -13724,13 +13703,13 @@
         <v>643</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="34" t="s">
-        <v>716</v>
+      <c r="D53" s="32" t="s">
+        <v>715</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>162</v>
@@ -13742,31 +13721,31 @@
         <v>643</v>
       </c>
       <c r="B54" s="17" t="s">
+        <v>716</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="32" t="s">
         <v>717</v>
       </c>
-      <c r="C54" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D54" s="34" t="s">
-        <v>718</v>
-      </c>
       <c r="E54" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F54" s="34"/>
+      <c r="F54" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="17" t="s">
         <v>643</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D55" s="34" t="s">
-        <v>720</v>
+      <c r="D55" s="32" t="s">
+        <v>719</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>23</v>
@@ -13778,13 +13757,13 @@
         <v>643</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C56" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D56" s="34" t="s">
-        <v>722</v>
+      <c r="D56" s="32" t="s">
+        <v>721</v>
       </c>
       <c r="E56" s="17" t="s">
         <v>23</v>
@@ -13796,13 +13775,13 @@
         <v>643</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C57" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="34" t="s">
-        <v>724</v>
+      <c r="D57" s="32" t="s">
+        <v>723</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>23</v>
@@ -13814,13 +13793,13 @@
         <v>643</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="34" t="s">
-        <v>722</v>
+      <c r="D58" s="32" t="s">
+        <v>721</v>
       </c>
       <c r="E58" s="17" t="s">
         <v>23</v>
@@ -13832,13 +13811,13 @@
         <v>643</v>
       </c>
       <c r="B59" s="17" t="s">
+        <v>725</v>
+      </c>
+      <c r="C59" s="17" t="s">
         <v>726</v>
       </c>
-      <c r="C59" s="17" t="s">
+      <c r="D59" s="32" t="s">
         <v>727</v>
-      </c>
-      <c r="D59" s="34" t="s">
-        <v>728</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>23</v>
@@ -13850,13 +13829,13 @@
         <v>643</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C60" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D60" s="34" t="s">
-        <v>730</v>
+      <c r="D60" s="32" t="s">
+        <v>729</v>
       </c>
       <c r="E60" s="17" t="s">
         <v>23</v>
@@ -13868,13 +13847,13 @@
         <v>643</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D61" s="34" t="s">
-        <v>730</v>
+      <c r="D61" s="32" t="s">
+        <v>729</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>23</v>
@@ -13888,13 +13867,13 @@
         <v>643</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C62" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D62" s="34" t="s">
-        <v>722</v>
+      <c r="D62" s="32" t="s">
+        <v>721</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>23</v>
@@ -13906,13 +13885,13 @@
         <v>643</v>
       </c>
       <c r="B63" s="17" t="s">
+        <v>732</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>726</v>
+      </c>
+      <c r="D63" s="32" t="s">
         <v>733</v>
-      </c>
-      <c r="C63" s="17" t="s">
-        <v>727</v>
-      </c>
-      <c r="D63" s="34" t="s">
-        <v>734</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>23</v>
@@ -13924,16 +13903,16 @@
         <v>643</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C64" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D64" s="34" t="s">
+      <c r="D64" s="32" t="s">
         <v>14</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F64" s="18">
         <v>1</v>
@@ -13944,13 +13923,13 @@
         <v>643</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C65" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D65" s="34" t="s">
-        <v>737</v>
+      <c r="D65" s="32" t="s">
+        <v>736</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>23</v>
@@ -13962,13 +13941,13 @@
         <v>643</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C66" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D66" s="34" t="s">
-        <v>739</v>
+      <c r="D66" s="32" t="s">
+        <v>738</v>
       </c>
       <c r="E66" s="17" t="s">
         <v>23</v>
@@ -13980,13 +13959,13 @@
         <v>643</v>
       </c>
       <c r="B67" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C67" s="25" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E67" s="25" t="s">
         <v>23</v>
@@ -13998,13 +13977,13 @@
         <v>643</v>
       </c>
       <c r="B68" s="25" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C68" s="25" t="s">
         <v>25</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E68" s="25" t="s">
         <v>23</v>
@@ -14016,13 +13995,13 @@
         <v>643</v>
       </c>
       <c r="B69" s="25" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C69" s="25" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E69" s="25" t="s">
         <v>23</v>
@@ -14034,13 +14013,13 @@
         <v>643</v>
       </c>
       <c r="B70" s="17" t="s">
+        <v>745</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="32" t="s">
         <v>746</v>
-      </c>
-      <c r="C70" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D70" s="34" t="s">
-        <v>747</v>
       </c>
       <c r="E70" s="17" t="s">
         <v>23</v>

--- a/src/global/utils/file-utils/locators(2).xlsx
+++ b/src/global/utils/file-utils/locators(2).xlsx
@@ -2026,19 +2026,19 @@
     <t>betwayScoresApp</t>
   </si>
   <si>
-    <t>Betway Scores App</t>
+    <t xml:space="preserve"> Betway Scores App</t>
   </si>
   <si>
     <t>howTo</t>
   </si>
   <si>
-    <t>How To</t>
+    <t>{"name":"How To","exact":true}</t>
   </si>
   <si>
     <t>statistics</t>
   </si>
   <si>
-    <t>Statistics</t>
+    <t>{"name":"Statistics"}</t>
   </si>
   <si>
     <t>oddsFormat</t>
@@ -2128,7 +2128,7 @@
     <t>responsibleGaming</t>
   </si>
   <si>
-    <t xml:space="preserve"> Responsible Gaming</t>
+    <t>#Responsible\ Gaming-hamburger-menu-btn</t>
   </si>
   <si>
     <t>documentVerification</t>
@@ -2161,7 +2161,7 @@
     <t>hamburgerEyeButton</t>
   </si>
   <si>
-    <t>(.w-6.h-6.cursor-pointer &gt; path').first()</t>
+    <t>div.mr-2 &gt; svg.w-6.h-6.cursor-pointer</t>
   </si>
   <si>
     <t>accountsButtonMZ</t>
@@ -2559,7 +2559,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2651,12 +2651,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2732,7 +2726,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2831,33 +2825,27 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="15" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="15" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="18" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="18" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="18" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
@@ -2866,7 +2854,7 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="19" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="18" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3198,11 +3186,11 @@
       <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="6" t="s">
         <v>803</v>
       </c>
@@ -3222,7 +3210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="6" t="s">
         <v>803</v>
       </c>
@@ -3240,7 +3228,7 @@
       </c>
       <c r="F3" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="6" t="s">
         <v>803</v>
       </c>
@@ -3258,7 +3246,7 @@
       </c>
       <c r="F4" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="6" t="s">
         <v>803</v>
       </c>
@@ -3276,7 +3264,7 @@
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="6" t="s">
         <v>803</v>
       </c>
@@ -3294,7 +3282,7 @@
       </c>
       <c r="F6" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="6" t="s">
         <v>803</v>
       </c>
@@ -3312,7 +3300,7 @@
       </c>
       <c r="F7" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="6" t="s">
         <v>803</v>
       </c>
@@ -3330,7 +3318,7 @@
       </c>
       <c r="F8" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="6" t="s">
         <v>803</v>
       </c>
@@ -3348,7 +3336,7 @@
       </c>
       <c r="F9" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="6" t="s">
         <v>803</v>
       </c>
@@ -3366,7 +3354,7 @@
       </c>
       <c r="F10" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="6" t="s">
         <v>803</v>
       </c>
@@ -3382,9 +3370,11 @@
       <c r="E11" s="25" t="s">
         <v>823</v>
       </c>
-      <c r="F11" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="6" t="s">
         <v>803</v>
       </c>
@@ -3402,7 +3392,7 @@
       </c>
       <c r="F12" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="6" t="s">
         <v>803</v>
       </c>
@@ -3420,7 +3410,7 @@
       </c>
       <c r="F13" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="6" t="s">
         <v>803</v>
       </c>
@@ -3438,7 +3428,7 @@
       </c>
       <c r="F14" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="6" t="s">
         <v>803</v>
       </c>
@@ -3456,7 +3446,7 @@
       </c>
       <c r="F15" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="6" t="s">
         <v>803</v>
       </c>
@@ -3474,7 +3464,7 @@
       </c>
       <c r="F16" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="6" t="s">
         <v>803</v>
       </c>
@@ -3492,7 +3482,7 @@
       </c>
       <c r="F17" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="6" t="s">
         <v>803</v>
       </c>
@@ -3510,7 +3500,7 @@
       </c>
       <c r="F18" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="6" t="s">
         <v>803</v>
       </c>
@@ -3520,7 +3510,7 @@
       <c r="C19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="45" t="s">
+      <c r="D19" s="43" t="s">
         <v>838</v>
       </c>
       <c r="E19" s="25" t="s">
@@ -3528,7 +3518,7 @@
       </c>
       <c r="F19" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="6" t="s">
         <v>803</v>
       </c>
@@ -7234,7 +7224,7 @@
     <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -7254,7 +7244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="6" t="s">
         <v>276</v>
       </c>
@@ -7274,7 +7264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="6" t="s">
         <v>276</v>
       </c>
@@ -7294,7 +7284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="6" t="s">
         <v>276</v>
       </c>
@@ -7314,7 +7304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="6" t="s">
         <v>276</v>
       </c>
@@ -7334,7 +7324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="6" t="s">
         <v>276</v>
       </c>
@@ -7354,7 +7344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="6" t="s">
         <v>276</v>
       </c>
@@ -7374,7 +7364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="6" t="s">
         <v>276</v>
       </c>
@@ -7394,7 +7384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="6" t="s">
         <v>276</v>
       </c>
@@ -7414,7 +7404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="6" t="s">
         <v>276</v>
       </c>
@@ -7434,7 +7424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="6" t="s">
         <v>276</v>
       </c>
@@ -7454,7 +7444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="6" t="s">
         <v>276</v>
       </c>
@@ -7474,7 +7464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="6" t="s">
         <v>276</v>
       </c>
@@ -7494,7 +7484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="6" t="s">
         <v>276</v>
       </c>
@@ -7514,7 +7504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="6" t="s">
         <v>276</v>
       </c>
@@ -7534,7 +7524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="6" t="s">
         <v>276</v>
       </c>
@@ -7554,7 +7544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="6" t="s">
         <v>276</v>
       </c>
@@ -7574,7 +7564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="6" t="s">
         <v>276</v>
       </c>
@@ -7594,7 +7584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="6" t="s">
         <v>276</v>
       </c>
@@ -10943,7 +10933,7 @@
       <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11686,7 +11676,7 @@
       <c r="B9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="42" t="s">
         <v>786</v>
       </c>
       <c r="D9" s="14" t="s">
@@ -11757,7 +11747,7 @@
       <c r="D1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="41" t="s">
         <v>5</v>
       </c>
     </row>
@@ -12440,274 +12430,274 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="36" t="s">
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="35" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="36" t="s">
         <v>747</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="37" t="s">
         <v>748</v>
       </c>
-      <c r="C2" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="39" t="s">
+      <c r="C2" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="37" t="s">
         <v>749</v>
       </c>
-      <c r="F2" s="40">
+      <c r="F2" s="38">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="36" t="s">
         <v>747</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="37" t="s">
         <v>750</v>
       </c>
-      <c r="C3" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="39" t="s">
+      <c r="C3" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="37" t="s">
         <v>751</v>
       </c>
-      <c r="F3" s="40">
+      <c r="F3" s="38">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="36" t="s">
         <v>747</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="37" t="s">
         <v>752</v>
       </c>
-      <c r="C4" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="39" t="s">
+      <c r="C4" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="37" t="s">
         <v>753</v>
       </c>
-      <c r="E4" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="41"/>
+      <c r="E4" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="39"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="36" t="s">
         <v>747</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="37" t="s">
         <v>755</v>
       </c>
-      <c r="E5" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="40">
+      <c r="E5" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="38">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="36" t="s">
         <v>747</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="37" t="s">
         <v>756</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="37" t="s">
         <v>757</v>
       </c>
-      <c r="E6" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="40">
+      <c r="E6" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="38">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="36" t="s">
         <v>747</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="37" t="s">
         <v>758</v>
       </c>
-      <c r="C7" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="39" t="s">
+      <c r="C7" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="37" t="s">
         <v>759</v>
       </c>
-      <c r="E7" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="41"/>
+      <c r="E7" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="39"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="36" t="s">
         <v>747</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="37" t="s">
         <v>760</v>
       </c>
-      <c r="C8" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="39" t="s">
+      <c r="C8" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="37" t="s">
         <v>761</v>
       </c>
-      <c r="E8" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="41"/>
+      <c r="E8" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="39"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="36" t="s">
         <v>747</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="37" t="s">
         <v>762</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="37" t="s">
         <v>763</v>
       </c>
-      <c r="E9" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="40">
+      <c r="E9" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="38">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="36" t="s">
         <v>747</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="37" t="s">
         <v>764</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="37" t="s">
         <v>765</v>
       </c>
-      <c r="E10" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="40">
+      <c r="E10" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="38">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="36" t="s">
         <v>747</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="37" t="s">
         <v>488</v>
       </c>
-      <c r="C11" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="39" t="s">
+      <c r="C11" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="37" t="s">
         <v>766</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="37" t="s">
         <v>489</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="38">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="36" t="s">
         <v>747</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="37" t="s">
         <v>490</v>
       </c>
-      <c r="C12" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="39" t="s">
+      <c r="C12" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="37" t="s">
         <v>766</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="37" t="s">
         <v>491</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="38">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="36" t="s">
         <v>747</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="37" t="s">
         <v>767</v>
       </c>
-      <c r="C13" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="39" t="s">
+      <c r="C13" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="37" t="s">
         <v>768</v>
       </c>
-      <c r="E13" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="41"/>
+      <c r="E13" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="39"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="36" t="s">
         <v>747</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="36" t="s">
         <v>769</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="36" t="s">
         <v>770</v>
       </c>
-      <c r="E14" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="42">
+      <c r="E14" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="40">
         <v>0</v>
       </c>
     </row>
@@ -13096,33 +13086,35 @@
       <c r="A20" s="17" t="s">
         <v>643</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="25" t="s">
         <v>661</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="7" t="s">
         <v>662</v>
       </c>
-      <c r="E20" s="33"/>
-      <c r="F20" s="34"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="17" t="s">
         <v>643</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="25" t="s">
         <v>663</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="34"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="17" t="s">
@@ -13132,15 +13124,17 @@
         <v>665</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="D22" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="17" t="s">
         <v>666</v>
       </c>
-      <c r="E22" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="18"/>
+      <c r="F22" s="18">
+        <v>0</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="17" t="s">
@@ -13150,17 +13144,15 @@
         <v>667</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="D23" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="17" t="s">
         <v>668</v>
       </c>
-      <c r="E23" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="18">
-        <v>0</v>
-      </c>
+      <c r="F23" s="18"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="17" t="s">
@@ -13518,7 +13510,7 @@
         <v>697</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D43" s="32" t="s">
         <v>698</v>
@@ -13526,9 +13518,7 @@
       <c r="E43" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F43" s="16">
-        <v>0</v>
-      </c>
+      <c r="F43" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="17" t="s">

--- a/src/global/utils/file-utils/locators(2).xlsx
+++ b/src/global/utils/file-utils/locators(2).xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="17"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="HomePage"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2917" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2992" uniqueCount="856">
   <si>
     <t>page</t>
   </si>
@@ -1828,13 +1828,16 @@
     <t>:text("Results") &gt;&gt; svg</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>GamingLobbyPage</t>
   </si>
   <si>
     <t>Aviator</t>
   </si>
   <si>
-    <t>a[href='/lobby/casino-games/game/aviator']</t>
+    <t>a[href='/lobby/Casino/featured/Aviator']</t>
   </si>
   <si>
     <t>loginInPopup</t>
@@ -1876,16 +1879,25 @@
     <t>casinoGames</t>
   </si>
   <si>
-    <t>casino games</t>
-  </si>
-  <si>
     <t>{ "hasText": true }</t>
   </si>
   <si>
     <t>promotionsInCasino</t>
   </si>
   <si>
-    <t>//img[@alt='/Betway/South-Africa/SA_Responsible_gambling_CL/']</t>
+    <t>//img[@alt='/Betway/South-Africa/SA_Hacksaw_LeBandit_DeulAtDawn_NewGames/']</t>
+  </si>
+  <si>
+    <t>promotionsInCasinoNG</t>
+  </si>
+  <si>
+    <t>//img[@alt='/Betway/Nigeria/NG_Premier_League_Reels/']</t>
+  </si>
+  <si>
+    <t>promotionsInCasinoGH</t>
+  </si>
+  <si>
+    <t>//img[@alt='/Betway/Ghana/GH_Drops_and_Wins_26/']</t>
   </si>
   <si>
     <t>casinoSearch</t>
@@ -1918,18 +1930,36 @@
     <t>betGames</t>
   </si>
   <si>
+    <t>a[href='/lobby/betgames']</t>
+  </si>
+  <si>
+    <t>promotionsInBetGamesNG</t>
+  </si>
+  <si>
+    <t>img</t>
+  </si>
+  <si>
+    <t>{"name": "/Betway/Nigeria-Synapse/NG_Betgames_New_Lobby_Lucky7/"}</t>
+  </si>
+  <si>
+    <t>promotionsInBetGamesGH</t>
+  </si>
+  <si>
+    <t>{ "name": "/Betway/Ghana/Betgames_New_Lobby_Lucky7/" }</t>
+  </si>
+  <si>
     <t>promotionsInBetGames</t>
   </si>
   <si>
-    <t>img</t>
-  </si>
-  <si>
     <t>{ "name": "/Betway/South-Africa/Betgames_New_Lobby_Skyward/" }</t>
   </si>
   <si>
     <t>betGamesFilter</t>
   </si>
   <si>
+    <t>a[href='/lobby/betgames/betgames'].flex.gap-2.items-center</t>
+  </si>
+  <si>
     <t>gameDivBetGames</t>
   </si>
   <si>
@@ -1939,6 +1969,18 @@
     <t>virtuals</t>
   </si>
   <si>
+    <t>promotionsInVirtualsNG</t>
+  </si>
+  <si>
+    <t>{ "name": "/Betway/Nigeria-Synapse/Virtuals-_New_Lobby_PlatHounds/" }</t>
+  </si>
+  <si>
+    <t>promotionsInVirtualsGH</t>
+  </si>
+  <si>
+    <t>{ "name": "/Betway/Ghana/GH_FansWorldCup/" }</t>
+  </si>
+  <si>
     <t>promotionsInVirtuals</t>
   </si>
   <si>
@@ -1964,6 +2006,9 @@
   </si>
   <si>
     <t>//*[@id="tab"]/div/div[3]/div/div[2]/div/div/div[1]/div[1]</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>HeaderPage</t>
@@ -2729,7 +2774,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="50">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2825,6 +2870,21 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
@@ -3192,16 +3252,16 @@
       <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="47" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>805</v>
+        <v>820</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>8</v>
@@ -3210,7 +3270,7 @@
         <v>30</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="F2" s="8">
         <v>1</v>
@@ -3218,10 +3278,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>807</v>
+        <v>822</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>8</v>
@@ -3230,22 +3290,22 @@
         <v>30</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="F3" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>809</v>
+        <v>824</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>23</v>
@@ -3254,10 +3314,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>8</v>
@@ -3266,16 +3326,16 @@
         <v>30</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="F5" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>813</v>
+        <v>828</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>8</v>
@@ -3284,16 +3344,16 @@
         <v>30</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>814</v>
+        <v>829</v>
       </c>
       <c r="F6" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>815</v>
+        <v>830</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>8</v>
@@ -3302,22 +3362,22 @@
         <v>30</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>816</v>
+        <v>831</v>
       </c>
       <c r="F7" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>817</v>
+        <v>832</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>23</v>
@@ -3326,16 +3386,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>819</v>
+        <v>834</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>23</v>
@@ -3344,16 +3404,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>821</v>
+        <v>836</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>822</v>
+        <v>837</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>23</v>
@@ -3362,10 +3422,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>823</v>
+        <v>838</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>8</v>
@@ -3374,7 +3434,7 @@
         <v>30</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>824</v>
+        <v>839</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
@@ -3382,16 +3442,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>825</v>
+        <v>840</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>826</v>
+        <v>841</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>23</v>
@@ -3400,16 +3460,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>827</v>
+        <v>842</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>827</v>
+        <v>842</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>23</v>
@@ -3418,16 +3478,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>828</v>
+        <v>843</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>829</v>
+        <v>844</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>23</v>
@@ -3436,16 +3496,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>830</v>
+        <v>845</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>831</v>
+        <v>846</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>23</v>
@@ -3454,16 +3514,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>832</v>
+        <v>847</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>833</v>
+        <v>848</v>
       </c>
       <c r="E16" s="26" t="s">
         <v>23</v>
@@ -3472,16 +3532,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>834</v>
+        <v>849</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>835</v>
+        <v>850</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>23</v>
@@ -3490,16 +3550,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>836</v>
+        <v>851</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>837</v>
+        <v>852</v>
       </c>
       <c r="E18" s="26" t="s">
         <v>23</v>
@@ -3508,16 +3568,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>838</v>
+        <v>853</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="44" t="s">
-        <v>839</v>
+      <c r="D19" s="49" t="s">
+        <v>854</v>
       </c>
       <c r="E19" s="26" t="s">
         <v>23</v>
@@ -3526,10 +3586,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="6" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>8</v>
@@ -3538,7 +3598,7 @@
         <v>30</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="F20" s="8"/>
     </row>
@@ -10961,13 +11021,13 @@
       <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="47" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>178</v>
@@ -10987,7 +11047,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>189</v>
@@ -10999,7 +11059,7 @@
         <v>30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="F3" s="8">
         <v>0</v>
@@ -11007,7 +11067,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>191</v>
@@ -11027,7 +11087,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>193</v>
@@ -11047,7 +11107,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>195</v>
@@ -11067,7 +11127,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>197</v>
@@ -11087,7 +11147,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>199</v>
@@ -11099,7 +11159,7 @@
         <v>30</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>795</v>
+        <v>810</v>
       </c>
       <c r="F8" s="8">
         <v>0</v>
@@ -11107,7 +11167,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>201</v>
@@ -11119,7 +11179,7 @@
         <v>30</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="F9" s="8">
         <v>0</v>
@@ -11127,7 +11187,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>203</v>
@@ -11139,7 +11199,7 @@
         <v>30</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>797</v>
+        <v>812</v>
       </c>
       <c r="F10" s="8">
         <v>0</v>
@@ -11147,7 +11207,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>205</v>
@@ -11159,7 +11219,7 @@
         <v>30</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>798</v>
+        <v>813</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
@@ -11167,7 +11227,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>207</v>
@@ -11179,7 +11239,7 @@
         <v>30</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="F12" s="8">
         <v>0</v>
@@ -11187,7 +11247,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>209</v>
@@ -11199,7 +11259,7 @@
         <v>30</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="F13" s="8">
         <v>0</v>
@@ -11207,7 +11267,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>211</v>
@@ -11227,7 +11287,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>213</v>
@@ -11239,7 +11299,7 @@
         <v>30</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
@@ -11247,7 +11307,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>215</v>
@@ -11259,7 +11319,7 @@
         <v>30</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="F16" s="8">
         <v>0</v>
@@ -11267,7 +11327,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>217</v>
@@ -11279,7 +11339,7 @@
         <v>30</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="F17" s="8">
         <v>0</v>
@@ -11287,7 +11347,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>219</v>
@@ -11307,7 +11367,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>384</v>
@@ -11327,7 +11387,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>222</v>
@@ -11347,7 +11407,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>223</v>
@@ -11367,7 +11427,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>32</v>
@@ -11387,7 +11447,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>225</v>
@@ -11407,7 +11467,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>227</v>
@@ -11427,7 +11487,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>229</v>
@@ -11447,7 +11507,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="6" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>231</v>
@@ -11544,7 +11604,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>23</v>
@@ -11592,13 +11652,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="15" t="s">
-        <v>773</v>
+        <v>788</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>774</v>
+        <v>789</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>23</v>
@@ -11609,13 +11669,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="15" t="s">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>776</v>
+        <v>791</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>23</v>
@@ -11624,13 +11684,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="15" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>23</v>
@@ -11639,13 +11699,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="15" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>780</v>
+        <v>795</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>23</v>
@@ -11654,13 +11714,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="15" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>23</v>
@@ -11675,7 +11735,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>783</v>
+        <v>798</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>23</v>
@@ -11684,13 +11744,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>784</v>
+        <v>799</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>23</v>
@@ -11699,13 +11759,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="43" t="s">
-        <v>787</v>
+      <c r="C9" s="48" t="s">
+        <v>802</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>23</v>
@@ -11714,13 +11774,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>788</v>
+        <v>803</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>23</v>
@@ -11729,7 +11789,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>8</v>
@@ -11738,7 +11798,7 @@
         <v>14</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>791</v>
+        <v>806</v>
       </c>
       <c r="E11" s="8"/>
     </row>
@@ -11775,7 +11835,7 @@
       <c r="D1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="47" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11807,7 +11867,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="E3" s="16">
         <v>0</v>
@@ -12458,274 +12518,274 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35" t="s">
+      <c r="A1" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="37" t="s">
-        <v>748</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>749</v>
-      </c>
-      <c r="C2" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="38" t="s">
+      <c r="A2" s="42" t="s">
+        <v>763</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>764</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="38" t="s">
-        <v>750</v>
-      </c>
-      <c r="F2" s="39">
+      <c r="E2" s="43" t="s">
+        <v>765</v>
+      </c>
+      <c r="F2" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="37" t="s">
-        <v>748</v>
-      </c>
-      <c r="B3" s="38" t="s">
-        <v>751</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="38" t="s">
+      <c r="A3" s="42" t="s">
+        <v>763</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>766</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="38" t="s">
-        <v>752</v>
-      </c>
-      <c r="F3" s="39">
+      <c r="E3" s="43" t="s">
+        <v>767</v>
+      </c>
+      <c r="F3" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="37" t="s">
-        <v>748</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>753</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="38" t="s">
-        <v>754</v>
-      </c>
-      <c r="E4" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="40"/>
+      <c r="A4" s="42" t="s">
+        <v>763</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>768</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>769</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="45"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="37" t="s">
-        <v>748</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>755</v>
-      </c>
-      <c r="C5" s="38" t="s">
+      <c r="A5" s="42" t="s">
+        <v>763</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>770</v>
+      </c>
+      <c r="C5" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="38" t="s">
-        <v>756</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="39">
+      <c r="D5" s="43" t="s">
+        <v>771</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="37" t="s">
-        <v>748</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>757</v>
-      </c>
-      <c r="C6" s="38" t="s">
+      <c r="A6" s="42" t="s">
+        <v>763</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>772</v>
+      </c>
+      <c r="C6" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="38" t="s">
-        <v>758</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="39">
+      <c r="D6" s="43" t="s">
+        <v>773</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="37" t="s">
-        <v>748</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>759</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="38" t="s">
-        <v>760</v>
-      </c>
-      <c r="E7" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="40"/>
+      <c r="A7" s="42" t="s">
+        <v>763</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>774</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>775</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="45"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="37" t="s">
-        <v>748</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>761</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="38" t="s">
-        <v>762</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="40"/>
+      <c r="A8" s="42" t="s">
+        <v>763</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>776</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>777</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="45"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="37" t="s">
-        <v>748</v>
-      </c>
-      <c r="B9" s="38" t="s">
+      <c r="A9" s="42" t="s">
         <v>763</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="B9" s="43" t="s">
+        <v>778</v>
+      </c>
+      <c r="C9" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="38" t="s">
-        <v>764</v>
-      </c>
-      <c r="E9" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="39">
+      <c r="D9" s="43" t="s">
+        <v>779</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="37" t="s">
-        <v>748</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>765</v>
-      </c>
-      <c r="C10" s="38" t="s">
+      <c r="A10" s="42" t="s">
+        <v>763</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>780</v>
+      </c>
+      <c r="C10" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="38" t="s">
-        <v>766</v>
-      </c>
-      <c r="E10" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="39">
+      <c r="D10" s="43" t="s">
+        <v>781</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="37" t="s">
-        <v>748</v>
-      </c>
-      <c r="B11" s="38" t="s">
+      <c r="A11" s="42" t="s">
+        <v>763</v>
+      </c>
+      <c r="B11" s="43" t="s">
         <v>489</v>
       </c>
-      <c r="C11" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>767</v>
-      </c>
-      <c r="E11" s="38" t="s">
+      <c r="C11" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>782</v>
+      </c>
+      <c r="E11" s="43" t="s">
         <v>490</v>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="37" t="s">
-        <v>748</v>
-      </c>
-      <c r="B12" s="38" t="s">
+      <c r="A12" s="42" t="s">
+        <v>763</v>
+      </c>
+      <c r="B12" s="43" t="s">
         <v>491</v>
       </c>
-      <c r="C12" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="38" t="s">
-        <v>767</v>
-      </c>
-      <c r="E12" s="38" t="s">
+      <c r="C12" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>782</v>
+      </c>
+      <c r="E12" s="43" t="s">
         <v>492</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="44">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="37" t="s">
-        <v>748</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>768</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="38" t="s">
-        <v>769</v>
-      </c>
-      <c r="E13" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="40"/>
+      <c r="A13" s="42" t="s">
+        <v>763</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>783</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>784</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="45"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="37" t="s">
-        <v>748</v>
-      </c>
-      <c r="B14" s="37" t="s">
-        <v>770</v>
-      </c>
-      <c r="C14" s="37" t="s">
+      <c r="A14" s="42" t="s">
+        <v>763</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>785</v>
+      </c>
+      <c r="C14" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="37" t="s">
-        <v>771</v>
-      </c>
-      <c r="E14" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="41">
+      <c r="D14" s="42" t="s">
+        <v>786</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="46">
         <v>0</v>
       </c>
     </row>
@@ -12772,19 +12832,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>645</v>
+        <v>660</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="38" t="s">
         <v>30</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>646</v>
+        <v>661</v>
       </c>
       <c r="F2" s="19">
         <v>0</v>
@@ -12792,7 +12852,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>7</v>
@@ -12800,7 +12860,7 @@
       <c r="C3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="38" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="18" t="s">
@@ -12810,7 +12870,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>273</v>
@@ -12818,7 +12878,7 @@
       <c r="C4" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="38" t="s">
         <v>274</v>
       </c>
       <c r="E4" s="18" t="s">
@@ -12828,7 +12888,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>275</v>
@@ -12836,7 +12896,7 @@
       <c r="C5" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="38" t="s">
         <v>77</v>
       </c>
       <c r="E5" s="18" t="s">
@@ -12848,7 +12908,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>105</v>
@@ -12856,7 +12916,7 @@
       <c r="C6" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="38" t="s">
         <v>106</v>
       </c>
       <c r="E6" s="18" t="s">
@@ -12866,7 +12926,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>13</v>
@@ -12874,7 +12934,7 @@
       <c r="C7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="38" t="s">
         <v>171</v>
       </c>
       <c r="E7" s="18" t="s">
@@ -12884,7 +12944,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>172</v>
@@ -12892,7 +12952,7 @@
       <c r="C8" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="38" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="18" t="s">
@@ -12904,15 +12964,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>647</v>
+        <v>662</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="38" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="18" t="s">
@@ -12924,7 +12984,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>174</v>
@@ -12932,7 +12992,7 @@
       <c r="C10" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="38" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="18" t="s">
@@ -12942,7 +13002,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>176</v>
@@ -12950,7 +13010,7 @@
       <c r="C11" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="38" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="18" t="s">
@@ -12962,16 +13022,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>648</v>
+        <v>663</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="33" t="s">
-        <v>649</v>
+      <c r="D12" s="38" t="s">
+        <v>664</v>
       </c>
       <c r="E12" s="18" t="s">
         <v>23</v>
@@ -12980,16 +13040,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>650</v>
+        <v>665</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="33" t="s">
-        <v>651</v>
+      <c r="D13" s="38" t="s">
+        <v>666</v>
       </c>
       <c r="E13" s="18" t="s">
         <v>23</v>
@@ -13000,16 +13060,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="33" t="s">
-        <v>653</v>
+      <c r="D14" s="38" t="s">
+        <v>668</v>
       </c>
       <c r="E14" s="18" t="s">
         <v>23</v>
@@ -13020,16 +13080,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="C15" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="33" t="s">
-        <v>655</v>
+      <c r="D15" s="38" t="s">
+        <v>670</v>
       </c>
       <c r="E15" s="18" t="s">
         <v>23</v>
@@ -13038,16 +13098,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>656</v>
+        <v>671</v>
       </c>
       <c r="C16" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="33" t="s">
-        <v>657</v>
+      <c r="D16" s="38" t="s">
+        <v>672</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>23</v>
@@ -13056,16 +13116,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>658</v>
+        <v>673</v>
       </c>
       <c r="C17" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="33" t="s">
-        <v>655</v>
+      <c r="D17" s="38" t="s">
+        <v>670</v>
       </c>
       <c r="E17" s="18" t="s">
         <v>23</v>
@@ -13074,16 +13134,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>659</v>
+        <v>674</v>
       </c>
       <c r="C18" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="33" t="s">
-        <v>657</v>
+      <c r="D18" s="38" t="s">
+        <v>672</v>
       </c>
       <c r="E18" s="18" t="s">
         <v>23</v>
@@ -13094,16 +13154,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>660</v>
+        <v>675</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="33" t="s">
-        <v>661</v>
+      <c r="D19" s="38" t="s">
+        <v>676</v>
       </c>
       <c r="E19" s="18" t="s">
         <v>23</v>
@@ -13112,32 +13172,32 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>662</v>
+        <v>677</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>68</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>663</v>
+        <v>678</v>
       </c>
       <c r="E20" s="26"/>
       <c r="F20" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>664</v>
+        <v>679</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>68</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>665</v>
+        <v>680</v>
       </c>
       <c r="E21" s="26"/>
       <c r="F21" s="7">
@@ -13146,19 +13206,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>666</v>
+        <v>681</v>
       </c>
       <c r="C22" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="33" t="s">
+      <c r="D22" s="38" t="s">
         <v>30</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>667</v>
+        <v>682</v>
       </c>
       <c r="F22" s="19">
         <v>0</v>
@@ -13166,34 +13226,34 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>668</v>
+        <v>683</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="33" t="s">
+      <c r="D23" s="38" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>669</v>
+        <v>684</v>
       </c>
       <c r="F23" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>670</v>
+        <v>685</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="33" t="s">
-        <v>671</v>
+      <c r="D24" s="38" t="s">
+        <v>686</v>
       </c>
       <c r="E24" s="18" t="s">
         <v>23</v>
@@ -13202,10 +13262,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>672</v>
+        <v>687</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>68</v>
@@ -13222,15 +13282,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>673</v>
+        <v>688</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="33" t="s">
+      <c r="D26" s="38" t="s">
         <v>381</v>
       </c>
       <c r="E26" s="18" t="s">
@@ -13240,7 +13300,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B27" s="18" t="s">
         <v>167</v>
@@ -13248,7 +13308,7 @@
       <c r="C27" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="33" t="s">
+      <c r="D27" s="38" t="s">
         <v>382</v>
       </c>
       <c r="E27" s="18" t="s">
@@ -13258,16 +13318,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>674</v>
+        <v>689</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="33" t="s">
-        <v>675</v>
+      <c r="D28" s="38" t="s">
+        <v>690</v>
       </c>
       <c r="E28" s="18" t="s">
         <v>23</v>
@@ -13276,16 +13336,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>676</v>
+        <v>691</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="33" t="s">
-        <v>677</v>
+      <c r="D29" s="38" t="s">
+        <v>692</v>
       </c>
       <c r="E29" s="18" t="s">
         <v>23</v>
@@ -13294,7 +13354,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B30" s="18" t="s">
         <v>384</v>
@@ -13302,7 +13362,7 @@
       <c r="C30" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D30" s="33" t="s">
+      <c r="D30" s="38" t="s">
         <v>385</v>
       </c>
       <c r="E30" s="18" t="s">
@@ -13312,15 +13372,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>678</v>
+        <v>693</v>
       </c>
       <c r="C31" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="33" t="s">
+      <c r="D31" s="38" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="18" t="s">
@@ -13330,19 +13390,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>679</v>
+        <v>694</v>
       </c>
       <c r="C32" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="33" t="s">
+      <c r="D32" s="38" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>680</v>
+        <v>695</v>
       </c>
       <c r="F32" s="17">
         <v>1</v>
@@ -13350,33 +13410,33 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>681</v>
+        <v>696</v>
       </c>
       <c r="C33" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="D33" s="38" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>682</v>
+        <v>697</v>
       </c>
       <c r="F33" s="17"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>683</v>
+        <v>698</v>
       </c>
       <c r="C34" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="33" t="s">
+      <c r="D34" s="38" t="s">
         <v>77</v>
       </c>
       <c r="E34" s="18" t="s">
@@ -13388,16 +13448,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>684</v>
+        <v>699</v>
       </c>
       <c r="C35" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D35" s="33" t="s">
-        <v>685</v>
+      <c r="D35" s="38" t="s">
+        <v>700</v>
       </c>
       <c r="E35" s="18" t="s">
         <v>23</v>
@@ -13406,16 +13466,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>686</v>
+        <v>701</v>
       </c>
       <c r="C36" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D36" s="33" t="s">
-        <v>687</v>
+      <c r="D36" s="38" t="s">
+        <v>702</v>
       </c>
       <c r="E36" s="18" t="s">
         <v>23</v>
@@ -13424,16 +13484,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>688</v>
+        <v>703</v>
       </c>
       <c r="C37" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D37" s="33" t="s">
-        <v>689</v>
+      <c r="D37" s="38" t="s">
+        <v>704</v>
       </c>
       <c r="E37" s="18" t="s">
         <v>23</v>
@@ -13442,16 +13502,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>690</v>
+        <v>705</v>
       </c>
       <c r="C38" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="33" t="s">
-        <v>691</v>
+      <c r="D38" s="38" t="s">
+        <v>706</v>
       </c>
       <c r="E38" s="18" t="s">
         <v>23</v>
@@ -13460,16 +13520,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>692</v>
+        <v>707</v>
       </c>
       <c r="C39" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="33" t="s">
-        <v>693</v>
+      <c r="D39" s="38" t="s">
+        <v>708</v>
       </c>
       <c r="E39" s="18" t="s">
         <v>23</v>
@@ -13478,7 +13538,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B40" s="18" t="s">
         <v>186</v>
@@ -13486,7 +13546,7 @@
       <c r="C40" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="33" t="s">
+      <c r="D40" s="38" t="s">
         <v>187</v>
       </c>
       <c r="E40" s="18" t="s">
@@ -13496,16 +13556,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>694</v>
+        <v>709</v>
       </c>
       <c r="C41" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="33" t="s">
-        <v>695</v>
+      <c r="D41" s="38" t="s">
+        <v>710</v>
       </c>
       <c r="E41" s="18" t="s">
         <v>23</v>
@@ -13514,16 +13574,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>696</v>
+        <v>711</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D42" s="33" t="s">
-        <v>697</v>
+      <c r="D42" s="38" t="s">
+        <v>712</v>
       </c>
       <c r="E42" s="18" t="s">
         <v>23</v>
@@ -13532,16 +13592,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>698</v>
+        <v>713</v>
       </c>
       <c r="C43" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D43" s="33" t="s">
-        <v>699</v>
+      <c r="D43" s="38" t="s">
+        <v>714</v>
       </c>
       <c r="E43" s="18" t="s">
         <v>23</v>
@@ -13550,16 +13610,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D44" s="33" t="s">
-        <v>701</v>
+      <c r="D44" s="38" t="s">
+        <v>716</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>23</v>
@@ -13568,16 +13628,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>702</v>
+        <v>717</v>
       </c>
       <c r="C45" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="33" t="s">
-        <v>703</v>
+      <c r="D45" s="38" t="s">
+        <v>718</v>
       </c>
       <c r="E45" s="18" t="s">
         <v>23</v>
@@ -13586,16 +13646,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>704</v>
+        <v>719</v>
       </c>
       <c r="C46" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="33" t="s">
-        <v>705</v>
+      <c r="D46" s="38" t="s">
+        <v>720</v>
       </c>
       <c r="E46" s="18" t="s">
         <v>23</v>
@@ -13604,16 +13664,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>706</v>
+        <v>721</v>
       </c>
       <c r="C47" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D47" s="33" t="s">
-        <v>707</v>
+      <c r="D47" s="38" t="s">
+        <v>722</v>
       </c>
       <c r="E47" s="18" t="s">
         <v>23</v>
@@ -13622,16 +13682,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>640</v>
+        <v>654</v>
       </c>
       <c r="C48" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="33" t="s">
-        <v>641</v>
+      <c r="D48" s="38" t="s">
+        <v>655</v>
       </c>
       <c r="E48" s="18" t="s">
         <v>23</v>
@@ -13640,15 +13700,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>708</v>
+        <v>723</v>
       </c>
       <c r="C49" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="33" t="s">
+      <c r="D49" s="38" t="s">
         <v>77</v>
       </c>
       <c r="E49" s="18" t="s">
@@ -13660,16 +13720,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="C50" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D50" s="33" t="s">
-        <v>710</v>
+      <c r="D50" s="38" t="s">
+        <v>725</v>
       </c>
       <c r="E50" s="18" t="s">
         <v>23</v>
@@ -13678,16 +13738,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="C51" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D51" s="33" t="s">
-        <v>712</v>
+      <c r="D51" s="38" t="s">
+        <v>727</v>
       </c>
       <c r="E51" s="18" t="s">
         <v>23</v>
@@ -13698,16 +13758,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="C52" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D52" s="33" t="s">
-        <v>714</v>
+      <c r="D52" s="38" t="s">
+        <v>729</v>
       </c>
       <c r="E52" s="18" t="s">
         <v>23</v>
@@ -13718,16 +13778,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>715</v>
+        <v>730</v>
       </c>
       <c r="C53" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="33" t="s">
-        <v>716</v>
+      <c r="D53" s="38" t="s">
+        <v>731</v>
       </c>
       <c r="E53" s="18" t="s">
         <v>164</v>
@@ -13736,34 +13796,34 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>717</v>
+        <v>732</v>
       </c>
       <c r="C54" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="33" t="s">
-        <v>718</v>
+      <c r="D54" s="38" t="s">
+        <v>733</v>
       </c>
       <c r="E54" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F54" s="33"/>
+      <c r="F54" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="C55" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D55" s="33" t="s">
-        <v>720</v>
+      <c r="D55" s="38" t="s">
+        <v>735</v>
       </c>
       <c r="E55" s="18" t="s">
         <v>23</v>
@@ -13772,16 +13832,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>721</v>
+        <v>736</v>
       </c>
       <c r="C56" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D56" s="33" t="s">
-        <v>722</v>
+      <c r="D56" s="38" t="s">
+        <v>737</v>
       </c>
       <c r="E56" s="18" t="s">
         <v>23</v>
@@ -13790,16 +13850,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>723</v>
+        <v>738</v>
       </c>
       <c r="C57" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="33" t="s">
-        <v>724</v>
+      <c r="D57" s="38" t="s">
+        <v>739</v>
       </c>
       <c r="E57" s="18" t="s">
         <v>23</v>
@@ -13808,16 +13868,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="C58" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="33" t="s">
-        <v>722</v>
+      <c r="D58" s="38" t="s">
+        <v>737</v>
       </c>
       <c r="E58" s="18" t="s">
         <v>23</v>
@@ -13826,16 +13886,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>727</v>
-      </c>
-      <c r="D59" s="33" t="s">
-        <v>728</v>
+        <v>742</v>
+      </c>
+      <c r="D59" s="38" t="s">
+        <v>743</v>
       </c>
       <c r="E59" s="18" t="s">
         <v>23</v>
@@ -13844,16 +13904,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="C60" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D60" s="33" t="s">
-        <v>730</v>
+      <c r="D60" s="38" t="s">
+        <v>745</v>
       </c>
       <c r="E60" s="18" t="s">
         <v>23</v>
@@ -13862,16 +13922,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>731</v>
+        <v>746</v>
       </c>
       <c r="C61" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D61" s="33" t="s">
-        <v>730</v>
+      <c r="D61" s="38" t="s">
+        <v>745</v>
       </c>
       <c r="E61" s="18" t="s">
         <v>23</v>
@@ -13882,16 +13942,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>732</v>
+        <v>747</v>
       </c>
       <c r="C62" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D62" s="33" t="s">
-        <v>722</v>
+      <c r="D62" s="38" t="s">
+        <v>737</v>
       </c>
       <c r="E62" s="18" t="s">
         <v>23</v>
@@ -13900,16 +13960,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>727</v>
-      </c>
-      <c r="D63" s="33" t="s">
-        <v>734</v>
+        <v>742</v>
+      </c>
+      <c r="D63" s="38" t="s">
+        <v>749</v>
       </c>
       <c r="E63" s="18" t="s">
         <v>23</v>
@@ -13918,19 +13978,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5">
       <c r="A64" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>735</v>
+        <v>750</v>
       </c>
       <c r="C64" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D64" s="33" t="s">
+      <c r="D64" s="38" t="s">
         <v>14</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>680</v>
+        <v>695</v>
       </c>
       <c r="F64" s="19">
         <v>1</v>
@@ -13938,16 +13998,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
       <c r="A65" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="C65" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D65" s="33" t="s">
-        <v>737</v>
+      <c r="D65" s="38" t="s">
+        <v>752</v>
       </c>
       <c r="E65" s="18" t="s">
         <v>23</v>
@@ -13956,16 +14016,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="C66" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D66" s="33" t="s">
-        <v>739</v>
+      <c r="D66" s="38" t="s">
+        <v>754</v>
       </c>
       <c r="E66" s="18" t="s">
         <v>23</v>
@@ -13974,16 +14034,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="26" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="C67" s="26" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>741</v>
+        <v>756</v>
       </c>
       <c r="E67" s="26" t="s">
         <v>23</v>
@@ -13992,16 +14052,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="26" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="C68" s="26" t="s">
         <v>25</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>743</v>
+        <v>758</v>
       </c>
       <c r="E68" s="26" t="s">
         <v>23</v>
@@ -14010,16 +14070,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="26" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>744</v>
+        <v>759</v>
       </c>
       <c r="C69" s="26" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="E69" s="26" t="s">
         <v>23</v>
@@ -14028,16 +14088,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="19.5">
       <c r="A70" s="18" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="C70" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D70" s="33" t="s">
-        <v>747</v>
+      <c r="D70" s="38" t="s">
+        <v>762</v>
       </c>
       <c r="E70" s="18" t="s">
         <v>23</v>
@@ -14054,7 +14114,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -14082,160 +14142,172 @@
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>5</v>
+        <v>598</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>599</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>600</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>602</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>603</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>605</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>606</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>607</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>608</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="8"/>
+      <c r="F7" s="8" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="8">
-        <v>0</v>
+      <c r="F8" s="8" t="s">
+        <v>598</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>614</v>
+        <v>181</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="F9" s="8">
-        <v>0</v>
+      <c r="F9" s="8" t="s">
+        <v>598</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>616</v>
@@ -14249,17 +14321,19 @@
       <c r="E10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="8"/>
+      <c r="F10" s="8" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>618</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>619</v>
@@ -14267,39 +14341,39 @@
       <c r="E11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="8">
-        <v>0</v>
+      <c r="F11" s="8" t="s">
+        <v>598</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="6" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>620</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>621</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>615</v>
-      </c>
-      <c r="F12" s="8">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>598</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="6" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>622</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>623</v>
@@ -14307,295 +14381,477 @@
       <c r="E13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="8"/>
+      <c r="F13" s="8" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>321</v>
+        <v>624</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="F14" s="8">
-        <v>0</v>
+      <c r="F14" s="8" t="s">
+        <v>598</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>598</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>625</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>626</v>
-      </c>
-      <c r="F15" s="8">
-        <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="6" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>627</v>
+        <v>321</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>199</v>
+        <v>628</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="F16" s="8"/>
+      <c r="F16" s="8" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>629</v>
+        <v>14</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="F17" s="8">
-        <v>0</v>
+      <c r="F17" s="8" t="s">
+        <v>598</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>631</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>284</v>
+        <v>632</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>615</v>
-      </c>
-      <c r="F18" s="8"/>
+        <v>23</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="F19" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>632</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>633</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>634</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>615</v>
-      </c>
-      <c r="F20" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>598</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="8">
-        <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="8" t="s">
         <v>598</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="8">
-        <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>598</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="8">
-        <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="F24" s="8" t="s">
         <v>598</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24" s="8">
-        <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>598</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>635</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>629</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>636</v>
-      </c>
-      <c r="F25" s="8">
-        <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="33" t="s">
         <v>598</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>637</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>638</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>639</v>
-      </c>
-      <c r="F26" s="8">
-        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="33" t="s">
         <v>598</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>640</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>641</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" s="17"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="33" t="s">
         <v>598</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>642</v>
-      </c>
-      <c r="C28" s="6" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="F30" s="33" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="F32" s="33" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="33" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+      <c r="A34" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>643</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" s="8"/>
+      <c r="D34" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="33"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+      <c r="A36" s="34" t="s">
+        <v>658</v>
+      </c>
+      <c r="B36" s="35" t="s">
+        <v>658</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>658</v>
+      </c>
+      <c r="D36" s="35" t="s">
+        <v>658</v>
+      </c>
+      <c r="E36" s="35" t="s">
+        <v>658</v>
+      </c>
+      <c r="F36" s="36" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+      <c r="A37" s="34" t="s">
+        <v>658</v>
+      </c>
+      <c r="B37" s="34" t="s">
+        <v>658</v>
+      </c>
+      <c r="C37" s="34" t="s">
+        <v>658</v>
+      </c>
+      <c r="D37" s="34" t="s">
+        <v>658</v>
+      </c>
+      <c r="E37" s="34" t="s">
+        <v>658</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>658</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/global/utils/file-utils/locators(2).xlsx
+++ b/src/global/utils/file-utils/locators(2).xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="7"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="HomePage"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2992" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2980" uniqueCount="855">
   <si>
     <t>page</t>
   </si>
@@ -2008,9 +2008,6 @@
     <t>//*[@id="tab"]/div/div[3]/div/div[2]/div/div/div[1]/div[1]</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>HeaderPage</t>
   </si>
   <si>
@@ -2239,7 +2236,7 @@
     <t>balanceDropdown</t>
   </si>
   <si>
-    <t>//*[@id="__nuxt"]/div/div/div[1]/header/div/div[2]/div/div[2]/div[2]</t>
+    <t>//*[@id="__nuxt"]/div/div[1]/header/div/div[2]/div/div[2]/div[2]</t>
   </si>
   <si>
     <t>balanceCurrency</t>
@@ -2290,7 +2287,7 @@
     <t>notificationBellIcon</t>
   </si>
   <si>
-    <t>//*[@id="__nuxt"]/div/div[1]/div[1]/header/div/div[2]/div/div[3]</t>
+    <t>//*[@id="__nuxt"]/div/div[1]/header/div/div[2]/div/div[3]</t>
   </si>
   <si>
     <t>allBalanceTxt</t>
@@ -2607,7 +2604,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2624,6 +2621,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -2774,7 +2777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="46">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2800,7 +2803,7 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -2809,55 +2812,49 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
@@ -2866,61 +2863,55 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="15" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="15" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="18" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="18" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="18" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="17" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="18" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="19" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3252,16 +3243,16 @@
       <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="43" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>819</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>820</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>8</v>
@@ -3270,7 +3261,7 @@
         <v>30</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F2" s="8">
         <v>1</v>
@@ -3278,10 +3269,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>8</v>
@@ -3290,22 +3281,22 @@
         <v>30</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F3" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>23</v>
@@ -3314,10 +3305,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>8</v>
@@ -3326,16 +3317,16 @@
         <v>30</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="F5" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>8</v>
@@ -3344,16 +3335,16 @@
         <v>30</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="F6" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>8</v>
@@ -3362,22 +3353,22 @@
         <v>30</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="F7" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>23</v>
@@ -3386,16 +3377,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>23</v>
@@ -3404,16 +3395,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>23</v>
@@ -3422,10 +3413,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>8</v>
@@ -3434,7 +3425,7 @@
         <v>30</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
@@ -3442,16 +3433,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>840</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>841</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>23</v>
@@ -3460,16 +3451,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>23</v>
@@ -3478,16 +3469,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>842</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>843</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>844</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>23</v>
@@ -3496,16 +3487,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>23</v>
@@ -3514,16 +3505,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E16" s="26" t="s">
         <v>23</v>
@@ -3532,16 +3523,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>23</v>
@@ -3550,16 +3541,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>851</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>852</v>
       </c>
       <c r="E18" s="26" t="s">
         <v>23</v>
@@ -3568,16 +3559,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="45" t="s">
         <v>853</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="49" t="s">
-        <v>854</v>
       </c>
       <c r="E19" s="26" t="s">
         <v>23</v>
@@ -3586,10 +3577,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>8</v>
@@ -3598,7 +3589,7 @@
         <v>30</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F20" s="8"/>
     </row>
@@ -11021,13 +11012,13 @@
       <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="43" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>178</v>
@@ -11047,7 +11038,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>189</v>
@@ -11059,7 +11050,7 @@
         <v>30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F3" s="8">
         <v>0</v>
@@ -11067,7 +11058,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>191</v>
@@ -11087,7 +11078,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>193</v>
@@ -11107,7 +11098,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>195</v>
@@ -11127,7 +11118,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>197</v>
@@ -11147,7 +11138,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>199</v>
@@ -11159,7 +11150,7 @@
         <v>30</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F8" s="8">
         <v>0</v>
@@ -11167,7 +11158,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>201</v>
@@ -11179,7 +11170,7 @@
         <v>30</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F9" s="8">
         <v>0</v>
@@ -11187,7 +11178,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>203</v>
@@ -11199,7 +11190,7 @@
         <v>30</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F10" s="8">
         <v>0</v>
@@ -11207,7 +11198,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>205</v>
@@ -11219,7 +11210,7 @@
         <v>30</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
@@ -11227,7 +11218,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>207</v>
@@ -11239,7 +11230,7 @@
         <v>30</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F12" s="8">
         <v>0</v>
@@ -11247,7 +11238,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>209</v>
@@ -11259,7 +11250,7 @@
         <v>30</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F13" s="8">
         <v>0</v>
@@ -11267,7 +11258,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>211</v>
@@ -11287,7 +11278,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>213</v>
@@ -11299,7 +11290,7 @@
         <v>30</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
@@ -11307,7 +11298,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>215</v>
@@ -11319,7 +11310,7 @@
         <v>30</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="F16" s="8">
         <v>0</v>
@@ -11327,7 +11318,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>217</v>
@@ -11339,7 +11330,7 @@
         <v>30</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F17" s="8">
         <v>0</v>
@@ -11347,7 +11338,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>219</v>
@@ -11367,7 +11358,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>384</v>
@@ -11387,7 +11378,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>222</v>
@@ -11407,7 +11398,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>223</v>
@@ -11427,7 +11418,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>32</v>
@@ -11447,7 +11438,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>225</v>
@@ -11467,7 +11458,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>227</v>
@@ -11487,7 +11478,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>229</v>
@@ -11507,7 +11498,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>231</v>
@@ -11604,7 +11595,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>23</v>
@@ -11652,13 +11643,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="15" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>23</v>
@@ -11669,13 +11660,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="15" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>23</v>
@@ -11684,13 +11675,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="15" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>23</v>
@@ -11699,13 +11690,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="15" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>23</v>
@@ -11714,13 +11705,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="15" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>23</v>
@@ -11735,7 +11726,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>23</v>
@@ -11744,13 +11735,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>799</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>800</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>23</v>
@@ -11759,13 +11750,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="44" t="s">
         <v>801</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>802</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>23</v>
@@ -11774,13 +11765,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>23</v>
@@ -11789,7 +11780,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>8</v>
@@ -11798,7 +11789,7 @@
         <v>14</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E11" s="8"/>
     </row>
@@ -11835,7 +11826,7 @@
       <c r="D1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="43" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11867,7 +11858,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E3" s="16">
         <v>0</v>
@@ -12518,274 +12509,274 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="40" t="s">
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="37" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="38" t="s">
+        <v>762</v>
+      </c>
+      <c r="B2" s="39" t="s">
         <v>763</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="C2" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="39" t="s">
         <v>764</v>
       </c>
-      <c r="C2" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="43" t="s">
+      <c r="F2" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="38" t="s">
+        <v>762</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>765</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="43" t="s">
-        <v>765</v>
-      </c>
-      <c r="F2" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="42" t="s">
-        <v>763</v>
-      </c>
-      <c r="B3" s="43" t="s">
+      <c r="E3" s="39" t="s">
         <v>766</v>
       </c>
-      <c r="C3" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="43" t="s">
+      <c r="F3" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="38" t="s">
+        <v>762</v>
+      </c>
+      <c r="B4" s="39" t="s">
         <v>767</v>
       </c>
-      <c r="F3" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="42" t="s">
-        <v>763</v>
-      </c>
-      <c r="B4" s="43" t="s">
+      <c r="C4" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="39" t="s">
         <v>768</v>
       </c>
-      <c r="C4" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="43" t="s">
+      <c r="E4" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="41"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="38" t="s">
+        <v>762</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>769</v>
       </c>
-      <c r="E4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="45"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="42" t="s">
-        <v>763</v>
-      </c>
-      <c r="B5" s="43" t="s">
+      <c r="C5" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="39" t="s">
         <v>770</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="E5" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="38" t="s">
+        <v>762</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>771</v>
+      </c>
+      <c r="C6" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="43" t="s">
-        <v>771</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="42" t="s">
-        <v>763</v>
-      </c>
-      <c r="B6" s="43" t="s">
+      <c r="D6" s="39" t="s">
         <v>772</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="E6" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="38" t="s">
+        <v>762</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>773</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>774</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="41"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="38" t="s">
+        <v>762</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>775</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>776</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="41"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="38" t="s">
+        <v>762</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>777</v>
+      </c>
+      <c r="C9" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="43" t="s">
-        <v>773</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="42" t="s">
-        <v>763</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>774</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>775</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="45"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="42" t="s">
-        <v>763</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>776</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>777</v>
-      </c>
-      <c r="E8" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="45"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="42" t="s">
-        <v>763</v>
-      </c>
-      <c r="B9" s="43" t="s">
+      <c r="D9" s="39" t="s">
         <v>778</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="E9" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="38" t="s">
+        <v>762</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>779</v>
+      </c>
+      <c r="C10" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="43" t="s">
-        <v>779</v>
-      </c>
-      <c r="E9" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="42" t="s">
-        <v>763</v>
-      </c>
-      <c r="B10" s="43" t="s">
+      <c r="D10" s="39" t="s">
         <v>780</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="E10" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="38" t="s">
+        <v>762</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>489</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>781</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>490</v>
+      </c>
+      <c r="F11" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="38" t="s">
+        <v>762</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>491</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>781</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>492</v>
+      </c>
+      <c r="F12" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="38" t="s">
+        <v>762</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>782</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>783</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="41"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="38" t="s">
+        <v>762</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>784</v>
+      </c>
+      <c r="C14" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="43" t="s">
-        <v>781</v>
-      </c>
-      <c r="E10" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="42" t="s">
-        <v>763</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>489</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>782</v>
-      </c>
-      <c r="E11" s="43" t="s">
-        <v>490</v>
-      </c>
-      <c r="F11" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="42" t="s">
-        <v>763</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>491</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="43" t="s">
-        <v>782</v>
-      </c>
-      <c r="E12" s="43" t="s">
-        <v>492</v>
-      </c>
-      <c r="F12" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="42" t="s">
-        <v>763</v>
-      </c>
-      <c r="B13" s="43" t="s">
-        <v>783</v>
-      </c>
-      <c r="C13" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="43" t="s">
-        <v>784</v>
-      </c>
-      <c r="E13" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="45"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="42" t="s">
-        <v>763</v>
-      </c>
-      <c r="B14" s="42" t="s">
+      <c r="D14" s="38" t="s">
         <v>785</v>
       </c>
-      <c r="C14" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="42" t="s">
-        <v>786</v>
-      </c>
-      <c r="E14" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="46">
+      <c r="E14" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="42">
         <v>0</v>
       </c>
     </row>
@@ -12832,19 +12823,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="18" t="s">
+        <v>658</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>659</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="C2" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="18" t="s">
         <v>660</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>661</v>
       </c>
       <c r="F2" s="19">
         <v>0</v>
@@ -12852,7 +12843,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>7</v>
@@ -12860,7 +12851,7 @@
       <c r="C3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="34" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="18" t="s">
@@ -12870,7 +12861,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>273</v>
@@ -12878,7 +12869,7 @@
       <c r="C4" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="34" t="s">
         <v>274</v>
       </c>
       <c r="E4" s="18" t="s">
@@ -12888,7 +12879,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>275</v>
@@ -12896,7 +12887,7 @@
       <c r="C5" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="34" t="s">
         <v>77</v>
       </c>
       <c r="E5" s="18" t="s">
@@ -12908,7 +12899,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>105</v>
@@ -12916,7 +12907,7 @@
       <c r="C6" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="34" t="s">
         <v>106</v>
       </c>
       <c r="E6" s="18" t="s">
@@ -12926,7 +12917,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>13</v>
@@ -12934,7 +12925,7 @@
       <c r="C7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="34" t="s">
         <v>171</v>
       </c>
       <c r="E7" s="18" t="s">
@@ -12944,7 +12935,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>172</v>
@@ -12952,7 +12943,7 @@
       <c r="C8" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="34" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="18" t="s">
@@ -12964,15 +12955,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="34" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="18" t="s">
@@ -12984,7 +12975,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>174</v>
@@ -12992,7 +12983,7 @@
       <c r="C10" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="34" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="18" t="s">
@@ -13002,7 +12993,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>176</v>
@@ -13010,7 +13001,7 @@
       <c r="C11" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="34" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="18" t="s">
@@ -13022,16 +13013,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="38" t="s">
-        <v>664</v>
+      <c r="D12" s="34" t="s">
+        <v>663</v>
       </c>
       <c r="E12" s="18" t="s">
         <v>23</v>
@@ -13040,16 +13031,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="38" t="s">
-        <v>666</v>
+      <c r="D13" s="34" t="s">
+        <v>665</v>
       </c>
       <c r="E13" s="18" t="s">
         <v>23</v>
@@ -13060,16 +13051,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>666</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="34" t="s">
         <v>667</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="38" t="s">
-        <v>668</v>
       </c>
       <c r="E14" s="18" t="s">
         <v>23</v>
@@ -13080,16 +13071,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C15" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="38" t="s">
-        <v>670</v>
+      <c r="D15" s="34" t="s">
+        <v>669</v>
       </c>
       <c r="E15" s="18" t="s">
         <v>23</v>
@@ -13098,16 +13089,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C16" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="38" t="s">
-        <v>672</v>
+      <c r="D16" s="34" t="s">
+        <v>671</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>23</v>
@@ -13116,16 +13107,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C17" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="38" t="s">
-        <v>670</v>
+      <c r="D17" s="34" t="s">
+        <v>669</v>
       </c>
       <c r="E17" s="18" t="s">
         <v>23</v>
@@ -13134,16 +13125,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C18" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="38" t="s">
-        <v>672</v>
+      <c r="D18" s="34" t="s">
+        <v>671</v>
       </c>
       <c r="E18" s="18" t="s">
         <v>23</v>
@@ -13154,16 +13145,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="38" t="s">
-        <v>676</v>
+      <c r="D19" s="34" t="s">
+        <v>675</v>
       </c>
       <c r="E19" s="18" t="s">
         <v>23</v>
@@ -13172,32 +13163,32 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>68</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E20" s="26"/>
       <c r="F20" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>68</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E21" s="26"/>
       <c r="F21" s="7">
@@ -13206,19 +13197,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B22" s="18" t="s">
+        <v>680</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="18" t="s">
         <v>681</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>682</v>
       </c>
       <c r="F22" s="19">
         <v>0</v>
@@ -13226,34 +13217,34 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B23" s="18" t="s">
+        <v>682</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="18" t="s">
         <v>683</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>684</v>
       </c>
       <c r="F23" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="38" t="s">
-        <v>686</v>
+      <c r="D24" s="34" t="s">
+        <v>685</v>
       </c>
       <c r="E24" s="18" t="s">
         <v>23</v>
@@ -13262,10 +13253,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>68</v>
@@ -13282,15 +13273,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="38" t="s">
+      <c r="D26" s="34" t="s">
         <v>381</v>
       </c>
       <c r="E26" s="18" t="s">
@@ -13300,7 +13291,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B27" s="18" t="s">
         <v>167</v>
@@ -13308,7 +13299,7 @@
       <c r="C27" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="38" t="s">
+      <c r="D27" s="34" t="s">
         <v>382</v>
       </c>
       <c r="E27" s="18" t="s">
@@ -13318,16 +13309,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="38" t="s">
-        <v>690</v>
+      <c r="D28" s="34" t="s">
+        <v>689</v>
       </c>
       <c r="E28" s="18" t="s">
         <v>23</v>
@@ -13336,16 +13327,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="38" t="s">
-        <v>692</v>
+      <c r="D29" s="34" t="s">
+        <v>691</v>
       </c>
       <c r="E29" s="18" t="s">
         <v>23</v>
@@ -13354,7 +13345,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B30" s="18" t="s">
         <v>384</v>
@@ -13362,7 +13353,7 @@
       <c r="C30" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D30" s="38" t="s">
+      <c r="D30" s="34" t="s">
         <v>385</v>
       </c>
       <c r="E30" s="18" t="s">
@@ -13372,15 +13363,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C31" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="38" t="s">
+      <c r="D31" s="34" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="18" t="s">
@@ -13390,19 +13381,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B32" s="18" t="s">
+        <v>693</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="18" t="s">
         <v>694</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>695</v>
       </c>
       <c r="F32" s="17">
         <v>1</v>
@@ -13410,33 +13401,33 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B33" s="18" t="s">
+        <v>695</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="18" t="s">
         <v>696</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>697</v>
       </c>
       <c r="F33" s="17"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C34" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="38" t="s">
+      <c r="D34" s="34" t="s">
         <v>77</v>
       </c>
       <c r="E34" s="18" t="s">
@@ -13448,16 +13439,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B35" s="18" t="s">
+        <v>698</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="34" t="s">
         <v>699</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" s="38" t="s">
-        <v>700</v>
       </c>
       <c r="E35" s="18" t="s">
         <v>23</v>
@@ -13466,16 +13457,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B36" s="18" t="s">
+        <v>700</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="34" t="s">
         <v>701</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" s="38" t="s">
-        <v>702</v>
       </c>
       <c r="E36" s="18" t="s">
         <v>23</v>
@@ -13484,16 +13475,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C37" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D37" s="38" t="s">
-        <v>704</v>
+      <c r="D37" s="34" t="s">
+        <v>703</v>
       </c>
       <c r="E37" s="18" t="s">
         <v>23</v>
@@ -13502,16 +13493,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C38" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="38" t="s">
-        <v>706</v>
+      <c r="D38" s="34" t="s">
+        <v>705</v>
       </c>
       <c r="E38" s="18" t="s">
         <v>23</v>
@@ -13520,16 +13511,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C39" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="38" t="s">
-        <v>708</v>
+      <c r="D39" s="34" t="s">
+        <v>707</v>
       </c>
       <c r="E39" s="18" t="s">
         <v>23</v>
@@ -13538,7 +13529,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B40" s="18" t="s">
         <v>186</v>
@@ -13546,7 +13537,7 @@
       <c r="C40" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="34" t="s">
         <v>187</v>
       </c>
       <c r="E40" s="18" t="s">
@@ -13556,16 +13547,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C41" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="38" t="s">
-        <v>710</v>
+      <c r="D41" s="34" t="s">
+        <v>709</v>
       </c>
       <c r="E41" s="18" t="s">
         <v>23</v>
@@ -13574,16 +13565,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D42" s="38" t="s">
-        <v>712</v>
+      <c r="D42" s="34" t="s">
+        <v>711</v>
       </c>
       <c r="E42" s="18" t="s">
         <v>23</v>
@@ -13592,16 +13583,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B43" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="34" t="s">
         <v>713</v>
-      </c>
-      <c r="C43" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D43" s="38" t="s">
-        <v>714</v>
       </c>
       <c r="E43" s="18" t="s">
         <v>23</v>
@@ -13610,16 +13601,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D44" s="38" t="s">
-        <v>716</v>
+      <c r="D44" s="34" t="s">
+        <v>715</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>23</v>
@@ -13628,16 +13619,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B45" s="18" t="s">
+        <v>716</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="34" t="s">
         <v>717</v>
-      </c>
-      <c r="C45" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" s="38" t="s">
-        <v>718</v>
       </c>
       <c r="E45" s="18" t="s">
         <v>23</v>
@@ -13646,16 +13637,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B46" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="34" t="s">
         <v>719</v>
-      </c>
-      <c r="C46" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D46" s="38" t="s">
-        <v>720</v>
       </c>
       <c r="E46" s="18" t="s">
         <v>23</v>
@@ -13664,16 +13655,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C47" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D47" s="38" t="s">
-        <v>722</v>
+      <c r="D47" s="34" t="s">
+        <v>721</v>
       </c>
       <c r="E47" s="18" t="s">
         <v>23</v>
@@ -13682,7 +13673,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B48" s="18" t="s">
         <v>654</v>
@@ -13690,7 +13681,7 @@
       <c r="C48" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="38" t="s">
+      <c r="D48" s="34" t="s">
         <v>655</v>
       </c>
       <c r="E48" s="18" t="s">
@@ -13700,15 +13691,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C49" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="38" t="s">
+      <c r="D49" s="34" t="s">
         <v>77</v>
       </c>
       <c r="E49" s="18" t="s">
@@ -13720,16 +13711,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B50" s="18" t="s">
+        <v>723</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="34" t="s">
         <v>724</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D50" s="38" t="s">
-        <v>725</v>
       </c>
       <c r="E50" s="18" t="s">
         <v>23</v>
@@ -13738,16 +13729,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B51" s="18" t="s">
+        <v>725</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="34" t="s">
         <v>726</v>
-      </c>
-      <c r="C51" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D51" s="38" t="s">
-        <v>727</v>
       </c>
       <c r="E51" s="18" t="s">
         <v>23</v>
@@ -13758,16 +13749,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B52" s="18" t="s">
+        <v>727</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" s="34" t="s">
         <v>728</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D52" s="38" t="s">
-        <v>729</v>
       </c>
       <c r="E52" s="18" t="s">
         <v>23</v>
@@ -13778,16 +13769,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C53" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="38" t="s">
-        <v>731</v>
+      <c r="D53" s="34" t="s">
+        <v>730</v>
       </c>
       <c r="E53" s="18" t="s">
         <v>164</v>
@@ -13796,34 +13787,34 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B54" s="18" t="s">
+        <v>731</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="34" t="s">
         <v>732</v>
       </c>
-      <c r="C54" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D54" s="38" t="s">
-        <v>733</v>
-      </c>
       <c r="E54" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F54" s="38"/>
+      <c r="F54" s="34"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C55" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D55" s="38" t="s">
-        <v>735</v>
+      <c r="D55" s="34" t="s">
+        <v>734</v>
       </c>
       <c r="E55" s="18" t="s">
         <v>23</v>
@@ -13832,16 +13823,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C56" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D56" s="38" t="s">
-        <v>737</v>
+      <c r="D56" s="34" t="s">
+        <v>736</v>
       </c>
       <c r="E56" s="18" t="s">
         <v>23</v>
@@ -13850,16 +13841,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C57" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="38" t="s">
-        <v>739</v>
+      <c r="D57" s="34" t="s">
+        <v>738</v>
       </c>
       <c r="E57" s="18" t="s">
         <v>23</v>
@@ -13868,16 +13859,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C58" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="38" t="s">
-        <v>737</v>
+      <c r="D58" s="34" t="s">
+        <v>736</v>
       </c>
       <c r="E58" s="18" t="s">
         <v>23</v>
@@ -13886,16 +13877,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B59" s="18" t="s">
+        <v>740</v>
+      </c>
+      <c r="C59" s="18" t="s">
         <v>741</v>
       </c>
-      <c r="C59" s="18" t="s">
+      <c r="D59" s="34" t="s">
         <v>742</v>
-      </c>
-      <c r="D59" s="38" t="s">
-        <v>743</v>
       </c>
       <c r="E59" s="18" t="s">
         <v>23</v>
@@ -13904,16 +13895,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C60" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D60" s="38" t="s">
-        <v>745</v>
+      <c r="D60" s="34" t="s">
+        <v>744</v>
       </c>
       <c r="E60" s="18" t="s">
         <v>23</v>
@@ -13922,16 +13913,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C61" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D61" s="38" t="s">
-        <v>745</v>
+      <c r="D61" s="34" t="s">
+        <v>744</v>
       </c>
       <c r="E61" s="18" t="s">
         <v>23</v>
@@ -13942,16 +13933,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C62" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D62" s="38" t="s">
-        <v>737</v>
+      <c r="D62" s="34" t="s">
+        <v>736</v>
       </c>
       <c r="E62" s="18" t="s">
         <v>23</v>
@@ -13960,16 +13951,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B63" s="18" t="s">
+        <v>747</v>
+      </c>
+      <c r="C63" s="18" t="s">
+        <v>741</v>
+      </c>
+      <c r="D63" s="34" t="s">
         <v>748</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>742</v>
-      </c>
-      <c r="D63" s="38" t="s">
-        <v>749</v>
       </c>
       <c r="E63" s="18" t="s">
         <v>23</v>
@@ -13978,19 +13969,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5">
       <c r="A64" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C64" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D64" s="38" t="s">
+      <c r="D64" s="34" t="s">
         <v>14</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F64" s="19">
         <v>1</v>
@@ -13998,16 +13989,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
       <c r="A65" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C65" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D65" s="38" t="s">
-        <v>752</v>
+      <c r="D65" s="34" t="s">
+        <v>751</v>
       </c>
       <c r="E65" s="18" t="s">
         <v>23</v>
@@ -14016,16 +14007,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C66" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D66" s="38" t="s">
-        <v>754</v>
+      <c r="D66" s="34" t="s">
+        <v>753</v>
       </c>
       <c r="E66" s="18" t="s">
         <v>23</v>
@@ -14034,16 +14025,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="26" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C67" s="26" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E67" s="26" t="s">
         <v>23</v>
@@ -14052,16 +14043,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="26" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C68" s="26" t="s">
         <v>25</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E68" s="26" t="s">
         <v>23</v>
@@ -14070,16 +14061,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="26" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C69" s="26" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E69" s="26" t="s">
         <v>23</v>
@@ -14088,16 +14079,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="19.5">
       <c r="A70" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B70" s="18" t="s">
+        <v>760</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="34" t="s">
         <v>761</v>
-      </c>
-      <c r="C70" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D70" s="38" t="s">
-        <v>762</v>
       </c>
       <c r="E70" s="18" t="s">
         <v>23</v>
@@ -14125,7 +14116,7 @@
     <col min="6" max="6" style="11" width="23.433571428571426" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -14145,7 +14136,7 @@
         <v>598</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="6" t="s">
         <v>599</v>
       </c>
@@ -14165,7 +14156,7 @@
         <v>598</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="6" t="s">
         <v>599</v>
       </c>
@@ -14185,7 +14176,7 @@
         <v>598</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="6" t="s">
         <v>599</v>
       </c>
@@ -14205,7 +14196,7 @@
         <v>598</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="6" t="s">
         <v>599</v>
       </c>
@@ -14225,7 +14216,7 @@
         <v>598</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="6" t="s">
         <v>599</v>
       </c>
@@ -14245,7 +14236,7 @@
         <v>598</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="6" t="s">
         <v>599</v>
       </c>
@@ -14265,7 +14256,7 @@
         <v>598</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="6" t="s">
         <v>599</v>
       </c>
@@ -14285,7 +14276,7 @@
         <v>598</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="6" t="s">
         <v>599</v>
       </c>
@@ -14305,7 +14296,7 @@
         <v>598</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="6" t="s">
         <v>599</v>
       </c>
@@ -14325,7 +14316,7 @@
         <v>598</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="6" t="s">
         <v>599</v>
       </c>
@@ -14345,7 +14336,7 @@
         <v>598</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="6" t="s">
         <v>599</v>
       </c>
@@ -14365,7 +14356,7 @@
         <v>598</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="6" t="s">
         <v>599</v>
       </c>
@@ -14385,7 +14376,7 @@
         <v>598</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="6" t="s">
         <v>599</v>
       </c>
@@ -14405,7 +14396,7 @@
         <v>598</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="6" t="s">
         <v>599</v>
       </c>
@@ -14425,7 +14416,7 @@
         <v>598</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="6" t="s">
         <v>599</v>
       </c>
@@ -14814,44 +14805,20 @@
       <c r="F35" s="33"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="34" t="s">
-        <v>658</v>
-      </c>
-      <c r="B36" s="35" t="s">
-        <v>658</v>
-      </c>
-      <c r="C36" s="35" t="s">
-        <v>658</v>
-      </c>
-      <c r="D36" s="35" t="s">
-        <v>658</v>
-      </c>
-      <c r="E36" s="35" t="s">
-        <v>658</v>
-      </c>
-      <c r="F36" s="36" t="s">
-        <v>658</v>
-      </c>
+      <c r="A36" s="6"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="17"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="34" t="s">
-        <v>658</v>
-      </c>
-      <c r="B37" s="34" t="s">
-        <v>658</v>
-      </c>
-      <c r="C37" s="34" t="s">
-        <v>658</v>
-      </c>
-      <c r="D37" s="34" t="s">
-        <v>658</v>
-      </c>
-      <c r="E37" s="34" t="s">
-        <v>658</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>658</v>
-      </c>
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
